--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFFE2AF-ED0B-49C2-AB09-F55F9C29EE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECB1905-E940-4D83-8C55-54A5BADAA702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="2388" windowWidth="14484" windowHeight="6948" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="0" yWindow="504" windowWidth="17256" windowHeight="10440" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="explanation" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,19 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>Wave1</t>
   </si>
   <si>
-    <t>HP:1.2:10;ATK:1.1:0,Speed:1.1:0,DashSpeed:1.1:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>HP:1.5:10;ATK:1.5:0,Speed:2.0:0,DashSpeed:1.1:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Enemy_Normal_Comp</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -116,6 +109,599 @@
   </si>
   <si>
     <t>SpawnOval</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>↓例</t>
+    <rPh sb="1" eb="2">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>WaveDataアセットの名前。
+同じ名前を指定することで、
+同じアセット内に生成情報が記録される。</t>
+    <rPh sb="13" eb="15">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>セイセイジョウホウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成する敵プレハブの名前。
+フォルダ内にある敵のプレハブを記録する。
+(フォルダの参照先はAssets/06_Prefabs/Unit/Character/Enemy/EnemyComp)</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>サンショウサキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成処理を行う回数。</t>
+    <rPh sb="0" eb="4">
+      <t>セイセイショリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>敵の最小の生成数。
+Maxの値との間の乱数が
+実際の生成数となる。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ランスウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>セイセイスウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>敵の最大の生成数。
+Minの値との間の乱数が
+実際の生成数となる。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この生成処理を初めて行う時間。</t>
+    <rPh sb="2" eb="6">
+      <t>セイセイショリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この生成処理を強制終了する時間。
+（0の場合何も指定しないことと同意義）</t>
+    <rPh sb="2" eb="6">
+      <t>セイセイショリ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>キョウセイシュウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イギ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この生成処理を行う間隔。
+（基本0.01以上の値を指定する）</t>
+    <rPh sb="2" eb="6">
+      <t>セイセイショリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウェーブごとの敵の成長率。
+値が0.1のときウェーブ2であれば1.1倍の強化。
+ウェーブ9であれば1.9倍の強化となる。</t>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>セイチョウリツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>最初の生成時の</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>名。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成される場所に配置される
+エフェクト名。</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成した敵が自動で死亡するまでのカウント数。
+（0の場合何も指定しないことと同意義）</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>敵生成の法則。
+（ISpawnComponent継承クラス名で指定する。）</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウソク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケイショウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnRandom：画面外のランダムな位置から生成
+SpawnSide：画面外の特定の方向から生成
+SpawnOval：プレイヤーを中心とした楕円形になるように生成
+SpawnRectangle：プレイヤーを中心とした長方形になるように生成</t>
+    <rPh sb="38" eb="41">
+      <t>ガメンガイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="73" eb="76">
+      <t>ダエンケイ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="111" eb="114">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>強化するステータスと強化倍率と強化固定値。
+（「ステータス名:倍率:固定値」 の順で記述する）
+（複数指定する場合は「;」で区切る）</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+MaxHP:1.2:10;ATK:1.1:0,Speed:1.1:0,DashSpeed:1.1:0</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コテイチ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>コテイチ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="49" eb="53">
+      <t>フクスウシテイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>クギ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.2:10;ATK:1.1:0,Speed:1.1:0,DashSpeed:1.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.5:10;ATK:1.5:0,Speed:2.0:0,DashSpeed:1.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP：最大HP
+ATK：攻撃倍率（1.0なら100%、2.5なら250%）
+DEF：防御ダメージ量（1なら5ダメージが4ダメージに減少）
+Speed：基本移動速度
+DashSpeed：アクション時の移動速度
+DamageRatio：被弾ダメージ倍率（1.5なら10ダメージが15ダメージ、計算式の最後に倍率加算）</t>
+    <rPh sb="6" eb="8">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="80" eb="84">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="102" eb="106">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="147" eb="150">
+      <t>ケイサンシキ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>false：フラグを設定しない。
+true：フラグを設定する。</t>
+    <rPh sb="10" eb="12">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成する敵にクリアフラグを
+設定するか否か。
+（クリアフラグ対象の全滅でクリアとなる）</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゼンメツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：未設定</t>
+    <rPh sb="2" eb="5">
+      <t>ミセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：未設定</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：生成を行わない。</t>
+    <rPh sb="2" eb="4">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：生成を行わない。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未入力：生成を行わない。</t>
+    <rPh sb="0" eb="3">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未入力：エフェクトなし。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未入力：SEなし。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>同名：同じアセット内に生成情報を記録。</t>
+    <rPh sb="0" eb="2">
+      <t>ドウメイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>セイセイジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キロク</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -123,7 +709,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +737,22 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,7 +792,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -199,6 +801,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,49 +1145,49 @@
   <sheetData>
     <row r="1" spans="1:15" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -581,7 +1195,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
@@ -613,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -624,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -656,11 +1270,264 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22332C8A-7304-4E64-9BD3-13AF5949C9BF}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="39.8984375" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="25.3984375" customWidth="1"/>
+    <col min="4" max="4" width="22.3984375" customWidth="1"/>
+    <col min="5" max="5" width="23.09765625" customWidth="1"/>
+    <col min="6" max="6" width="32.8984375" customWidth="1"/>
+    <col min="7" max="7" width="37.3984375" customWidth="1"/>
+    <col min="8" max="8" width="30.8984375" customWidth="1"/>
+    <col min="9" max="9" width="41.796875" customWidth="1"/>
+    <col min="10" max="10" width="42.296875" customWidth="1"/>
+    <col min="11" max="11" width="27.69921875" customWidth="1"/>
+    <col min="12" max="12" width="22.296875" customWidth="1"/>
+    <col min="13" max="13" width="38.09765625" customWidth="1"/>
+    <col min="14" max="14" width="86.19921875" customWidth="1"/>
+    <col min="15" max="15" width="59.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="28.2" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="108" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECB1905-E940-4D83-8C55-54A5BADAA702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419673CA-17B6-4BFF-A953-5B56551926AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="17256" windowHeight="10440" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="0" yWindow="3468" windowWidth="21264" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="explanation" sheetId="2" r:id="rId2"/>
+    <sheet name="TestData" sheetId="4" r:id="rId2"/>
+    <sheet name="explanation" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="103">
   <si>
     <t>Wave1</t>
   </si>
@@ -332,90 +333,6 @@
     </rPh>
     <rPh sb="54" eb="56">
       <t>キョウカ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>最初の生成時の</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>名。</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>生成される場所に配置される
-エフェクト名。</t>
-    <rPh sb="0" eb="2">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>生成した敵が自動で死亡するまでのカウント数。
-（0の場合何も指定しないことと同意義）</t>
-    <rPh sb="0" eb="2">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シボウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>スウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -622,30 +539,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>生成する敵にクリアフラグを
-設定するか否か。
-（クリアフラグ対象の全滅でクリアとなる）</t>
-    <rPh sb="0" eb="2">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>イナ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ゼンメツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>0：未設定</t>
     <rPh sb="2" eb="5">
       <t>ミセッテイ</t>
@@ -653,10 +546,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>0：未設定</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>0：生成を行わない。</t>
     <rPh sb="2" eb="4">
       <t>セイセイ</t>
@@ -678,10 +567,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>未入力：エフェクトなし。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>未入力：SEなし。</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -702,6 +587,547 @@
     <rPh sb="16" eb="18">
       <t>キロク</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[0] WaveName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[1] PrefabName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[2] ProcessCount</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[3] ProcessIntervalInterval</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[4] SpawnMin</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[5] SpawnMax</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[6] ProcessStart</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[7] ProcessEnd</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[8] SpawnDelay</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[9] WaveIncreaseRate</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[10] DestroyTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[12] PreviewEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[11] IsClear</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[14] FirstProcessSEName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[15] FirstProcessSEVolume</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[16] StatusOverrides</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[17] CompClass</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[18] CompClass.ApplyParameters</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TestWave1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TestWave2</t>
+  </si>
+  <si>
+    <t>MaxHP:1.5:10;ATK:1.5:0,Speed:2.0:0,DashSpeed:1.1:1</t>
+  </si>
+  <si>
+    <t>TestWave3</t>
+  </si>
+  <si>
+    <t>MaxHP:1.5:10;ATK:1.5:0,Speed:2.0:0,DashSpeed:1.1:2</t>
+  </si>
+  <si>
+    <t>SpawnSide</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:Right</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnRectangle</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:10;sizey:7</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>敵生成の法則ごとに設定するパラメーター。
+（各パラメーターごとの変数名で指定する。）</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウソク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[13] SpawneEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成される前に
+生成場所に配置される予告エフェクト名。</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>セイセイバショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヨコク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成された瞬間に
+生成場所に配置される生成エフェクト名。</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュンカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>最初の処理開始時の</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>名。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セイジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>最初の処理開始時の</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の音量。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セイジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0~1の値</t>
+    <rPh sb="4" eb="5">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>敵生成のディレイ。
+（予告エフェクトから敵生成するまで）</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨコク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成する敵にクリアフラグを
+設定するか否か。
+（クリアフラグ対象の全滅で
+ゲームクリアとなる）</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゼンメツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成した敵が自動で死亡するまでの計測時間。
+（0の場合何も指定しないことと同意義）</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ケイソクジカン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>radiusx:10;radiusy:8</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnRandom：入力無し
+SpawnSide：spawnDirection:Right（方角を指定する：Right,Left,Up,Down,UpperRight,UpperLeft,LowerRight,LowerLeft）
+SpawnOval：radiusx:10;radiusy:8（楕円のX軸;楕円のY軸）
+SpawnRectangle：sizex:10;sizey:7（長方形のX軸;長方形のY軸）</t>
+    <rPh sb="12" eb="15">
+      <t>ニュウリョクナ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ホウガク</t>
+    </rPh>
+    <rPh sb="194" eb="197">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="201" eb="204">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0.01以下：処理の一部がスキップされるかも。</t>
+    <rPh sb="4" eb="6">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>59以上：生成を行わない。
+（ウェーブ時間を超えるため）</t>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：未設定
+59以上：処理終了を行わない。
+（ウェーブ時間を超えるため）</t>
+    <rPh sb="8" eb="10">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0：ディレイ無し</t>
+    <rPh sb="6" eb="7">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GenerationNotice</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnLanding</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未入力：エフェクトなし。
+(EnemySpawnerに設定された
+ デフォルトエフェクトを使用する)
+GenerationNotice：赤！マーク</t>
+    <rPh sb="27" eb="29">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>アカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未入力：エフェクトなし。
+SpawnLanding：着地土埃</t>
+    <rPh sb="26" eb="28">
+      <t>チャクチ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ツチボコリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:1.0:0,DashSpeed:1.0:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:00;ATK:1.0:0,Speed:1.0:0,DashSpeed:1.0:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[3] ProcessCount</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[4] ProcessIntervalInterval</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[5] SpawnMin</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[6] SpawnMax</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[2] ProcessStartTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[7] ProcessEndTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:Left</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:Up</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:Down</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Boss_Normal_Comp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:18;sizey:12</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -763,7 +1189,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -786,13 +1212,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -813,6 +1291,18 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1128,153 +1618,827 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.296875" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" customWidth="1"/>
-    <col min="3" max="8" width="9.8984375" customWidth="1"/>
-    <col min="9" max="9" width="11.296875" customWidth="1"/>
-    <col min="10" max="12" width="9.8984375" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" customWidth="1"/>
-    <col min="14" max="14" width="54.5" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="17" width="15.09765625" customWidth="1"/>
-    <col min="18" max="20" width="19.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.69921875" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" customWidth="1"/>
+    <col min="5" max="5" width="27.19921875" customWidth="1"/>
+    <col min="6" max="7" width="15.19921875" customWidth="1"/>
+    <col min="8" max="8" width="20.59765625" customWidth="1"/>
+    <col min="9" max="9" width="16.3984375" customWidth="1"/>
+    <col min="10" max="10" width="24.796875" customWidth="1"/>
+    <col min="11" max="11" width="16.796875" customWidth="1"/>
+    <col min="12" max="12" width="16.19921875" customWidth="1"/>
+    <col min="13" max="14" width="24.59765625" customWidth="1"/>
+    <col min="15" max="15" width="25.796875" customWidth="1"/>
+    <col min="16" max="16" width="27.19921875" customWidth="1"/>
+    <col min="17" max="17" width="63.19921875" customWidth="1"/>
+    <col min="18" max="18" width="23.59765625" customWidth="1"/>
+    <col min="19" max="19" width="35.796875" customWidth="1"/>
+    <col min="20" max="21" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>15</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="7"/>
+    </row>
+    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>5</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="8"/>
+    </row>
+    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="8"/>
+    </row>
+    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9">
+        <v>25</v>
+      </c>
+      <c r="D7" s="10">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10">
+        <v>25</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>15</v>
+      </c>
+      <c r="G9" s="8">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>40</v>
+      </c>
+      <c r="D10" s="8">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
+      <c r="E10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="2" t="s">
+    <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8">
+        <v>40</v>
+      </c>
+      <c r="D11" s="8">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8">
+        <v>45</v>
+      </c>
+      <c r="D12" s="10">
+        <v>5</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8">
+        <v>45</v>
+      </c>
+      <c r="D13" s="10">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8">
+        <v>50</v>
+      </c>
+      <c r="D14" s="10">
+        <v>5</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R14" s="8" t="s">
         <v>17</v>
       </c>
+      <c r="S14" s="8"/>
     </row>
-    <row r="3" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>18</v>
-      </c>
+    <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="8">
+        <v>59</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S15" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -1283,75 +2447,397 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D671765-6BFE-4606-9C59-1F74507BF60E}">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.69921875" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" customWidth="1"/>
+    <col min="5" max="5" width="27.19921875" customWidth="1"/>
+    <col min="6" max="7" width="15.19921875" customWidth="1"/>
+    <col min="8" max="8" width="20.59765625" customWidth="1"/>
+    <col min="9" max="9" width="16.3984375" customWidth="1"/>
+    <col min="10" max="10" width="24.796875" customWidth="1"/>
+    <col min="11" max="11" width="16.796875" customWidth="1"/>
+    <col min="12" max="12" width="16.19921875" customWidth="1"/>
+    <col min="13" max="14" width="24.59765625" customWidth="1"/>
+    <col min="15" max="15" width="25.796875" customWidth="1"/>
+    <col min="16" max="16" width="27.19921875" customWidth="1"/>
+    <col min="17" max="17" width="63.19921875" customWidth="1"/>
+    <col min="18" max="18" width="23.59765625" customWidth="1"/>
+    <col min="19" max="19" width="35.796875" customWidth="1"/>
+    <col min="20" max="21" width="19.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="2"/>
+    </row>
+    <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22332C8A-7304-4E64-9BD3-13AF5949C9BF}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="39.8984375" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="2" max="2" width="56.296875" customWidth="1"/>
     <col min="3" max="3" width="25.3984375" customWidth="1"/>
-    <col min="4" max="4" width="22.3984375" customWidth="1"/>
-    <col min="5" max="5" width="23.09765625" customWidth="1"/>
-    <col min="6" max="6" width="32.8984375" customWidth="1"/>
-    <col min="7" max="7" width="37.3984375" customWidth="1"/>
-    <col min="8" max="8" width="30.8984375" customWidth="1"/>
+    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="6" width="26.19921875" customWidth="1"/>
+    <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="8" max="8" width="37.296875" customWidth="1"/>
     <col min="9" max="9" width="41.796875" customWidth="1"/>
     <col min="10" max="10" width="42.296875" customWidth="1"/>
-    <col min="11" max="11" width="27.69921875" customWidth="1"/>
-    <col min="12" max="12" width="22.296875" customWidth="1"/>
-    <col min="13" max="13" width="38.09765625" customWidth="1"/>
-    <col min="14" max="14" width="86.19921875" customWidth="1"/>
-    <col min="15" max="15" width="59.8984375" customWidth="1"/>
+    <col min="11" max="11" width="43.8984375" customWidth="1"/>
+    <col min="12" max="12" width="28.19921875" customWidth="1"/>
+    <col min="13" max="14" width="37.8984375" customWidth="1"/>
+    <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="16" max="16" width="31.5" customWidth="1"/>
+    <col min="17" max="17" width="86.296875" customWidth="1"/>
+    <col min="18" max="18" width="62.59765625" customWidth="1"/>
+    <col min="19" max="19" width="109.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28.2" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:19" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:19" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -1362,88 +2848,118 @@
         <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="I2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="R2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="108" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>33</v>
+      <c r="S3" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="108" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1490,7 +3006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419673CA-17B6-4BFF-A953-5B56551926AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603B960F-F1F9-432D-9097-76E162874693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3468" windowWidth="21264" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="0" yWindow="24" windowWidth="20760" windowHeight="12012" activeTab="3" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ImportData" sheetId="1" r:id="rId1"/>
     <sheet name="TestData" sheetId="4" r:id="rId2"/>
     <sheet name="explanation" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,73 +36,113 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={65B6A188-F81E-4121-9301-0FFE406E0779}</author>
+    <author>tc={D610F583-95B2-4ADF-A107-F230AC715730}</author>
+    <author>tc={7F798097-5361-4E6E-B97D-EF1CCEC6F0C1}</author>
+    <author>tc={FDFDCC22-BE58-4D42-8331-AAB5B041174C}</author>
+    <author>tc={07931406-406C-431D-B4C7-2BB098EFE2B7}</author>
+    <author>tc={51A3F559-40AA-431D-88AE-A6E41F82C579}</author>
+    <author>tc={EB6B3A68-8148-45AE-9278-985634B59876}</author>
+    <author>tc={2EA2148F-5DB8-45A5-B6B5-E8B64F389B05}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{65B6A188-F81E-4121-9301-0FFE406E0779}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave1
+ノーマルの動きを知ってもらう。
+最初なので生成数は少なめを意識。</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="1" shapeId="0" xr:uid="{D610F583-95B2-4ADF-A107-F230AC715730}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave２
+Wave１より出現数を増やす。
+まだノーマルのみでゲームに慣れさせる。
+生成法則でバリエーションを増やす。</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="2" shapeId="0" xr:uid="{7F798097-5361-4E6E-B97D-EF1CCEC6F0C1}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave３
+スナイパーの動きを知ってもらう。
+ノーマルの生成を減らす。</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="3" shapeId="0" xr:uid="{FDFDCC22-BE58-4D42-8331-AAB5B041174C}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave４
+スナイパーとノーマルを交互に生成する。
+ノーマルはプレイヤーの近くに生成する。
+２種同時に対処する方法を学習させる。</t>
+      </text>
+    </comment>
+    <comment ref="A43" authorId="4" shapeId="0" xr:uid="{07931406-406C-431D-B4C7-2BB098EFE2B7}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</t>
+      </text>
+    </comment>
+    <comment ref="A51" authorId="5" shapeId="0" xr:uid="{51A3F559-40AA-431D-88AE-A6E41F82C579}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave５
+スナイパーをより多く出現させる。
+弾幕の中を移動する方法を探らせる。</t>
+      </text>
+    </comment>
+    <comment ref="A65" authorId="6" shapeId="0" xr:uid="{EB6B3A68-8148-45AE-9278-985634B59876}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave６
+タンクの動きを知ってもらう。
+ノーマルとタンクを同時に対処する方法を探らせる。
+ボスを２体同時に出現させる。</t>
+      </text>
+    </comment>
+    <comment ref="A82" authorId="7" shapeId="0" xr:uid="{2EA2148F-5DB8-45A5-B6B5-E8B64F389B05}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave７
+主にスナイパーとタンクを出現させ、
+対処法を探らせる。
+ノーマルを囲み要因として使う。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="136">
   <si>
     <t>Wave1</t>
   </si>
   <si>
     <t>Enemy_Normal_Comp</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>WaveName</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>PrefabName</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Min</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Max</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Start</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>End</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Interval</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>StatusRate</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Destroy</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Effect</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>SE</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>IsClear</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>StatusOverrides</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>CompClass</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -117,10 +158,6 @@
     <rPh sb="1" eb="2">
       <t>レイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Wave1</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -560,13 +597,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>未入力：生成を行わない。</t>
-    <rPh sb="0" eb="3">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>未入力：SEなし。</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -595,30 +625,6 @@
   </si>
   <si>
     <t>[1] PrefabName</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[2] ProcessCount</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[3] ProcessIntervalInterval</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[4] SpawnMin</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[5] SpawnMax</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[6] ProcessStart</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>[7] ProcessEnd</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1127,7 +1133,258 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>sizex:18;sizey:12</t>
+    <t>未入力：生成を行わない。
+Enemy_Normal_Comp
+Boss_Normal_Comp
+Enemy_Sniper_Comp
+Boss_Sniper_Comp
+Enemy_Tank_Comp
+Enemy_Tank_Comp</t>
+    <rPh sb="0" eb="3">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave2</t>
+  </si>
+  <si>
+    <t>Wave2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnSide</t>
+  </si>
+  <si>
+    <t>SpawnRectangle</t>
+  </si>
+  <si>
+    <t>SpawnRandom</t>
+  </si>
+  <si>
+    <t>[5] CompClass</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[6] CompClass.ApplyParameters</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[7] SpawnMin</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[8] SpawnMax</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[9] ProcessEndTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[10] SpawnDelay</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[11] WaveIncreaseRate</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[12] StatusOverrides</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[13] DestroyTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[14] IsClear</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[15] PreviewEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[16] SpawneEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[17] FirstProcessSEName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[18] FirstProcessSEVolume</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[2] ProcessStart</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[9] ProcessEnd</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:1.0:0,DashSpeed:1.0:0</t>
+  </si>
+  <si>
+    <t>Wave3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Enemy_Sniper_Comp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnOval</t>
+  </si>
+  <si>
+    <t>spawnDirection:UpperRight</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:LowerLeft</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:UpperLeft</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>spawnDirection:LowerRight</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Boss_Sniper_Comp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave4</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:14;sizey:10</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:20;sizey:16</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.25:0;ATK:1.25:0,Speed:1.1:0,DashSpeed:1.1:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.25:0;ATK:1.25:0,Speed:1.1:0,DashSpeed:1.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.7:0;ATK:1.7:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.7:0;ATK:1.7:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:1.6:0,DashSpeed:1.6:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:1.6:0,DashSpeed:1.6:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.0:20;ATK:2.0:0,Speed:0.2:0,DashSpeed:0.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Lv</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>NextLevelExp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>NextLevelRate</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave5</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>radiusx:15;radiusy:12</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:10;sizey:8</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:16;sizey:13</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.5:0;ATK:2.2:0,Speed:1.8:0,DashSpeed:1.8:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave6</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Enemy_Tank_Comp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:16;sizey:12</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave7</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.75:0;ATK:2.5:0,Speed:1.9:0,DashSpeed:1.9:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.75:0;ATK:2.5:0,Speed:1.9:0,DashSpeed:1.9:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:2.75:0,Speed:2.0:0,DashSpeed:2.0:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生成情報にパラメータ実装済み　インポート設計に追加する</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>セイセイジョウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ツイカ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1135,7 +1392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1180,6 +1437,12 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1189,7 +1452,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1264,13 +1527,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1304,6 +1610,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1319,6 +1634,1052 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NextLevelExp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$AY$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43.199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.839999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62.207999999999991</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.649599999999992</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>89.579519999999988</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107.49542399999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128.99450879999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>154.79341055999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>185.75209267199995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>222.90251120639994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>267.48301344767992</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>320.97961613721588</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>385.17553936465907</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>462.21064723759088</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>554.65277668510907</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>665.58333202213089</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>798.69999842655704</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>958.43999811186836</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1150.1279977342419</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1380.1535972810902</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1656.1843167373083</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1987.42118008477</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2384.9054161017239</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2861.8864993220686</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3434.2637991864822</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4121.1165590237788</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4945.339870828534</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5934.4078449942408</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7121.2894139930886</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8545.5472967917067</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10254.656756150047</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>12305.588107380056</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14766.705728856066</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17720.046874627278</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>21264.056249552734</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>25516.867499463278</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>30620.240999355934</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>36744.289199227118</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44093.147039072537</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>52911.776446887045</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>63494.131736264448</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>76192.95808351734</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>91431.549700220799</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>109717.85964026496</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>131661.43156831793</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>157993.71788198152</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>189592.4614583778</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>227510.95375005336</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0954-4B96-B698-D957363CF405}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1103807215"/>
+        <c:axId val="1103805295"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1103807215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1103805295"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1103805295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1103807215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97467BE8-ADA0-2891-FC0F-E6DACA46173E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="希空 山中" id="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" userId="1ee968124d7379dd" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1616,9 +2977,57 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2026-02-09T05:45:06.73" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{65B6A188-F81E-4121-9301-0FFE406E0779}">
+    <text>〇Wave1
+ノーマルの動きを知ってもらう。
+最初なので生成数は少なめを意識。</text>
+  </threadedComment>
+  <threadedComment ref="A14" dT="2026-02-09T05:44:23.57" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{D610F583-95B2-4ADF-A107-F230AC715730}">
+    <text>〇Wave２
+Wave１より出現数を増やす。
+まだノーマルのみでゲームに慣れさせる。
+生成法則でバリエーションを増やす。</text>
+  </threadedComment>
+  <threadedComment ref="A24" dT="2026-02-09T05:43:11.55" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{7F798097-5361-4E6E-B97D-EF1CCEC6F0C1}">
+    <text>〇Wave３
+スナイパーの動きを知ってもらう。
+ノーマルの生成を減らす。</text>
+  </threadedComment>
+  <threadedComment ref="A37" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{FDFDCC22-BE58-4D42-8331-AAB5B041174C}">
+    <text>〇Wave４
+スナイパーとノーマルを交互に生成する。
+ノーマルはプレイヤーの近くに生成する。
+２種同時に対処する方法を学習させる。</text>
+  </threadedComment>
+  <threadedComment ref="A43" dT="2026-02-09T06:02:10.44" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{07931406-406C-431D-B4C7-2BB098EFE2B7}">
+    <text>囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</text>
+  </threadedComment>
+  <threadedComment ref="A51" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{51A3F559-40AA-431D-88AE-A6E41F82C579}">
+    <text>〇Wave５
+スナイパーをより多く出現させる。
+弾幕の中を移動する方法を探らせる。</text>
+  </threadedComment>
+  <threadedComment ref="A65" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{EB6B3A68-8148-45AE-9278-985634B59876}">
+    <text>〇Wave６
+タンクの動きを知ってもらう。
+ノーマルとタンクを同時に対処する方法を探らせる。
+ボスを２体同時に出現させる。</text>
+  </threadedComment>
+  <threadedComment ref="A82" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{2EA2148F-5DB8-45A5-B6B5-E8B64F389B05}">
+    <text>〇Wave７
+主にスナイパーとタンクを出現させ、
+対処法を探らせる。
+ノーマルを囲み要因として使う。</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
-  <dimension ref="A1:S15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
+  <dimension ref="A1:S83"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.69921875" customWidth="1"/>
@@ -1626,78 +3035,78 @@
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="17.09765625" customWidth="1"/>
     <col min="5" max="5" width="27.19921875" customWidth="1"/>
-    <col min="6" max="7" width="15.19921875" customWidth="1"/>
-    <col min="8" max="8" width="20.59765625" customWidth="1"/>
-    <col min="9" max="9" width="16.3984375" customWidth="1"/>
-    <col min="10" max="10" width="24.796875" customWidth="1"/>
-    <col min="11" max="11" width="16.796875" customWidth="1"/>
-    <col min="12" max="12" width="16.19921875" customWidth="1"/>
-    <col min="13" max="14" width="24.59765625" customWidth="1"/>
-    <col min="15" max="15" width="25.796875" customWidth="1"/>
-    <col min="16" max="16" width="27.19921875" customWidth="1"/>
-    <col min="17" max="17" width="63.19921875" customWidth="1"/>
-    <col min="18" max="18" width="23.59765625" customWidth="1"/>
-    <col min="19" max="19" width="35.796875" customWidth="1"/>
+    <col min="6" max="6" width="23.59765625" customWidth="1"/>
+    <col min="7" max="7" width="35.796875" customWidth="1"/>
+    <col min="8" max="9" width="15.19921875" customWidth="1"/>
+    <col min="10" max="10" width="20.59765625" customWidth="1"/>
+    <col min="11" max="11" width="16.3984375" customWidth="1"/>
+    <col min="12" max="12" width="24.796875" customWidth="1"/>
+    <col min="13" max="13" width="63.19921875" customWidth="1"/>
+    <col min="14" max="14" width="16.796875" customWidth="1"/>
+    <col min="15" max="15" width="16.19921875" customWidth="1"/>
+    <col min="16" max="17" width="24.59765625" customWidth="1"/>
+    <col min="18" max="18" width="25.796875" customWidth="1"/>
+    <col min="19" max="19" width="27.19921875" customWidth="1"/>
     <col min="20" max="21" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -1711,22 +3120,20 @@
         <v>0</v>
       </c>
       <c r="D2" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="7"/>
       <c r="H2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="7">
         <v>0</v>
@@ -1734,22 +3141,24 @@
       <c r="K2" s="7">
         <v>0</v>
       </c>
-      <c r="L2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="7"/>
+      <c r="L2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
@@ -1767,17 +3176,15 @@
       <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1</v>
-      </c>
+      <c r="F3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="8"/>
       <c r="H3" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -1785,22 +3192,24 @@
       <c r="K3" s="8">
         <v>0</v>
       </c>
-      <c r="L3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" s="8"/>
+      <c r="L3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
@@ -1810,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" s="8">
         <v>3</v>
@@ -1818,17 +3227,17 @@
       <c r="E4" s="8">
         <v>0.5</v>
       </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
+      <c r="F4" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="H4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -1836,22 +3245,24 @@
       <c r="K4" s="8">
         <v>0</v>
       </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="S4" s="8"/>
+      <c r="L4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
@@ -1861,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -1869,17 +3280,15 @@
       <c r="E5" s="8">
         <v>0.5</v>
       </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
+      <c r="F5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="8"/>
       <c r="H5" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -1887,182 +3296,180 @@
       <c r="K5" s="8">
         <v>0</v>
       </c>
-      <c r="L5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>67</v>
+      <c r="L5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="A6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
         <v>20</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="10">
         <v>3</v>
       </c>
-      <c r="E6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
+      <c r="E6" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9">
         <v>0</v>
       </c>
       <c r="K6" s="8">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>98</v>
+      <c r="L6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="A7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
         <v>25</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
+        <v>5</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <v>30</v>
+      </c>
+      <c r="D8" s="8">
         <v>3</v>
       </c>
-      <c r="E7" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10">
-        <v>25</v>
-      </c>
-      <c r="D8" s="10">
-        <v>3</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>100</v>
+      <c r="E8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -2073,22 +3480,20 @@
         <v>1</v>
       </c>
       <c r="C9" s="8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="8">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8">
-        <v>15</v>
-      </c>
-      <c r="G9" s="8">
-        <v>15</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="8"/>
       <c r="H9" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
@@ -2099,27 +3504,23 @@
       <c r="K9" s="8">
         <v>0</v>
       </c>
-      <c r="L9" s="8" t="b">
-        <v>0</v>
+      <c r="L9" s="8">
+        <v>0.5</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -2132,23 +3533,23 @@
       <c r="C10" s="8">
         <v>40</v>
       </c>
-      <c r="D10" s="8">
-        <v>5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="H10" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -2156,23 +3557,23 @@
       <c r="K10" s="8">
         <v>0</v>
       </c>
-      <c r="L10" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="S10" s="10" t="s">
-        <v>99</v>
+      <c r="L10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -2183,25 +3584,23 @@
         <v>1</v>
       </c>
       <c r="C11" s="8">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D11" s="8">
         <v>5</v>
       </c>
       <c r="E11" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="8"/>
       <c r="H11" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
@@ -2209,23 +3608,23 @@
       <c r="K11" s="8">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="S11" s="10" t="s">
-        <v>100</v>
+      <c r="L11" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -2236,25 +3635,23 @@
         <v>1</v>
       </c>
       <c r="C12" s="8">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D12" s="10">
         <v>5</v>
       </c>
       <c r="E12" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="8"/>
       <c r="H12" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -2262,187 +3659,3818 @@
       <c r="K12" s="8">
         <v>0</v>
       </c>
-      <c r="L12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8">
-        <v>45</v>
+      <c r="L12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="10">
+        <v>59</v>
       </c>
       <c r="D13" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="8">
-        <v>50</v>
-      </c>
-      <c r="D14" s="10">
-        <v>5</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="S14" s="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
+        <v>15</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13">
+        <v>1</v>
+      </c>
+      <c r="I14" s="13">
+        <v>1</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C15" s="8">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10">
+        <v>5</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="8">
+        <v>10</v>
+      </c>
+      <c r="D16" s="10">
+        <v>3</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="8">
+        <v>10</v>
+      </c>
+      <c r="D17" s="10">
+        <v>3</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A18" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8">
+        <v>20</v>
+      </c>
+      <c r="D18" s="10">
+        <v>10</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="8">
+        <v>30</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="8">
+        <v>10</v>
+      </c>
+      <c r="I19" s="8">
+        <v>10</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="8">
+        <v>40</v>
+      </c>
+      <c r="D20" s="10">
+        <v>5</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N20" s="8">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A21" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="8">
+        <v>40</v>
+      </c>
+      <c r="D21" s="10">
+        <v>5</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="8">
+        <v>50</v>
+      </c>
+      <c r="D22" s="10">
+        <v>10</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="10">
         <v>59</v>
       </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="S15" s="8"/>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13">
+        <v>10</v>
+      </c>
+      <c r="E24" s="13">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13">
+        <v>1</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="N24" s="13">
+        <v>0</v>
+      </c>
+      <c r="O24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8">
+        <v>5</v>
+      </c>
+      <c r="D25" s="10">
+        <v>3</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8">
+        <v>2</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="8">
+        <v>10</v>
+      </c>
+      <c r="D26" s="10">
+        <v>5</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8">
+        <v>2</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N26" s="8">
+        <v>0</v>
+      </c>
+      <c r="O26" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8">
+        <v>20</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="8">
+        <v>13</v>
+      </c>
+      <c r="I27" s="8">
+        <v>13</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="8">
+        <v>30</v>
+      </c>
+      <c r="D28" s="10">
+        <v>3</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0</v>
+      </c>
+      <c r="O28" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="8">
+        <v>30</v>
+      </c>
+      <c r="D29" s="10">
+        <v>3</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="8">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8">
+        <v>35</v>
+      </c>
+      <c r="D30" s="10">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="8">
+        <v>2</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0</v>
+      </c>
+      <c r="O30" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="8">
+        <v>40</v>
+      </c>
+      <c r="D31" s="10">
+        <v>3</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="8">
+        <v>40</v>
+      </c>
+      <c r="D32" s="10">
+        <v>3</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="8">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N32" s="8">
+        <v>0</v>
+      </c>
+      <c r="O32" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="8">
+        <v>45</v>
+      </c>
+      <c r="D33" s="10">
+        <v>2</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8">
+        <v>2</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="8">
+        <v>45</v>
+      </c>
+      <c r="D34" s="10">
+        <v>5</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="8">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N34" s="8">
+        <v>0</v>
+      </c>
+      <c r="O34" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="8">
+        <v>50</v>
+      </c>
+      <c r="D35" s="10">
+        <v>5</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8">
+        <v>1</v>
+      </c>
+      <c r="I35" s="8">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="8">
+        <v>59</v>
+      </c>
+      <c r="D36" s="10">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8">
+        <v>1</v>
+      </c>
+      <c r="I36" s="8">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N36" s="8">
+        <v>0</v>
+      </c>
+      <c r="O36" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="13">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13">
+        <v>3</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1</v>
+      </c>
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N37" s="13">
+        <v>0</v>
+      </c>
+      <c r="O37" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8">
+        <v>5</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H38" s="8">
+        <v>6</v>
+      </c>
+      <c r="I38" s="8">
+        <v>6</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0</v>
+      </c>
+      <c r="K38" s="8">
+        <v>1</v>
+      </c>
+      <c r="L38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="N38" s="8">
+        <v>0</v>
+      </c>
+      <c r="O38" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R38" s="8"/>
+      <c r="S38" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="8">
+        <v>8</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H39" s="8">
+        <v>6</v>
+      </c>
+      <c r="I39" s="8">
+        <v>6</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8">
+        <v>1</v>
+      </c>
+      <c r="L39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="N39" s="8">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q39" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8">
+        <v>11</v>
+      </c>
+      <c r="D40" s="10">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" s="8">
+        <v>6</v>
+      </c>
+      <c r="I40" s="8">
+        <v>6</v>
+      </c>
+      <c r="J40" s="8">
+        <v>0</v>
+      </c>
+      <c r="K40" s="8">
+        <v>1</v>
+      </c>
+      <c r="L40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N40" s="8">
+        <v>0</v>
+      </c>
+      <c r="O40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q40" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="8">
+        <v>15</v>
+      </c>
+      <c r="D41" s="10">
+        <v>5</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="8">
+        <v>1</v>
+      </c>
+      <c r="I41" s="8">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N41" s="8">
+        <v>0</v>
+      </c>
+      <c r="O41" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="8">
+        <v>15</v>
+      </c>
+      <c r="D42" s="10">
+        <v>5</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="8">
+        <v>1</v>
+      </c>
+      <c r="I42" s="8">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N42" s="8">
+        <v>0</v>
+      </c>
+      <c r="O42" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8">
+        <v>20</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="8">
+        <v>30</v>
+      </c>
+      <c r="I43" s="8">
+        <v>30</v>
+      </c>
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8">
+        <v>1</v>
+      </c>
+      <c r="L43" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="N43" s="8">
+        <v>20</v>
+      </c>
+      <c r="O43" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q43" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R43" s="8"/>
+      <c r="S43" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="8">
+        <v>25</v>
+      </c>
+      <c r="D44" s="10">
+        <v>10</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N44" s="8">
+        <v>0</v>
+      </c>
+      <c r="O44" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="8">
+        <v>30</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8">
+        <v>4</v>
+      </c>
+      <c r="I45" s="8">
+        <v>5</v>
+      </c>
+      <c r="J45" s="8">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N45" s="8">
+        <v>0</v>
+      </c>
+      <c r="O45" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="8">
+        <v>35</v>
+      </c>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8">
+        <v>4</v>
+      </c>
+      <c r="I46" s="8">
+        <v>5</v>
+      </c>
+      <c r="J46" s="8">
+        <v>0</v>
+      </c>
+      <c r="K46" s="8">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N46" s="8">
+        <v>0</v>
+      </c>
+      <c r="O46" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8">
+        <v>40</v>
+      </c>
+      <c r="D47" s="10">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H47" s="8">
+        <v>8</v>
+      </c>
+      <c r="I47" s="8">
+        <v>8</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8">
+        <v>1</v>
+      </c>
+      <c r="L47" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N47" s="8">
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q47" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R47" s="8"/>
+      <c r="S47" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="8">
+        <v>50</v>
+      </c>
+      <c r="D48" s="10">
+        <v>5</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1</v>
+      </c>
+      <c r="I48" s="8">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8">
+        <v>0</v>
+      </c>
+      <c r="K48" s="8">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N48" s="8">
+        <v>0</v>
+      </c>
+      <c r="O48" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="8"/>
+      <c r="S48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="8">
+        <v>50</v>
+      </c>
+      <c r="D49" s="10">
+        <v>5</v>
+      </c>
+      <c r="E49" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="8">
+        <v>1</v>
+      </c>
+      <c r="I49" s="8">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N49" s="8">
+        <v>0</v>
+      </c>
+      <c r="O49" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="8"/>
+      <c r="S49" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A50" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="8">
+        <v>59</v>
+      </c>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
+      <c r="K50" s="8">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N50" s="8">
+        <v>0</v>
+      </c>
+      <c r="O50" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q50" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R50" s="8"/>
+      <c r="S50" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="13">
+        <v>1</v>
+      </c>
+      <c r="D51" s="13">
+        <v>5</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13">
+        <v>1</v>
+      </c>
+      <c r="I51" s="13">
+        <v>1</v>
+      </c>
+      <c r="J51" s="13">
+        <v>0</v>
+      </c>
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="N51" s="13">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="8">
+        <v>5</v>
+      </c>
+      <c r="D52" s="10">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H52" s="8">
+        <v>8</v>
+      </c>
+      <c r="I52" s="8">
+        <v>8</v>
+      </c>
+      <c r="J52" s="8">
+        <v>0</v>
+      </c>
+      <c r="K52" s="8">
+        <v>1</v>
+      </c>
+      <c r="L52" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N52" s="8">
+        <v>0</v>
+      </c>
+      <c r="O52" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q52" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="8">
+        <v>10</v>
+      </c>
+      <c r="D53" s="10">
+        <v>5</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8">
+        <v>1</v>
+      </c>
+      <c r="I53" s="8">
+        <v>1</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N53" s="8">
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="8"/>
+      <c r="S53" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="8">
+        <v>15</v>
+      </c>
+      <c r="D54" s="10">
+        <v>1</v>
+      </c>
+      <c r="E54" s="10">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H54" s="8">
+        <v>8</v>
+      </c>
+      <c r="I54" s="8">
+        <v>8</v>
+      </c>
+      <c r="J54" s="8">
+        <v>0</v>
+      </c>
+      <c r="K54" s="8">
+        <v>1</v>
+      </c>
+      <c r="L54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N54" s="8">
+        <v>0</v>
+      </c>
+      <c r="O54" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q54" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R54" s="8"/>
+      <c r="S54" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="8">
+        <v>20</v>
+      </c>
+      <c r="D55" s="10">
+        <v>3</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1</v>
+      </c>
+      <c r="I55" s="8">
+        <v>2</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N55" s="8">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="8"/>
+      <c r="S55" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="8">
+        <v>20</v>
+      </c>
+      <c r="D56" s="10">
+        <v>3</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8">
+        <v>2</v>
+      </c>
+      <c r="J56" s="8">
+        <v>0</v>
+      </c>
+      <c r="K56" s="8">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N56" s="8">
+        <v>0</v>
+      </c>
+      <c r="O56" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="8"/>
+      <c r="S56" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="8">
+        <v>25</v>
+      </c>
+      <c r="D57" s="10">
+        <v>3</v>
+      </c>
+      <c r="E57" s="10">
+        <v>3</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H57" s="8">
+        <v>4</v>
+      </c>
+      <c r="I57" s="8">
+        <v>4</v>
+      </c>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>1</v>
+      </c>
+      <c r="L57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N57" s="8">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q57" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R57" s="8"/>
+      <c r="S57" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="8">
+        <v>30</v>
+      </c>
+      <c r="D58" s="10">
+        <v>5</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8">
+        <v>1</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N58" s="8">
+        <v>0</v>
+      </c>
+      <c r="O58" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="8"/>
+      <c r="S58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="8">
+        <v>40</v>
+      </c>
+      <c r="D59" s="10">
+        <v>3</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H59" s="8">
+        <v>1</v>
+      </c>
+      <c r="I59" s="8">
+        <v>2</v>
+      </c>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N59" s="8">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="8"/>
+      <c r="S59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="8">
+        <v>40</v>
+      </c>
+      <c r="D60" s="10">
+        <v>3</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8">
+        <v>2</v>
+      </c>
+      <c r="J60" s="8">
+        <v>0</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N60" s="8">
+        <v>0</v>
+      </c>
+      <c r="O60" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="8"/>
+      <c r="S60" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="8">
+        <v>45</v>
+      </c>
+      <c r="D61" s="10">
+        <v>1</v>
+      </c>
+      <c r="E61" s="10">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H61" s="8">
+        <v>6</v>
+      </c>
+      <c r="I61" s="8">
+        <v>6</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8">
+        <v>1</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N61" s="8">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q61" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R61" s="8"/>
+      <c r="S61" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="8">
+        <v>45</v>
+      </c>
+      <c r="D62" s="10">
+        <v>1</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62" s="8">
+        <v>4</v>
+      </c>
+      <c r="I62" s="8">
+        <v>4</v>
+      </c>
+      <c r="J62" s="8">
+        <v>0</v>
+      </c>
+      <c r="K62" s="8">
+        <v>1</v>
+      </c>
+      <c r="L62" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N62" s="8">
+        <v>0</v>
+      </c>
+      <c r="O62" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q62" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R62" s="8"/>
+      <c r="S62" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="8">
+        <v>50</v>
+      </c>
+      <c r="D63" s="10">
+        <v>5</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8">
+        <v>1</v>
+      </c>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N63" s="8">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="8"/>
+      <c r="S63" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A64" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="8">
+        <v>59</v>
+      </c>
+      <c r="D64" s="10">
+        <v>1</v>
+      </c>
+      <c r="E64" s="10">
+        <v>1</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8">
+        <v>0</v>
+      </c>
+      <c r="K64" s="8">
+        <v>0</v>
+      </c>
+      <c r="L64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N64" s="8">
+        <v>0</v>
+      </c>
+      <c r="O64" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q64" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R64" s="8"/>
+      <c r="S64" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="13">
+        <v>1</v>
+      </c>
+      <c r="D65" s="13">
+        <v>10</v>
+      </c>
+      <c r="E65" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13">
+        <v>1</v>
+      </c>
+      <c r="I65" s="13">
+        <v>1</v>
+      </c>
+      <c r="J65" s="13">
+        <v>0</v>
+      </c>
+      <c r="K65" s="13">
+        <v>0</v>
+      </c>
+      <c r="L65" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M65" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="N65" s="13">
+        <v>0</v>
+      </c>
+      <c r="O65" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" s="13"/>
+      <c r="Q65" s="13"/>
+      <c r="R65" s="13"/>
+      <c r="S65" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="8">
+        <v>10</v>
+      </c>
+      <c r="D66" s="10">
+        <v>5</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8">
+        <v>1</v>
+      </c>
+      <c r="I66" s="8">
+        <v>2</v>
+      </c>
+      <c r="J66" s="8">
+        <v>0</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="L66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="N66" s="8">
+        <v>0</v>
+      </c>
+      <c r="O66" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="8"/>
+      <c r="S66" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="8">
+        <v>15</v>
+      </c>
+      <c r="D67" s="10">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H67" s="8">
+        <v>4</v>
+      </c>
+      <c r="I67" s="8">
+        <v>4</v>
+      </c>
+      <c r="J67" s="8">
+        <v>0</v>
+      </c>
+      <c r="K67" s="8">
+        <v>1</v>
+      </c>
+      <c r="L67" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="N67" s="8">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q67" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R67" s="8"/>
+      <c r="S67" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="8">
+        <v>20</v>
+      </c>
+      <c r="D68" s="10">
+        <v>5</v>
+      </c>
+      <c r="E68" s="10">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8">
+        <v>2</v>
+      </c>
+      <c r="I68" s="8">
+        <v>3</v>
+      </c>
+      <c r="J68" s="8">
+        <v>0</v>
+      </c>
+      <c r="K68" s="8">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N68" s="8">
+        <v>0</v>
+      </c>
+      <c r="O68" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="8"/>
+      <c r="S68" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="8">
+        <v>25</v>
+      </c>
+      <c r="D69" s="10">
+        <v>5</v>
+      </c>
+      <c r="E69" s="10">
+        <v>1</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H69" s="8">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8">
+        <v>1</v>
+      </c>
+      <c r="J69" s="8">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8">
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N69" s="8">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="8"/>
+      <c r="S69" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70" s="8">
+        <v>25</v>
+      </c>
+      <c r="D70" s="10">
+        <v>5</v>
+      </c>
+      <c r="E70" s="10">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" s="8">
+        <v>1</v>
+      </c>
+      <c r="I70" s="8">
+        <v>1</v>
+      </c>
+      <c r="J70" s="8">
+        <v>0</v>
+      </c>
+      <c r="K70" s="8">
+        <v>0</v>
+      </c>
+      <c r="L70" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N70" s="8">
+        <v>0</v>
+      </c>
+      <c r="O70" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="8"/>
+      <c r="S70" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="8">
+        <v>30</v>
+      </c>
+      <c r="D71" s="10">
+        <v>3</v>
+      </c>
+      <c r="E71" s="10">
+        <v>1</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H71" s="8">
+        <v>2</v>
+      </c>
+      <c r="I71" s="8">
+        <v>3</v>
+      </c>
+      <c r="J71" s="8">
+        <v>0</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="L71" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N71" s="8">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="8"/>
+      <c r="S71" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="8">
+        <v>30</v>
+      </c>
+      <c r="D72" s="10">
+        <v>3</v>
+      </c>
+      <c r="E72" s="10">
+        <v>1</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" s="8">
+        <v>2</v>
+      </c>
+      <c r="I72" s="8">
+        <v>3</v>
+      </c>
+      <c r="J72" s="8">
+        <v>0</v>
+      </c>
+      <c r="K72" s="8">
+        <v>0</v>
+      </c>
+      <c r="L72" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M72" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N72" s="8">
+        <v>0</v>
+      </c>
+      <c r="O72" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="8"/>
+      <c r="S72" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="8">
+        <v>35</v>
+      </c>
+      <c r="D73" s="10">
+        <v>3</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8">
+        <v>1</v>
+      </c>
+      <c r="I73" s="8">
+        <v>1</v>
+      </c>
+      <c r="J73" s="8">
+        <v>0</v>
+      </c>
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="L73" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N73" s="8">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="8"/>
+      <c r="S73" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="8">
+        <v>40</v>
+      </c>
+      <c r="D74" s="10">
+        <v>10</v>
+      </c>
+      <c r="E74" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8">
+        <v>1</v>
+      </c>
+      <c r="I74" s="8">
+        <v>1</v>
+      </c>
+      <c r="J74" s="8">
+        <v>0</v>
+      </c>
+      <c r="K74" s="8">
+        <v>0</v>
+      </c>
+      <c r="L74" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N74" s="8">
+        <v>0</v>
+      </c>
+      <c r="O74" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="8"/>
+      <c r="S74" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" s="8">
+        <v>45</v>
+      </c>
+      <c r="D75" s="10">
+        <v>1</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H75" s="8">
+        <v>1</v>
+      </c>
+      <c r="I75" s="8">
+        <v>1</v>
+      </c>
+      <c r="J75" s="8">
+        <v>0</v>
+      </c>
+      <c r="K75" s="8">
+        <v>1</v>
+      </c>
+      <c r="L75" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N75" s="8">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q75" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R75" s="8"/>
+      <c r="S75" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8">
+        <v>50</v>
+      </c>
+      <c r="D76" s="10">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10">
+        <v>1</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H76" s="8">
+        <v>2</v>
+      </c>
+      <c r="I76" s="8">
+        <v>3</v>
+      </c>
+      <c r="J76" s="8">
+        <v>0</v>
+      </c>
+      <c r="K76" s="8">
+        <v>0</v>
+      </c>
+      <c r="L76" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M76" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N76" s="8">
+        <v>0</v>
+      </c>
+      <c r="O76" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="8"/>
+      <c r="S76" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="8">
+        <v>50</v>
+      </c>
+      <c r="D77" s="10">
+        <v>3</v>
+      </c>
+      <c r="E77" s="10">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H77" s="8">
+        <v>2</v>
+      </c>
+      <c r="I77" s="8">
+        <v>3</v>
+      </c>
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+      <c r="K77" s="8">
+        <v>0</v>
+      </c>
+      <c r="L77" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N77" s="8">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="8"/>
+      <c r="S77" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="8">
+        <v>50</v>
+      </c>
+      <c r="D78" s="10">
+        <v>3</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H78" s="8">
+        <v>2</v>
+      </c>
+      <c r="I78" s="8">
+        <v>3</v>
+      </c>
+      <c r="J78" s="8">
+        <v>0</v>
+      </c>
+      <c r="K78" s="8">
+        <v>0</v>
+      </c>
+      <c r="L78" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M78" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N78" s="8">
+        <v>0</v>
+      </c>
+      <c r="O78" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="8"/>
+      <c r="S78" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8">
+        <v>50</v>
+      </c>
+      <c r="D79" s="10">
+        <v>3</v>
+      </c>
+      <c r="E79" s="10">
+        <v>1</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H79" s="8">
+        <v>2</v>
+      </c>
+      <c r="I79" s="8">
+        <v>3</v>
+      </c>
+      <c r="J79" s="8">
+        <v>0</v>
+      </c>
+      <c r="K79" s="8">
+        <v>0</v>
+      </c>
+      <c r="L79" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N79" s="8">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="8"/>
+      <c r="S79" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="8">
+        <v>59</v>
+      </c>
+      <c r="D80" s="10">
+        <v>1</v>
+      </c>
+      <c r="E80" s="10">
+        <v>1</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8">
+        <v>1</v>
+      </c>
+      <c r="I80" s="8">
+        <v>1</v>
+      </c>
+      <c r="J80" s="8">
+        <v>0</v>
+      </c>
+      <c r="K80" s="8">
+        <v>0</v>
+      </c>
+      <c r="L80" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M80" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N80" s="8">
+        <v>0</v>
+      </c>
+      <c r="O80" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P80" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q80" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R80" s="8"/>
+      <c r="S80" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A81" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" s="8">
+        <v>59</v>
+      </c>
+      <c r="D81" s="10">
+        <v>1</v>
+      </c>
+      <c r="E81" s="10">
+        <v>1</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8">
+        <v>1</v>
+      </c>
+      <c r="I81" s="8">
+        <v>1</v>
+      </c>
+      <c r="J81" s="8">
+        <v>0</v>
+      </c>
+      <c r="K81" s="8">
+        <v>0</v>
+      </c>
+      <c r="L81" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="N81" s="8">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q81" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R81" s="8"/>
+      <c r="S81" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" s="13">
+        <v>3</v>
+      </c>
+      <c r="D82" s="13">
+        <v>5</v>
+      </c>
+      <c r="E82" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13">
+        <v>1</v>
+      </c>
+      <c r="I82" s="13">
+        <v>1</v>
+      </c>
+      <c r="J82" s="13">
+        <v>0</v>
+      </c>
+      <c r="K82" s="13">
+        <v>0</v>
+      </c>
+      <c r="L82" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="N82" s="13">
+        <v>0</v>
+      </c>
+      <c r="O82" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" s="13"/>
+      <c r="Q82" s="13"/>
+      <c r="R82" s="13"/>
+      <c r="S82" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" s="8">
+        <v>5</v>
+      </c>
+      <c r="D83" s="10">
+        <v>5</v>
+      </c>
+      <c r="E83" s="10">
+        <v>1</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8">
+        <v>1</v>
+      </c>
+      <c r="I83" s="8">
+        <v>2</v>
+      </c>
+      <c r="J83" s="8">
+        <v>0</v>
+      </c>
+      <c r="K83" s="8">
+        <v>0</v>
+      </c>
+      <c r="L83" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="N83" s="8">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="8"/>
+      <c r="S83" s="8">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O83" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
+      <formula1>"false,true"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F83" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
+      <formula1>"SpawnRandom,SpawnSide,SpawnRectangle,SpawnOval"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2473,66 +7501,66 @@
   <sheetData>
     <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -2568,24 +7596,24 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
@@ -2621,26 +7649,26 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
@@ -2676,26 +7704,26 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
@@ -2731,21 +7759,21 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2756,297 +7784,917 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22332C8A-7304-4E64-9BD3-13AF5949C9BF}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="39.8984375" customWidth="1"/>
     <col min="2" max="2" width="56.296875" customWidth="1"/>
-    <col min="3" max="3" width="25.3984375" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
-    <col min="5" max="6" width="26.19921875" customWidth="1"/>
-    <col min="7" max="7" width="34.5" customWidth="1"/>
-    <col min="8" max="8" width="37.296875" customWidth="1"/>
-    <col min="9" max="9" width="41.796875" customWidth="1"/>
-    <col min="10" max="10" width="42.296875" customWidth="1"/>
-    <col min="11" max="11" width="43.8984375" customWidth="1"/>
-    <col min="12" max="12" width="28.19921875" customWidth="1"/>
-    <col min="13" max="14" width="37.8984375" customWidth="1"/>
-    <col min="15" max="15" width="31" customWidth="1"/>
-    <col min="16" max="16" width="31.5" customWidth="1"/>
-    <col min="17" max="17" width="86.296875" customWidth="1"/>
-    <col min="18" max="18" width="62.59765625" customWidth="1"/>
-    <col min="19" max="19" width="109.796875" customWidth="1"/>
+    <col min="3" max="3" width="34.5" customWidth="1"/>
+    <col min="4" max="4" width="25.3984375" customWidth="1"/>
+    <col min="5" max="5" width="41" customWidth="1"/>
+    <col min="6" max="6" width="62.59765625" customWidth="1"/>
+    <col min="7" max="7" width="109.796875" customWidth="1"/>
+    <col min="8" max="9" width="26.19921875" customWidth="1"/>
+    <col min="10" max="10" width="37.296875" customWidth="1"/>
+    <col min="11" max="11" width="41.796875" customWidth="1"/>
+    <col min="12" max="12" width="42.296875" customWidth="1"/>
+    <col min="13" max="13" width="86.296875" customWidth="1"/>
+    <col min="14" max="14" width="43.8984375" customWidth="1"/>
+    <col min="15" max="15" width="28.19921875" customWidth="1"/>
+    <col min="16" max="17" width="37.8984375" customWidth="1"/>
+    <col min="18" max="18" width="31" customWidth="1"/>
+    <col min="19" max="19" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="O3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="108" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>81</v>
+      <c r="S3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+    </row>
+    <row r="5" spans="1:19" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>15</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>5</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <v>15</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="3" t="s">
+      <c r="F8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
         <v>3</v>
       </c>
-      <c r="F6" s="1">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88203281-AD27-4579-B140-3641B5403CC3}">
+  <dimension ref="A1:AY5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+      <c r="N1">
+        <v>13</v>
+      </c>
+      <c r="O1">
+        <v>14</v>
+      </c>
+      <c r="P1">
+        <v>15</v>
+      </c>
+      <c r="Q1">
+        <v>16</v>
+      </c>
+      <c r="R1">
+        <v>17</v>
+      </c>
+      <c r="S1">
+        <v>18</v>
+      </c>
+      <c r="T1">
+        <v>19</v>
+      </c>
+      <c r="U1">
+        <v>20</v>
+      </c>
+      <c r="V1">
+        <v>21</v>
+      </c>
+      <c r="W1">
+        <v>22</v>
+      </c>
+      <c r="X1">
+        <v>23</v>
+      </c>
+      <c r="Y1">
+        <v>24</v>
+      </c>
+      <c r="Z1">
+        <v>25</v>
+      </c>
+      <c r="AA1">
+        <v>26</v>
+      </c>
+      <c r="AB1">
+        <v>27</v>
+      </c>
+      <c r="AC1">
+        <v>28</v>
+      </c>
+      <c r="AD1">
+        <v>29</v>
+      </c>
+      <c r="AE1">
+        <v>30</v>
+      </c>
+      <c r="AF1">
+        <v>31</v>
+      </c>
+      <c r="AG1">
+        <v>32</v>
+      </c>
+      <c r="AH1">
+        <v>33</v>
+      </c>
+      <c r="AI1">
+        <v>34</v>
+      </c>
+      <c r="AJ1">
+        <v>35</v>
+      </c>
+      <c r="AK1">
+        <v>36</v>
+      </c>
+      <c r="AL1">
+        <v>37</v>
+      </c>
+      <c r="AM1">
+        <v>38</v>
+      </c>
+      <c r="AN1">
+        <v>39</v>
+      </c>
+      <c r="AO1">
+        <v>40</v>
+      </c>
+      <c r="AP1">
+        <v>41</v>
+      </c>
+      <c r="AQ1">
+        <v>42</v>
+      </c>
+      <c r="AR1">
+        <v>43</v>
+      </c>
+      <c r="AS1">
+        <v>44</v>
+      </c>
+      <c r="AT1">
+        <v>45</v>
+      </c>
+      <c r="AU1">
+        <v>46</v>
+      </c>
+      <c r="AV1">
+        <v>47</v>
+      </c>
+      <c r="AW1">
+        <v>48</v>
+      </c>
+      <c r="AX1">
+        <v>49</v>
+      </c>
+      <c r="AY1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <f>B2*$B$3</f>
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:AY2" si="0">C2*$B$3</f>
+        <v>43.199999999999996</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>51.839999999999996</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>62.207999999999991</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>74.649599999999992</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>89.579519999999988</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>107.49542399999999</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>128.99450879999998</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>154.79341055999996</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>185.75209267199995</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>222.90251120639994</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>267.48301344767992</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>320.97961613721588</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>385.17553936465907</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>462.21064723759088</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>554.65277668510907</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>665.58333202213089</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>798.69999842655704</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>958.43999811186836</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>1150.1279977342419</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>1380.1535972810902</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>1656.1843167373083</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>1987.42118008477</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>2384.9054161017239</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>2861.8864993220686</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>3434.2637991864822</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" si="0"/>
+        <v>4121.1165590237788</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" si="0"/>
+        <v>4945.339870828534</v>
+      </c>
+      <c r="AE2">
+        <f t="shared" si="0"/>
+        <v>5934.4078449942408</v>
+      </c>
+      <c r="AF2">
+        <f t="shared" si="0"/>
+        <v>7121.2894139930886</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" si="0"/>
+        <v>8545.5472967917067</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" si="0"/>
+        <v>10254.656756150047</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>12305.588107380056</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>14766.705728856066</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>17720.046874627278</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>21264.056249552734</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>25516.867499463278</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>30620.240999355934</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>36744.289199227118</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>44093.147039072537</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>52911.776446887045</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>63494.131736264448</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>76192.95808351734</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>91431.549700220799</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>109717.85964026496</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>131661.43156831793</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>157993.71788198152</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>189592.4614583778</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>227510.95375005336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603B960F-F1F9-432D-9097-76E162874693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4C0A9B-64AE-4C8B-9A59-B84FB9BE3526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="24" windowWidth="20760" windowHeight="12012" activeTab="3" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="0" yWindow="24" windowWidth="14460" windowHeight="10488" firstSheet="1" activeTab="3" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
     <sheet name="ImportData" sheetId="1" r:id="rId1"/>
     <sheet name="TestData" sheetId="4" r:id="rId2"/>
     <sheet name="explanation" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,6 +48,7 @@
     <author>tc={51A3F559-40AA-431D-88AE-A6E41F82C579}</author>
     <author>tc={EB6B3A68-8148-45AE-9278-985634B59876}</author>
     <author>tc={2EA2148F-5DB8-45A5-B6B5-E8B64F389B05}</author>
+    <author>tc={B8461874-3A04-4C37-B137-668B2D0D0DD9}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{65B6A188-F81E-4121-9301-0FFE406E0779}">
@@ -132,12 +134,23 @@
 ノーマルを囲み要因として使う。</t>
       </text>
     </comment>
+    <comment ref="A96" authorId="8" shapeId="0" xr:uid="{B8461874-3A04-4C37-B137-668B2D0D0DD9}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave８
+主にスナイパーとタンクを出現させ、
+対処法を探らせる。
+ノーマルを囲み要因として使う。</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="152">
   <si>
     <t>Wave1</t>
   </si>
@@ -1279,24 +1292,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:1.7:0;ATK:1.7:0,Speed:1.5:0,DashSpeed:1.5:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.7:0;ATK:1.7:0,Speed:1.5:0,DashSpeed:1.5:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:1.6:0,DashSpeed:1.6:0</t>
-  </si>
-  <si>
-    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:1.6:0,DashSpeed:1.6:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:3.0:20;ATK:2.0:0,Speed:0.2:0,DashSpeed:0.2:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Lv</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1305,10 +1300,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>NextLevelRate</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Wave5</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1325,10 +1316,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:2.5:0;ATK:2.2:0,Speed:1.8:0,DashSpeed:1.8:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Wave6</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1345,46 +1332,106 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:2.75:0;ATK:2.5:0,Speed:1.9:0,DashSpeed:1.9:0</t>
-  </si>
-  <si>
-    <t>MaxHP:2.75:0;ATK:2.5:0,Speed:1.9:0,DashSpeed:1.9:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:3.0:0;ATK:2.75:0,Speed:2.0:0,DashSpeed:2.0:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生成情報にパラメータ実装済み　インポート設計に追加する</t>
-    </r>
-    <rPh sb="1" eb="5">
-      <t>セイセイジョウホウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>セッケイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ツイカ</t>
-    </rPh>
+    <t>[13] ExpAdditionPerWave</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[14] ExpMultiplierPerWave</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[15] DestroyTime</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[16] IsClear</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[17] PreviewEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[18] SpawneEffectName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[19] FirstProcessSEName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[20] FirstProcessSEVolume</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>baseExp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>linearWeightoeff</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>quadraticWeight</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.7:0;ATK:1.5:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.7:0;ATK:1.5:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:1.6:0,Speed:1.6:0,DashSpeed:1.6:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:1.6:0,Speed:1.6:0,DashSpeed:1.6:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.0:20;ATK:1.6:0,Speed:0.2:0,DashSpeed:0.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.5:0;ATK:1.85:0,Speed:1.8:0,DashSpeed:1.8:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.5:0;ATK:1.85:0,Speed:1.8:0,DashSpeed:1.8:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.75:0;ATK:2.1:0,Speed:1.9:0,DashSpeed:1.9:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.75:0;ATK:2.1:0,Speed:1.9:0,DashSpeed:1.9:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:23;sizey:17</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Boss_Tank_Comp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave8</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:2.3:0,Speed:2.0:0,DashSpeed:2.0:0</t>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:2.3:0,Speed:2.0:0,DashSpeed:2.0:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:2.3:0,Speed:0.1:0,DashSpeed:2.0:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.2:0;ATK:2.4:0,Speed:2.1:0,DashSpeed:2.0:0</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1392,7 +1439,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1436,12 +1483,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1722,151 +1763,151 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.199999999999996</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.839999999999996</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62.207999999999991</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>74.649599999999992</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>89.579519999999988</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>107.49542399999999</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>128.99450879999998</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>154.79341055999996</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>185.75209267199995</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>222.90251120639994</c:v>
+                  <c:v>184</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>267.48301344767992</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>320.97961613721588</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>385.17553936465907</c:v>
+                  <c:v>268</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>462.21064723759088</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>554.65277668510907</c:v>
+                  <c:v>334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>665.58333202213089</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>798.69999842655704</c:v>
+                  <c:v>408</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>958.43999811186836</c:v>
+                  <c:v>448</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1150.1279977342419</c:v>
+                  <c:v>490</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1380.1535972810902</c:v>
+                  <c:v>534</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1656.1843167373083</c:v>
+                  <c:v>580</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1987.42118008477</c:v>
+                  <c:v>628</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2384.9054161017239</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2861.8864993220686</c:v>
+                  <c:v>730</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3434.2637991864822</c:v>
+                  <c:v>784</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4121.1165590237788</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4945.339870828534</c:v>
+                  <c:v>898</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5934.4078449942408</c:v>
+                  <c:v>958</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7121.2894139930886</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8545.5472967917067</c:v>
+                  <c:v>1084</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10254.656756150047</c:v>
+                  <c:v>1150</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>12305.588107380056</c:v>
+                  <c:v>1218</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>14766.705728856066</c:v>
+                  <c:v>1288</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>17720.046874627278</c:v>
+                  <c:v>1360</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>21264.056249552734</c:v>
+                  <c:v>1434</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>25516.867499463278</c:v>
+                  <c:v>1510</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>30620.240999355934</c:v>
+                  <c:v>1588</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>36744.289199227118</c:v>
+                  <c:v>1668</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>44093.147039072537</c:v>
+                  <c:v>1750</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>52911.776446887045</c:v>
+                  <c:v>1834</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>63494.131736264448</c:v>
+                  <c:v>1920</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>76192.95808351734</c:v>
+                  <c:v>2008</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>91431.549700220799</c:v>
+                  <c:v>2098</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>109717.85964026496</c:v>
+                  <c:v>2190</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>131661.43156831793</c:v>
+                  <c:v>2284</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>157993.71788198152</c:v>
+                  <c:v>2380</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>189592.4614583778</c:v>
+                  <c:v>2478</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>227510.95375005336</c:v>
+                  <c:v>2578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3022,12 +3063,18 @@
 対処法を探らせる。
 ノーマルを囲み要因として使う。</text>
   </threadedComment>
+  <threadedComment ref="A96" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{B8461874-3A04-4C37-B137-668B2D0D0DD9}">
+    <text>〇Wave８
+主にスナイパーとタンクを出現させ、
+対処法を探らせる。
+ノーマルを囲み要因として使う。</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.69921875" customWidth="1"/>
@@ -3042,15 +3089,16 @@
     <col min="11" max="11" width="16.3984375" customWidth="1"/>
     <col min="12" max="12" width="24.796875" customWidth="1"/>
     <col min="13" max="13" width="63.19921875" customWidth="1"/>
-    <col min="14" max="14" width="16.796875" customWidth="1"/>
-    <col min="15" max="15" width="16.19921875" customWidth="1"/>
-    <col min="16" max="17" width="24.59765625" customWidth="1"/>
-    <col min="18" max="18" width="25.796875" customWidth="1"/>
-    <col min="19" max="19" width="27.19921875" customWidth="1"/>
-    <col min="20" max="21" width="19.59765625" customWidth="1"/>
+    <col min="14" max="14" width="24.796875" customWidth="1"/>
+    <col min="15" max="15" width="26.5" customWidth="1"/>
+    <col min="16" max="16" width="16.796875" customWidth="1"/>
+    <col min="17" max="17" width="16.19921875" customWidth="1"/>
+    <col min="18" max="19" width="24.59765625" customWidth="1"/>
+    <col min="20" max="20" width="25.796875" customWidth="1"/>
+    <col min="21" max="21" width="27.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -3091,25 +3139,31 @@
         <v>92</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -3150,17 +3204,23 @@
       <c r="N2" s="7">
         <v>0</v>
       </c>
-      <c r="O2" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="11" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" s="7"/>
-      <c r="S2" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -3201,17 +3261,23 @@
       <c r="N3" s="8">
         <v>0</v>
       </c>
-      <c r="O3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" s="8"/>
-      <c r="S3" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -3254,17 +3320,23 @@
       <c r="N4" s="8">
         <v>0</v>
       </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" s="8"/>
-      <c r="S4" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
@@ -3305,17 +3377,23 @@
       <c r="N5" s="8">
         <v>0</v>
       </c>
-      <c r="O5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" s="8"/>
-      <c r="S5" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
@@ -3355,20 +3433,26 @@
       <c r="M6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" s="9"/>
-      <c r="S6" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
@@ -3409,17 +3493,23 @@
       <c r="N7" s="8">
         <v>0</v>
       </c>
-      <c r="O7" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" s="8"/>
-      <c r="S7" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
@@ -3462,17 +3552,23 @@
       <c r="N8" s="8">
         <v>0</v>
       </c>
-      <c r="O8" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" s="8"/>
-      <c r="S8" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
@@ -3513,17 +3609,23 @@
       <c r="N9" s="8">
         <v>0</v>
       </c>
-      <c r="O9" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
+      <c r="O9" s="8">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" s="8"/>
-      <c r="S9" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
@@ -3566,17 +3668,23 @@
       <c r="N10" s="8">
         <v>0</v>
       </c>
-      <c r="O10" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" s="8"/>
-      <c r="S10" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>0</v>
       </c>
@@ -3617,17 +3725,23 @@
       <c r="N11" s="8">
         <v>0</v>
       </c>
-      <c r="O11" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" s="8"/>
-      <c r="S11" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
         <v>0</v>
       </c>
@@ -3668,17 +3782,23 @@
       <c r="N12" s="8">
         <v>0</v>
       </c>
-      <c r="O12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" s="8"/>
-      <c r="S12" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="10" t="s">
         <v>0</v>
       </c>
@@ -3719,21 +3839,27 @@
       <c r="N13" s="10">
         <v>0</v>
       </c>
-      <c r="O13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="10" t="s">
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q13" s="10" t="s">
+      <c r="S13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="T13" s="10"/>
+      <c r="U13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>81</v>
       </c>
@@ -3772,19 +3898,25 @@
         <v>114</v>
       </c>
       <c r="N14" s="13">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" s="13"/>
-      <c r="S14" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
         <v>81</v>
       </c>
@@ -3823,19 +3955,25 @@
         <v>114</v>
       </c>
       <c r="N15" s="8">
-        <v>0</v>
-      </c>
-      <c r="O15" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" s="8"/>
-      <c r="S15" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A16" s="8" t="s">
         <v>80</v>
       </c>
@@ -3876,19 +4014,25 @@
         <v>114</v>
       </c>
       <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="O16" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" s="8"/>
-      <c r="S16" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A17" s="8" t="s">
         <v>80</v>
       </c>
@@ -3929,19 +4073,25 @@
         <v>113</v>
       </c>
       <c r="N17" s="8">
-        <v>0</v>
-      </c>
-      <c r="O17" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" s="8"/>
-      <c r="S17" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
         <v>80</v>
       </c>
@@ -3980,19 +4130,25 @@
         <v>113</v>
       </c>
       <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" s="8"/>
-      <c r="S18" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A19" s="8" t="s">
         <v>80</v>
       </c>
@@ -4033,23 +4189,29 @@
         <v>113</v>
       </c>
       <c r="N19" s="8">
-        <v>0</v>
-      </c>
-      <c r="O19" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="S19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T19" s="8"/>
+      <c r="U19" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A20" s="8" t="s">
         <v>80</v>
       </c>
@@ -4090,19 +4252,25 @@
         <v>113</v>
       </c>
       <c r="N20" s="8">
-        <v>0</v>
-      </c>
-      <c r="O20" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R20" s="8"/>
-      <c r="S20" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A21" s="8" t="s">
         <v>80</v>
       </c>
@@ -4143,19 +4311,25 @@
         <v>113</v>
       </c>
       <c r="N21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" s="8"/>
-      <c r="S21" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A22" s="8" t="s">
         <v>80</v>
       </c>
@@ -4194,19 +4368,25 @@
         <v>113</v>
       </c>
       <c r="N22" s="8">
-        <v>0</v>
-      </c>
-      <c r="O22" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8" t="b">
+        <v>0</v>
+      </c>
       <c r="R22" s="8"/>
-      <c r="S22" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="10" t="s">
         <v>81</v>
       </c>
@@ -4245,23 +4425,29 @@
         <v>114</v>
       </c>
       <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q23" s="10" t="s">
+      <c r="S23" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="T23" s="10"/>
+      <c r="U23" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>102</v>
       </c>
@@ -4297,22 +4483,28 @@
         <v>0.5</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="N24" s="13">
-        <v>0</v>
-      </c>
-      <c r="O24" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
+        <v>4</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0</v>
+      </c>
+      <c r="P24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R24" s="13"/>
-      <c r="S24" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="8" t="s">
         <v>102</v>
       </c>
@@ -4348,22 +4540,28 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="N25" s="8">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" s="8"/>
-      <c r="S25" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="8" t="s">
         <v>102</v>
       </c>
@@ -4399,22 +4597,28 @@
         <v>0.5</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="N26" s="8">
-        <v>0</v>
-      </c>
-      <c r="O26" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O26" s="8">
+        <v>0</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R26" s="8"/>
-      <c r="S26" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="8" t="s">
         <v>102</v>
       </c>
@@ -4452,26 +4656,32 @@
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="8">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q27" s="10" t="s">
+      <c r="S27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T27" s="8"/>
+      <c r="U27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="8" t="s">
         <v>102</v>
       </c>
@@ -4509,22 +4719,28 @@
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O28" s="8">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R28" s="8"/>
-      <c r="S28" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="8" t="s">
         <v>102</v>
       </c>
@@ -4562,22 +4778,28 @@
         <v>0.5</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N29" s="8">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O29" s="8">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R29" s="8"/>
-      <c r="S29" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="8" t="s">
         <v>102</v>
       </c>
@@ -4613,22 +4835,28 @@
         <v>0.5</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N30" s="8">
-        <v>0</v>
-      </c>
-      <c r="O30" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O30" s="8">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" s="8"/>
-      <c r="S30" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="8" t="s">
         <v>102</v>
       </c>
@@ -4666,22 +4894,28 @@
         <v>0.5</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N31" s="8">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O31" s="8">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R31" s="8"/>
-      <c r="S31" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="8" t="s">
         <v>102</v>
       </c>
@@ -4719,22 +4953,28 @@
         <v>0.5</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N32" s="8">
-        <v>0</v>
-      </c>
-      <c r="O32" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O32" s="8">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R32" s="8"/>
-      <c r="S32" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="8" t="s">
         <v>102</v>
       </c>
@@ -4770,22 +5010,28 @@
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N33" s="8">
-        <v>0</v>
-      </c>
-      <c r="O33" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O33" s="8">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R33" s="8"/>
-      <c r="S33" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="8" t="s">
         <v>102</v>
       </c>
@@ -4821,22 +5067,28 @@
         <v>0.5</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N34" s="8">
-        <v>0</v>
-      </c>
-      <c r="O34" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R34" s="8"/>
-      <c r="S34" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="8" t="s">
         <v>102</v>
       </c>
@@ -4872,22 +5124,28 @@
         <v>0.5</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="N35" s="8">
-        <v>0</v>
-      </c>
-      <c r="O35" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="O35" s="8">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="12" t="b">
+        <v>0</v>
+      </c>
       <c r="R35" s="8"/>
-      <c r="S35" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="8" t="s">
         <v>102</v>
       </c>
@@ -4923,26 +5181,32 @@
         <v>0.5</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="N36" s="8">
-        <v>0</v>
-      </c>
-      <c r="O36" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O36" s="8">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q36" s="10" t="s">
+      <c r="S36" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="T36" s="8"/>
+      <c r="U36" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A37" s="13" t="s">
         <v>110</v>
       </c>
@@ -4978,22 +5242,28 @@
         <v>0.5</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="N37" s="13">
-        <v>0</v>
-      </c>
-      <c r="O37" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
+        <v>5</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" s="13"/>
-      <c r="S37" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="8" t="s">
         <v>110</v>
       </c>
@@ -5031,26 +5301,32 @@
         <v>0.5</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="N38" s="8">
-        <v>0</v>
-      </c>
-      <c r="O38" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O38" s="8">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="S38" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T38" s="8"/>
+      <c r="U38" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="8" t="s">
         <v>110</v>
       </c>
@@ -5088,26 +5364,32 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="N39" s="8">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O39" s="8">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q39" s="10" t="s">
+      <c r="S39" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T39" s="8"/>
+      <c r="U39" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="8" t="s">
         <v>110</v>
       </c>
@@ -5145,26 +5427,32 @@
         <v>0.5</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N40" s="8">
-        <v>0</v>
-      </c>
-      <c r="O40" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O40" s="8">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q40" s="10" t="s">
+      <c r="S40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="8"/>
-      <c r="S40" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T40" s="8"/>
+      <c r="U40" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="8" t="s">
         <v>110</v>
       </c>
@@ -5202,22 +5490,28 @@
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N41" s="8">
-        <v>0</v>
-      </c>
-      <c r="O41" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O41" s="8">
+        <v>0</v>
+      </c>
+      <c r="P41" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="8" t="s">
         <v>110</v>
       </c>
@@ -5255,22 +5549,28 @@
         <v>0.5</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N42" s="8">
-        <v>0</v>
-      </c>
-      <c r="O42" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O42" s="8">
+        <v>0</v>
+      </c>
+      <c r="P42" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="8" t="s">
         <v>110</v>
       </c>
@@ -5308,26 +5608,32 @@
         <v>0.5</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="N43" s="8">
+        <v>5</v>
+      </c>
+      <c r="O43" s="8">
+        <v>0</v>
+      </c>
+      <c r="P43" s="8">
         <v>20</v>
       </c>
-      <c r="O43" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" s="10" t="s">
+      <c r="Q43" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q43" s="10" t="s">
+      <c r="S43" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T43" s="8"/>
+      <c r="U43" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="8" t="s">
         <v>110</v>
       </c>
@@ -5363,22 +5669,28 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N44" s="8">
-        <v>0</v>
-      </c>
-      <c r="O44" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O44" s="8">
+        <v>0</v>
+      </c>
+      <c r="P44" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="8" t="s">
         <v>110</v>
       </c>
@@ -5414,22 +5726,28 @@
         <v>0.5</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N45" s="8">
-        <v>0</v>
-      </c>
-      <c r="O45" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O45" s="8">
+        <v>0</v>
+      </c>
+      <c r="P45" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="8" t="s">
         <v>110</v>
       </c>
@@ -5465,22 +5783,28 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N46" s="8">
-        <v>0</v>
-      </c>
-      <c r="O46" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O46" s="8">
+        <v>0</v>
+      </c>
+      <c r="P46" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="8" t="s">
         <v>110</v>
       </c>
@@ -5518,26 +5842,32 @@
         <v>0.5</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="N47" s="8">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P47" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="8">
+        <v>0</v>
+      </c>
+      <c r="P47" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q47" s="10" t="s">
+      <c r="S47" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R47" s="8"/>
-      <c r="S47" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T47" s="8"/>
+      <c r="U47" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="8" t="s">
         <v>110</v>
       </c>
@@ -5575,22 +5905,28 @@
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="N48" s="8">
-        <v>0</v>
-      </c>
-      <c r="O48" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="8"/>
-      <c r="S48" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="O48" s="8">
+        <v>0</v>
+      </c>
+      <c r="P48" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="8" t="s">
         <v>110</v>
       </c>
@@ -5628,22 +5964,28 @@
         <v>0.5</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="N49" s="8">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="8"/>
-      <c r="S49" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>5</v>
+      </c>
+      <c r="O49" s="8">
+        <v>0</v>
+      </c>
+      <c r="P49" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A50" s="8" t="s">
         <v>110</v>
       </c>
@@ -5679,28 +6021,34 @@
         <v>0.5</v>
       </c>
       <c r="M50" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="N50" s="8">
+        <v>5</v>
+      </c>
+      <c r="O50" s="8">
+        <v>0</v>
+      </c>
+      <c r="P50" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S50" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T50" s="8"/>
+      <c r="U50" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="N50" s="8">
-        <v>0</v>
-      </c>
-      <c r="O50" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P50" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q50" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="13" t="s">
-        <v>123</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>103</v>
@@ -5734,24 +6082,30 @@
         <v>0.5</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="N51" s="13">
-        <v>0</v>
-      </c>
-      <c r="O51" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
+        <v>6</v>
+      </c>
+      <c r="O51" s="13">
+        <v>0</v>
+      </c>
+      <c r="P51" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R51" s="13"/>
-      <c r="S51" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>103</v>
@@ -5769,7 +6123,7 @@
         <v>104</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H52" s="8">
         <v>8</v>
@@ -5787,28 +6141,34 @@
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="N52" s="8">
-        <v>0</v>
-      </c>
-      <c r="O52" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P52" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O52" s="8">
+        <v>0</v>
+      </c>
+      <c r="P52" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q52" s="10" t="s">
+      <c r="S52" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T52" s="8"/>
+      <c r="U52" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -5842,24 +6202,30 @@
         <v>0.5</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="N53" s="8">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O53" s="8">
+        <v>0</v>
+      </c>
+      <c r="P53" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="8"/>
+      <c r="U53" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>103</v>
@@ -5877,7 +6243,7 @@
         <v>104</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H54" s="8">
         <v>8</v>
@@ -5895,28 +6261,34 @@
         <v>0.5</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N54" s="8">
-        <v>0</v>
-      </c>
-      <c r="O54" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P54" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O54" s="8">
+        <v>0</v>
+      </c>
+      <c r="P54" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R54" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q54" s="10" t="s">
+      <c r="S54" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T54" s="8"/>
+      <c r="U54" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>103</v>
@@ -5952,24 +6324,30 @@
         <v>0.5</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N55" s="8">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O55" s="8">
+        <v>0</v>
+      </c>
+      <c r="P55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="8"/>
+      <c r="U55" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>103</v>
@@ -6005,24 +6383,30 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N56" s="8">
-        <v>0</v>
-      </c>
-      <c r="O56" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="8"/>
-      <c r="S56" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O56" s="8">
+        <v>0</v>
+      </c>
+      <c r="P56" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>103</v>
@@ -6040,7 +6424,7 @@
         <v>83</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H57" s="8">
         <v>4</v>
@@ -6058,28 +6442,34 @@
         <v>0.5</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N57" s="8">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P57" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O57" s="8">
+        <v>0</v>
+      </c>
+      <c r="P57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q57" s="10" t="s">
+      <c r="S57" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R57" s="8"/>
-      <c r="S57" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T57" s="8"/>
+      <c r="U57" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>1</v>
@@ -6113,24 +6503,30 @@
         <v>0.5</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N58" s="8">
-        <v>0</v>
-      </c>
-      <c r="O58" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O58" s="8">
+        <v>0</v>
+      </c>
+      <c r="P58" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>103</v>
@@ -6166,24 +6562,30 @@
         <v>0.5</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N59" s="8">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O59" s="8">
+        <v>0</v>
+      </c>
+      <c r="P59" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="8"/>
+      <c r="U59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>103</v>
@@ -6219,24 +6621,30 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N60" s="8">
-        <v>0</v>
-      </c>
-      <c r="O60" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="O60" s="8">
+        <v>0</v>
+      </c>
+      <c r="P60" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="8"/>
+      <c r="U60" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>103</v>
@@ -6254,7 +6662,7 @@
         <v>83</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H61" s="8">
         <v>6</v>
@@ -6272,28 +6680,34 @@
         <v>0.5</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N61" s="8">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P61" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O61" s="8">
+        <v>0</v>
+      </c>
+      <c r="P61" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q61" s="10" t="s">
+      <c r="S61" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R61" s="8"/>
-      <c r="S61" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T61" s="8"/>
+      <c r="U61" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>103</v>
@@ -6329,28 +6743,34 @@
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N62" s="8">
-        <v>0</v>
-      </c>
-      <c r="O62" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P62" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O62" s="8">
+        <v>0</v>
+      </c>
+      <c r="P62" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q62" s="10" t="s">
+      <c r="S62" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T62" s="8"/>
+      <c r="U62" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>1</v>
@@ -6384,24 +6804,30 @@
         <v>0.5</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N63" s="8">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="8"/>
-      <c r="S63" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>6</v>
+      </c>
+      <c r="O63" s="8">
+        <v>0</v>
+      </c>
+      <c r="P63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>109</v>
@@ -6435,28 +6861,34 @@
         <v>0.5</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="N64" s="8">
-        <v>0</v>
-      </c>
-      <c r="O64" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P64" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O64" s="8">
+        <v>0</v>
+      </c>
+      <c r="P64" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q64" s="10" t="s">
+      <c r="S64" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="T64" s="8"/>
+      <c r="U64" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A65" s="13" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>1</v>
@@ -6490,24 +6922,30 @@
         <v>0.5</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="N65" s="13">
-        <v>0</v>
-      </c>
-      <c r="O65" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P65" s="13"/>
-      <c r="Q65" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="O65" s="13">
+        <v>0</v>
+      </c>
+      <c r="P65" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R65" s="13"/>
-      <c r="S65" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S65" s="13"/>
+      <c r="T65" s="13"/>
+      <c r="U65" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>1</v>
@@ -6541,24 +6979,30 @@
         <v>0.5</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="N66" s="8">
-        <v>0</v>
-      </c>
-      <c r="O66" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
-      <c r="R66" s="8"/>
-      <c r="S66" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O66" s="8">
+        <v>0</v>
+      </c>
+      <c r="P66" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>1</v>
@@ -6576,7 +7020,7 @@
         <v>83</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H67" s="8">
         <v>4</v>
@@ -6594,28 +7038,34 @@
         <v>0.5</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="N67" s="8">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P67" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O67" s="8">
+        <v>0</v>
+      </c>
+      <c r="P67" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q67" s="10" t="s">
+      <c r="S67" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R67" s="8"/>
-      <c r="S67" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T67" s="8"/>
+      <c r="U67" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>1</v>
@@ -6649,27 +7099,33 @@
         <v>0.5</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N68" s="8">
-        <v>0</v>
-      </c>
-      <c r="O68" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="8"/>
-      <c r="S68" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O68" s="8">
+        <v>0</v>
+      </c>
+      <c r="P68" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C69" s="8">
         <v>25</v>
@@ -6702,27 +7158,33 @@
         <v>0.5</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N69" s="8">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="8"/>
-      <c r="S69" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O69" s="8">
+        <v>0</v>
+      </c>
+      <c r="P69" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="8"/>
+      <c r="U69" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C70" s="8">
         <v>25</v>
@@ -6755,24 +7217,30 @@
         <v>0.5</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N70" s="8">
-        <v>0</v>
-      </c>
-      <c r="O70" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O70" s="8">
+        <v>0</v>
+      </c>
+      <c r="P70" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="8"/>
+      <c r="U70" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -6808,24 +7276,30 @@
         <v>0.5</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N71" s="8">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O71" s="8">
+        <v>0</v>
+      </c>
+      <c r="P71" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -6861,27 +7335,33 @@
         <v>0.5</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N72" s="8">
-        <v>0</v>
-      </c>
-      <c r="O72" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
-      <c r="R72" s="8"/>
-      <c r="S72" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O72" s="8">
+        <v>0</v>
+      </c>
+      <c r="P72" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C73" s="8">
         <v>35</v>
@@ -6912,24 +7392,30 @@
         <v>0.5</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N73" s="8">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="8"/>
-      <c r="S73" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O73" s="8">
+        <v>0</v>
+      </c>
+      <c r="P73" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="8"/>
+      <c r="U73" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -6963,27 +7449,33 @@
         <v>0.5</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N74" s="8">
-        <v>0</v>
-      </c>
-      <c r="O74" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
-      <c r="R74" s="8"/>
-      <c r="S74" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O74" s="8">
+        <v>0</v>
+      </c>
+      <c r="P74" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="8"/>
+      <c r="U74" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C75" s="8">
         <v>45</v>
@@ -6998,7 +7490,7 @@
         <v>83</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H75" s="8">
         <v>1</v>
@@ -7016,28 +7508,34 @@
         <v>0.5</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N75" s="8">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P75" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O75" s="8">
+        <v>0</v>
+      </c>
+      <c r="P75" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R75" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q75" s="10" t="s">
+      <c r="S75" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T75" s="8"/>
+      <c r="U75" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -7073,24 +7571,30 @@
         <v>0.5</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N76" s="8">
-        <v>0</v>
-      </c>
-      <c r="O76" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O76" s="8">
+        <v>0</v>
+      </c>
+      <c r="P76" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="8"/>
+      <c r="U76" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -7126,24 +7630,30 @@
         <v>0.5</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="N77" s="8">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="8"/>
-      <c r="S77" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O77" s="8">
+        <v>0</v>
+      </c>
+      <c r="P77" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="8"/>
+      <c r="U77" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>1</v>
@@ -7179,24 +7689,30 @@
         <v>0.5</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N78" s="8">
-        <v>0</v>
-      </c>
-      <c r="O78" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O78" s="8">
+        <v>0</v>
+      </c>
+      <c r="P78" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R78" s="10"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
@@ -7232,24 +7748,30 @@
         <v>0.5</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N79" s="8">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="O79" s="8">
+        <v>0</v>
+      </c>
+      <c r="P79" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>78</v>
@@ -7283,28 +7805,34 @@
         <v>0.5</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N80" s="8">
-        <v>0</v>
-      </c>
-      <c r="O80" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P80" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O80" s="8">
+        <v>0</v>
+      </c>
+      <c r="P80" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R80" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q80" s="10" t="s">
+      <c r="S80" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="T80" s="8"/>
+      <c r="U80" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A81" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>109</v>
@@ -7338,31 +7866,37 @@
         <v>0.5</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N81" s="8">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P81" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O81" s="8">
+        <v>0</v>
+      </c>
+      <c r="P81" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R81" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q81" s="10" t="s">
+      <c r="S81" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="T81" s="8"/>
+      <c r="U81" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A82" s="13" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C82" s="13">
         <v>3</v>
@@ -7393,24 +7927,30 @@
         <v>0.5</v>
       </c>
       <c r="M82" s="13" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N82" s="13">
-        <v>0</v>
-      </c>
-      <c r="O82" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P82" s="13"/>
-      <c r="Q82" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="O82" s="13">
+        <v>0</v>
+      </c>
+      <c r="P82" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="R82" s="13"/>
-      <c r="S82" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S82" s="13"/>
+      <c r="T82" s="13"/>
+      <c r="U82" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="8" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -7444,28 +7984,921 @@
         <v>0.5</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N83" s="8">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P83" s="10"/>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="8"/>
-      <c r="S83" s="8">
+        <v>7</v>
+      </c>
+      <c r="O83" s="8">
+        <v>0</v>
+      </c>
+      <c r="P83" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="8"/>
+      <c r="U83" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="8">
+        <v>10</v>
+      </c>
+      <c r="D84" s="10">
+        <v>1</v>
+      </c>
+      <c r="E84" s="10">
+        <v>1</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H84" s="8">
+        <v>34</v>
+      </c>
+      <c r="I84" s="8">
+        <v>34</v>
+      </c>
+      <c r="J84" s="8">
+        <v>0</v>
+      </c>
+      <c r="K84" s="8">
+        <v>1</v>
+      </c>
+      <c r="L84" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M84" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="N84" s="8">
+        <v>7</v>
+      </c>
+      <c r="O84" s="8">
+        <v>0</v>
+      </c>
+      <c r="P84" s="8">
+        <v>17.5</v>
+      </c>
+      <c r="Q84" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R84" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S84" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T84" s="8"/>
+      <c r="U84" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" s="8">
+        <v>15</v>
+      </c>
+      <c r="D85" s="10">
+        <v>3</v>
+      </c>
+      <c r="E85" s="10">
+        <v>1</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8">
+        <v>1</v>
+      </c>
+      <c r="I85" s="8">
+        <v>1</v>
+      </c>
+      <c r="J85" s="8">
+        <v>0</v>
+      </c>
+      <c r="K85" s="8">
+        <v>0</v>
+      </c>
+      <c r="L85" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N85" s="8">
+        <v>7</v>
+      </c>
+      <c r="O85" s="8">
+        <v>0</v>
+      </c>
+      <c r="P85" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="8"/>
+      <c r="U85" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="8">
+        <v>20</v>
+      </c>
+      <c r="D86" s="10">
+        <v>3</v>
+      </c>
+      <c r="E86" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H86" s="8">
+        <v>1</v>
+      </c>
+      <c r="I86" s="8">
+        <v>2</v>
+      </c>
+      <c r="J86" s="8">
+        <v>0</v>
+      </c>
+      <c r="K86" s="8">
+        <v>0</v>
+      </c>
+      <c r="L86" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M86" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N86" s="8">
+        <v>7</v>
+      </c>
+      <c r="O86" s="8">
+        <v>0</v>
+      </c>
+      <c r="P86" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R86" s="10"/>
+      <c r="S86" s="10"/>
+      <c r="T86" s="8"/>
+      <c r="U86" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="8">
+        <v>20</v>
+      </c>
+      <c r="D87" s="10">
+        <v>3</v>
+      </c>
+      <c r="E87" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H87" s="8">
+        <v>1</v>
+      </c>
+      <c r="I87" s="8">
+        <v>2</v>
+      </c>
+      <c r="J87" s="8">
+        <v>0</v>
+      </c>
+      <c r="K87" s="8">
+        <v>0</v>
+      </c>
+      <c r="L87" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N87" s="8">
+        <v>7</v>
+      </c>
+      <c r="O87" s="8">
+        <v>0</v>
+      </c>
+      <c r="P87" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="8"/>
+      <c r="U87" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C88" s="8">
+        <v>30</v>
+      </c>
+      <c r="D88" s="10">
+        <v>3</v>
+      </c>
+      <c r="E88" s="10">
+        <v>1</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8">
+        <v>1</v>
+      </c>
+      <c r="I88" s="8">
+        <v>1</v>
+      </c>
+      <c r="J88" s="8">
+        <v>0</v>
+      </c>
+      <c r="K88" s="8">
+        <v>0</v>
+      </c>
+      <c r="L88" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M88" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N88" s="8">
+        <v>7</v>
+      </c>
+      <c r="O88" s="8">
+        <v>0</v>
+      </c>
+      <c r="P88" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R88" s="10"/>
+      <c r="S88" s="10"/>
+      <c r="T88" s="8"/>
+      <c r="U88" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89" s="8">
+        <v>35</v>
+      </c>
+      <c r="D89" s="10">
+        <v>1</v>
+      </c>
+      <c r="E89" s="10">
+        <v>1</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89" s="8">
+        <v>6</v>
+      </c>
+      <c r="I89" s="8">
+        <v>6</v>
+      </c>
+      <c r="J89" s="8">
+        <v>0</v>
+      </c>
+      <c r="K89" s="8">
+        <v>1</v>
+      </c>
+      <c r="L89" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N89" s="8">
+        <v>7</v>
+      </c>
+      <c r="O89" s="8">
+        <v>0</v>
+      </c>
+      <c r="P89" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R89" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S89" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T89" s="8"/>
+      <c r="U89" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="8">
+        <v>40</v>
+      </c>
+      <c r="D90" s="10">
+        <v>1</v>
+      </c>
+      <c r="E90" s="10">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H90" s="8">
+        <v>34</v>
+      </c>
+      <c r="I90" s="8">
+        <v>34</v>
+      </c>
+      <c r="J90" s="8">
+        <v>0</v>
+      </c>
+      <c r="K90" s="8">
+        <v>1</v>
+      </c>
+      <c r="L90" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M90" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="N90" s="8">
+        <v>7</v>
+      </c>
+      <c r="O90" s="8">
+        <v>0</v>
+      </c>
+      <c r="P90" s="8">
+        <v>17.5</v>
+      </c>
+      <c r="Q90" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R90" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S90" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T90" s="8"/>
+      <c r="U90" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" s="8">
+        <v>45</v>
+      </c>
+      <c r="D91" s="10">
+        <v>3</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8">
+        <v>1</v>
+      </c>
+      <c r="I91" s="8">
+        <v>1</v>
+      </c>
+      <c r="J91" s="8">
+        <v>0</v>
+      </c>
+      <c r="K91" s="8">
+        <v>0</v>
+      </c>
+      <c r="L91" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N91" s="8">
+        <v>7</v>
+      </c>
+      <c r="O91" s="8">
+        <v>0</v>
+      </c>
+      <c r="P91" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="8"/>
+      <c r="U91" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92" s="8">
+        <v>50</v>
+      </c>
+      <c r="D92" s="10">
+        <v>3</v>
+      </c>
+      <c r="E92" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H92" s="8">
+        <v>1</v>
+      </c>
+      <c r="I92" s="8">
+        <v>2</v>
+      </c>
+      <c r="J92" s="8">
+        <v>0</v>
+      </c>
+      <c r="K92" s="8">
+        <v>0</v>
+      </c>
+      <c r="L92" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M92" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N92" s="8">
+        <v>7</v>
+      </c>
+      <c r="O92" s="8">
+        <v>0</v>
+      </c>
+      <c r="P92" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R92" s="10"/>
+      <c r="S92" s="10"/>
+      <c r="T92" s="8"/>
+      <c r="U92" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="8">
+        <v>50</v>
+      </c>
+      <c r="D93" s="10">
+        <v>3</v>
+      </c>
+      <c r="E93" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H93" s="8">
+        <v>1</v>
+      </c>
+      <c r="I93" s="8">
+        <v>2</v>
+      </c>
+      <c r="J93" s="8">
+        <v>0</v>
+      </c>
+      <c r="K93" s="8">
+        <v>0</v>
+      </c>
+      <c r="L93" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N93" s="8">
+        <v>7</v>
+      </c>
+      <c r="O93" s="8">
+        <v>0</v>
+      </c>
+      <c r="P93" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="8"/>
+      <c r="U93" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" s="8">
+        <v>55</v>
+      </c>
+      <c r="D94" s="10">
+        <v>1</v>
+      </c>
+      <c r="E94" s="10">
+        <v>1</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H94" s="8">
+        <v>6</v>
+      </c>
+      <c r="I94" s="8">
+        <v>6</v>
+      </c>
+      <c r="J94" s="8">
+        <v>0</v>
+      </c>
+      <c r="K94" s="8">
+        <v>1</v>
+      </c>
+      <c r="L94" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M94" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N94" s="8">
+        <v>7</v>
+      </c>
+      <c r="O94" s="8">
+        <v>0</v>
+      </c>
+      <c r="P94" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R94" s="10"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="8"/>
+      <c r="U94" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A95" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C95" s="8">
+        <v>59</v>
+      </c>
+      <c r="D95" s="10">
+        <v>1</v>
+      </c>
+      <c r="E95" s="10">
+        <v>1</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8">
+        <v>1</v>
+      </c>
+      <c r="I95" s="8">
+        <v>1</v>
+      </c>
+      <c r="J95" s="8">
+        <v>0</v>
+      </c>
+      <c r="K95" s="8">
+        <v>0</v>
+      </c>
+      <c r="L95" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N95" s="8">
+        <v>7</v>
+      </c>
+      <c r="O95" s="8">
+        <v>0</v>
+      </c>
+      <c r="P95" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R95" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S95" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T95" s="8"/>
+      <c r="U95" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="13">
+        <v>1</v>
+      </c>
+      <c r="D96" s="13">
+        <v>5</v>
+      </c>
+      <c r="E96" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13">
+        <v>2</v>
+      </c>
+      <c r="I96" s="13">
+        <v>3</v>
+      </c>
+      <c r="J96" s="13">
+        <v>0</v>
+      </c>
+      <c r="K96" s="13">
+        <v>0</v>
+      </c>
+      <c r="L96" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M96" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="N96" s="13">
+        <v>8</v>
+      </c>
+      <c r="O96" s="13">
+        <v>0</v>
+      </c>
+      <c r="P96" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R96" s="13"/>
+      <c r="S96" s="13"/>
+      <c r="T96" s="13"/>
+      <c r="U96" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="8">
+        <v>5</v>
+      </c>
+      <c r="D97" s="10">
+        <v>10</v>
+      </c>
+      <c r="E97" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8">
+        <v>1</v>
+      </c>
+      <c r="I97" s="8">
+        <v>1</v>
+      </c>
+      <c r="J97" s="8">
+        <v>0</v>
+      </c>
+      <c r="K97" s="8">
+        <v>0</v>
+      </c>
+      <c r="L97" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="N97" s="8">
+        <v>7</v>
+      </c>
+      <c r="O97" s="8">
+        <v>0</v>
+      </c>
+      <c r="P97" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="8"/>
+      <c r="U97" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="8">
+        <v>10</v>
+      </c>
+      <c r="D98" s="10">
+        <v>10</v>
+      </c>
+      <c r="E98" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8">
+        <v>1</v>
+      </c>
+      <c r="I98" s="8">
+        <v>1</v>
+      </c>
+      <c r="J98" s="8">
+        <v>0</v>
+      </c>
+      <c r="K98" s="8">
+        <v>0</v>
+      </c>
+      <c r="L98" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M98" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="N98" s="8">
+        <v>7</v>
+      </c>
+      <c r="O98" s="8">
+        <v>0</v>
+      </c>
+      <c r="P98" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R98" s="10"/>
+      <c r="S98" s="10"/>
+      <c r="T98" s="8"/>
+      <c r="U98" s="8">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O83" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q98" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
       <formula1>"false,true"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F83" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F98" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
       <formula1>"SpawnRandom,SpawnSide,SpawnRectangle,SpawnOval"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8316,13 +9749,13 @@
   <dimension ref="A1:AY5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.09765625" customWidth="1"/>
     <col min="3" max="3" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -8477,219 +9910,231 @@
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B2">
+        <f>$B$3+(B1+$B$4)+(B1^+$B$5)</f>
         <v>30</v>
       </c>
       <c r="C2">
-        <f>B2*$B$3</f>
-        <v>36</v>
+        <f>$B$3+(C1+$B$4)+(C1^+$B$5)</f>
+        <v>34</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AY2" si="0">C2*$B$3</f>
-        <v>43.199999999999996</v>
+        <f t="shared" ref="D2:AY2" si="0">$B$3+(D1+$B$4)+(D1^+$B$5)</f>
+        <v>40</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>51.839999999999996</v>
+        <v>48</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>62.207999999999991</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>74.649599999999992</v>
+        <v>70</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>89.579519999999988</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>107.49542399999999</v>
+        <v>100</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>128.99450879999998</v>
+        <v>118</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>154.79341055999996</v>
+        <v>138</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>185.75209267199995</v>
+        <v>160</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>222.90251120639994</v>
+        <v>184</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>267.48301344767992</v>
+        <v>210</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>320.97961613721588</v>
+        <v>238</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>385.17553936465907</v>
+        <v>268</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>462.21064723759088</v>
+        <v>300</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>554.65277668510907</v>
+        <v>334</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>665.58333202213089</v>
+        <v>370</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>798.69999842655704</v>
+        <v>408</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>958.43999811186836</v>
+        <v>448</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>1150.1279977342419</v>
+        <v>490</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>1380.1535972810902</v>
+        <v>534</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>1656.1843167373083</v>
+        <v>580</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>1987.42118008477</v>
+        <v>628</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>2384.9054161017239</v>
+        <v>678</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>2861.8864993220686</v>
+        <v>730</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>3434.2637991864822</v>
+        <v>784</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>4121.1165590237788</v>
+        <v>840</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>4945.339870828534</v>
+        <v>898</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>5934.4078449942408</v>
+        <v>958</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>7121.2894139930886</v>
+        <v>1020</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>8545.5472967917067</v>
+        <v>1084</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>10254.656756150047</v>
+        <v>1150</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>12305.588107380056</v>
+        <v>1218</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="0"/>
-        <v>14766.705728856066</v>
+        <v>1288</v>
       </c>
       <c r="AK2">
         <f t="shared" si="0"/>
-        <v>17720.046874627278</v>
+        <v>1360</v>
       </c>
       <c r="AL2">
         <f t="shared" si="0"/>
-        <v>21264.056249552734</v>
+        <v>1434</v>
       </c>
       <c r="AM2">
         <f t="shared" si="0"/>
-        <v>25516.867499463278</v>
+        <v>1510</v>
       </c>
       <c r="AN2">
         <f t="shared" si="0"/>
-        <v>30620.240999355934</v>
+        <v>1588</v>
       </c>
       <c r="AO2">
         <f t="shared" si="0"/>
-        <v>36744.289199227118</v>
+        <v>1668</v>
       </c>
       <c r="AP2">
         <f t="shared" si="0"/>
-        <v>44093.147039072537</v>
+        <v>1750</v>
       </c>
       <c r="AQ2">
         <f t="shared" si="0"/>
-        <v>52911.776446887045</v>
+        <v>1834</v>
       </c>
       <c r="AR2">
         <f t="shared" si="0"/>
-        <v>63494.131736264448</v>
+        <v>1920</v>
       </c>
       <c r="AS2">
         <f t="shared" si="0"/>
-        <v>76192.95808351734</v>
+        <v>2008</v>
       </c>
       <c r="AT2">
         <f t="shared" si="0"/>
-        <v>91431.549700220799</v>
+        <v>2098</v>
       </c>
       <c r="AU2">
         <f t="shared" si="0"/>
-        <v>109717.85964026496</v>
+        <v>2190</v>
       </c>
       <c r="AV2">
         <f t="shared" si="0"/>
-        <v>131661.43156831793</v>
+        <v>2284</v>
       </c>
       <c r="AW2">
         <f t="shared" si="0"/>
-        <v>157993.71788198152</v>
+        <v>2380</v>
       </c>
       <c r="AX2">
         <f t="shared" si="0"/>
-        <v>189592.4614583778</v>
+        <v>2478</v>
       </c>
       <c r="AY2">
         <f t="shared" si="0"/>
-        <v>227510.95375005336</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B3">
-        <v>1.2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>135</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8697,4 +10142,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEA4FC2-4AEE-4423-B407-B48D0DBD3E6C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4C0A9B-64AE-4C8B-9A59-B84FB9BE3526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CD44A8-08AC-4AD9-AAC7-1F65568A62B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="24" windowWidth="14460" windowHeight="10488" firstSheet="1" activeTab="3" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
     <sheet name="ImportData" sheetId="1" r:id="rId1"/>
@@ -49,6 +49,7 @@
     <author>tc={EB6B3A68-8148-45AE-9278-985634B59876}</author>
     <author>tc={2EA2148F-5DB8-45A5-B6B5-E8B64F389B05}</author>
     <author>tc={B8461874-3A04-4C37-B137-668B2D0D0DD9}</author>
+    <author>tc={BF2AB659-DF21-4F83-B65B-65B50FCE6343}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{65B6A188-F81E-4121-9301-0FFE406E0779}">
@@ -140,9 +141,19 @@
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     〇Wave８
-主にスナイパーとタンクを出現させ、
-対処法を探らせる。
-ノーマルを囲み要因として使う。</t>
+画面外から囲むように敵を生成する。
+生成処理を行う回数はおおよそ、
+N:S:T=４:1:５ の比率とする。
+ボスを３体同時出現させる。</t>
+      </text>
+    </comment>
+    <comment ref="A111" authorId="9" shapeId="0" xr:uid="{BF2AB659-DF21-4F83-B65B-65B50FCE6343}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave９
+ボスはタンクとスナイパーを同時に。</t>
       </text>
     </comment>
   </commentList>
@@ -150,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="159">
   <si>
     <t>Wave1</t>
   </si>
@@ -406,43 +417,6 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>SpawnRandom：画面外のランダムな位置から生成
-SpawnSide：画面外の特定の方向から生成
-SpawnOval：プレイヤーを中心とした楕円形になるように生成
-SpawnRectangle：プレイヤーを中心とした長方形になるように生成</t>
-    <rPh sb="38" eb="41">
-      <t>ガメンガイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>チュウシン</t>
-    </rPh>
-    <rPh sb="73" eb="76">
-      <t>ダエンケイ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>チュウシン</t>
-    </rPh>
-    <rPh sb="111" eb="114">
-      <t>チョウホウケイ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>セイセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -977,28 +951,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>SpawnRandom：入力無し
-SpawnSide：spawnDirection:Right（方角を指定する：Right,Left,Up,Down,UpperRight,UpperLeft,LowerRight,LowerLeft）
-SpawnOval：radiusx:10;radiusy:8（楕円のX軸;楕円のY軸）
-SpawnRectangle：sizex:10;sizey:7（長方形のX軸;長方形のY軸）</t>
-    <rPh sb="12" eb="15">
-      <t>ニュウリョクナ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ホウガク</t>
-    </rPh>
-    <rPh sb="194" eb="197">
-      <t>チョウホウケイ</t>
-    </rPh>
-    <rPh sb="199" eb="200">
-      <t>ジク</t>
-    </rPh>
-    <rPh sb="201" eb="204">
-      <t>チョウホウケイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>0.01以下：処理の一部がスキップされるかも。</t>
     <rPh sb="4" eb="6">
       <t>イカ</t>
@@ -1434,12 +1386,120 @@
     <t>MaxHP:3.2:0;ATK:2.4:0,Speed:2.1:0,DashSpeed:2.0:0</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>SpawnRandom：画面外のランダムな位置から生成
+SpawnSide：画面外の特定の方向から生成
+SpawnRandomRange：プレイヤーを中心としたドーナツ状の範囲内に生成
+SpawnOval：プレイヤーを中心とした楕円形になるように生成
+SpawnRectangle：プレイヤーを中心とした長方形になるように生成</t>
+    <rPh sb="38" eb="41">
+      <t>ガメンガイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="114" eb="117">
+      <t>ダエンケイ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="152" eb="155">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawnRandom：入力無し
+SpawnSide：spawnDirection:Right（方角を指定する：Right,Left,Up,Down,UpperRight,UpperLeft,LowerRight,LowerLeft）
+SpawnRandomRenge：minDistance:3;maxDistance:9（最小距離;最大距離）
+SpawnOval：radiusx:10;radiusy:8（楕円のX軸;楕円のY軸）
+SpawnRectangle：sizex:10;sizey:7（長方形のX軸;長方形のY軸）</t>
+    <rPh sb="12" eb="15">
+      <t>ニュウリョクナ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ホウガク</t>
+    </rPh>
+    <rPh sb="163" eb="167">
+      <t>サイショウキョリ</t>
+    </rPh>
+    <rPh sb="168" eb="172">
+      <t>サイダイキョリ</t>
+    </rPh>
+    <rPh sb="250" eb="253">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <rPh sb="255" eb="256">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="257" eb="260">
+      <t>チョウホウケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SpawmRamdomRange</t>
+  </si>
+  <si>
+    <t>minDistance:6;maxDistance:9</t>
+  </si>
+  <si>
+    <t>minDistance:6;maxDistance:9</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:15;sizey:12</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>minDistance:5;maxDistance:12</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wave9</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:3.4:0;ATK:2.6:0,Speed:2.2:0,DashSpeed:2.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1482,6 +1542,13 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -3065,17 +3132,22 @@
   </threadedComment>
   <threadedComment ref="A96" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{B8461874-3A04-4C37-B137-668B2D0D0DD9}">
     <text>〇Wave８
-主にスナイパーとタンクを出現させ、
-対処法を探らせる。
-ノーマルを囲み要因として使う。</text>
+画面外から囲むように敵を生成する。
+生成処理を行う回数はおおよそ、
+N:S:T=４:1:５ の比率とする。
+ボスを３体同時出現させる。</text>
+  </threadedComment>
+  <threadedComment ref="A111" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{BF2AB659-DF21-4F83-B65B-65B50FCE6343}">
+    <text>〇Wave９
+ボスはタンクとスナイパーを同時に。</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
-  <dimension ref="A1:U98"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:U111"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.69921875" customWidth="1"/>
     <col min="2" max="2" width="24.19921875" customWidth="1"/>
@@ -3098,72 +3170,72 @@
     <col min="21" max="21" width="27.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" ht="76.2" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -3180,7 +3252,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7">
@@ -3199,7 +3271,7 @@
         <v>0.5</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
@@ -3220,7 +3292,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" ht="18" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -3237,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8">
@@ -3256,7 +3328,7 @@
         <v>0.5</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -3277,7 +3349,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" ht="18" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -3294,10 +3366,10 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
@@ -3315,7 +3387,7 @@
         <v>0.5</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -3336,7 +3408,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" ht="18" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
@@ -3353,7 +3425,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8">
@@ -3372,7 +3444,7 @@
         <v>0.5</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -3393,7 +3465,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" ht="18" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
@@ -3410,10 +3482,10 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -3431,7 +3503,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N6" s="8">
         <v>0</v>
@@ -3452,7 +3524,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" ht="18" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
@@ -3469,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8">
@@ -3488,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N7" s="8">
         <v>0</v>
@@ -3509,7 +3581,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" ht="18" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
@@ -3526,10 +3598,10 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
@@ -3547,7 +3619,7 @@
         <v>0.5</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N8" s="8">
         <v>0</v>
@@ -3568,7 +3640,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="18" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
@@ -3585,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8">
@@ -3604,7 +3676,7 @@
         <v>0.5</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -3625,7 +3697,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" ht="18" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
@@ -3642,10 +3714,10 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
@@ -3663,7 +3735,7 @@
         <v>0.5</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -3684,7 +3756,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" ht="18" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>0</v>
       </c>
@@ -3701,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8">
@@ -3720,7 +3792,7 @@
         <v>0.5</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -3741,7 +3813,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" ht="18" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>0</v>
       </c>
@@ -3758,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8">
@@ -3777,7 +3849,7 @@
         <v>0.5</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -3798,12 +3870,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A13" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" s="10">
         <v>59</v>
@@ -3815,9 +3887,11 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="10"/>
+        <v>152</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="H13" s="10">
         <v>1</v>
       </c>
@@ -3828,13 +3902,13 @@
         <v>0</v>
       </c>
       <c r="K13" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="10">
         <v>0.5</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N13" s="10">
         <v>0</v>
@@ -3849,19 +3923,19 @@
         <v>1</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T13" s="10"/>
       <c r="U13" s="10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A14" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>1</v>
@@ -3876,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13">
@@ -3895,13 +3969,13 @@
         <v>0.5</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N14" s="13">
         <v>3</v>
       </c>
       <c r="O14" s="13">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="P14" s="13">
         <v>0</v>
@@ -3916,9 +3990,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" ht="18" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>1</v>
@@ -3933,7 +4007,7 @@
         <v>0.5</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8">
@@ -3952,13 +4026,13 @@
         <v>0.5</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N15" s="8">
         <v>3</v>
       </c>
       <c r="O15" s="8">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -3973,9 +4047,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21">
       <c r="A16" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>1</v>
@@ -3990,10 +4064,10 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H16" s="8">
         <v>1</v>
@@ -4011,13 +4085,13 @@
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N16" s="8">
         <v>3</v>
       </c>
       <c r="O16" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
@@ -4032,9 +4106,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21">
       <c r="A17" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>1</v>
@@ -4049,10 +4123,10 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H17" s="8">
         <v>1</v>
@@ -4070,13 +4144,13 @@
         <v>0.5</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N17" s="8">
         <v>3</v>
       </c>
       <c r="O17" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
@@ -4091,9 +4165,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21">
       <c r="A18" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>1</v>
@@ -4108,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8">
@@ -4127,13 +4201,13 @@
         <v>0.5</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N18" s="8">
         <v>3</v>
       </c>
       <c r="O18" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
@@ -4148,9 +4222,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1</v>
@@ -4165,10 +4239,10 @@
         <v>5</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H19" s="8">
         <v>10</v>
@@ -4186,13 +4260,13 @@
         <v>0.5</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N19" s="8">
         <v>3</v>
       </c>
       <c r="O19" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P19" s="8">
         <v>0</v>
@@ -4201,19 +4275,19 @@
         <v>0</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T19" s="8"/>
       <c r="U19" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21">
       <c r="A20" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>1</v>
@@ -4228,10 +4302,10 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="8">
         <v>1</v>
@@ -4249,13 +4323,13 @@
         <v>0.5</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N20" s="8">
         <v>3</v>
       </c>
       <c r="O20" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -4270,9 +4344,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21">
       <c r="A21" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1</v>
@@ -4287,10 +4361,10 @@
         <v>0.5</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H21" s="8">
         <v>1</v>
@@ -4308,13 +4382,13 @@
         <v>0.5</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N21" s="8">
         <v>3</v>
       </c>
       <c r="O21" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>
@@ -4329,9 +4403,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21">
       <c r="A22" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1</v>
@@ -4346,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8">
@@ -4365,13 +4439,13 @@
         <v>0.5</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N22" s="8">
         <v>3</v>
       </c>
       <c r="O22" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P22" s="8">
         <v>0</v>
@@ -4386,12 +4460,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A23" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" s="10">
         <v>59</v>
@@ -4403,9 +4477,11 @@
         <v>0.1</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="10"/>
+        <v>152</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="H23" s="10">
         <v>1</v>
       </c>
@@ -4416,19 +4492,19 @@
         <v>0</v>
       </c>
       <c r="K23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="10">
         <v>0.5</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N23" s="10">
         <v>3</v>
       </c>
       <c r="O23" s="10">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P23" s="10">
         <v>0</v>
@@ -4437,22 +4513,22 @@
         <v>1</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T23" s="10"/>
       <c r="U23" s="10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A24" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" s="13">
         <v>1</v>
@@ -4464,7 +4540,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13">
@@ -4483,13 +4559,13 @@
         <v>0.5</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N24" s="13">
         <v>4</v>
       </c>
       <c r="O24" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P24" s="13">
         <v>0</v>
@@ -4504,9 +4580,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" ht="18" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1</v>
@@ -4521,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8">
@@ -4540,13 +4616,13 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N25" s="8">
         <v>4</v>
       </c>
       <c r="O25" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P25" s="8">
         <v>0</v>
@@ -4561,12 +4637,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" ht="18" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" s="8">
         <v>10</v>
@@ -4578,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8">
@@ -4597,13 +4673,13 @@
         <v>0.5</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N26" s="8">
         <v>4</v>
       </c>
       <c r="O26" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P26" s="8">
         <v>0</v>
@@ -4618,9 +4694,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" ht="18" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1</v>
@@ -4635,10 +4711,10 @@
         <v>5</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27" s="8">
         <v>13</v>
@@ -4656,13 +4732,13 @@
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N27" s="8">
         <v>4</v>
       </c>
       <c r="O27" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P27" s="8">
         <v>0</v>
@@ -4671,22 +4747,22 @@
         <v>0</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T27" s="8"/>
       <c r="U27" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" ht="18" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C28" s="8">
         <v>30</v>
@@ -4698,10 +4774,10 @@
         <v>1</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H28" s="8">
         <v>1</v>
@@ -4719,13 +4795,13 @@
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N28" s="8">
         <v>4</v>
       </c>
       <c r="O28" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P28" s="8">
         <v>0</v>
@@ -4740,12 +4816,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" ht="18" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C29" s="8">
         <v>30</v>
@@ -4757,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
@@ -4778,13 +4854,13 @@
         <v>0.5</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N29" s="8">
         <v>4</v>
       </c>
       <c r="O29" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P29" s="8">
         <v>0</v>
@@ -4799,9 +4875,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" ht="18" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1</v>
@@ -4816,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8">
@@ -4835,13 +4911,13 @@
         <v>0.5</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N30" s="8">
         <v>4</v>
       </c>
       <c r="O30" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P30" s="8">
         <v>0</v>
@@ -4856,12 +4932,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" ht="18" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C31" s="8">
         <v>40</v>
@@ -4873,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H31" s="8">
         <v>1</v>
@@ -4894,13 +4970,13 @@
         <v>0.5</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N31" s="8">
         <v>4</v>
       </c>
       <c r="O31" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P31" s="8">
         <v>0</v>
@@ -4915,12 +4991,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" ht="18" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C32" s="8">
         <v>40</v>
@@ -4932,10 +5008,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H32" s="8">
         <v>1</v>
@@ -4953,13 +5029,13 @@
         <v>0.5</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N32" s="8">
         <v>4</v>
       </c>
       <c r="O32" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P32" s="8">
         <v>0</v>
@@ -4974,9 +5050,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:21" ht="18" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1</v>
@@ -4991,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8">
@@ -5010,13 +5086,13 @@
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N33" s="8">
         <v>4</v>
       </c>
       <c r="O33" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P33" s="8">
         <v>0</v>
@@ -5031,12 +5107,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:21" ht="18" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C34" s="8">
         <v>45</v>
@@ -5048,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8">
@@ -5067,13 +5143,13 @@
         <v>0.5</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N34" s="8">
         <v>4</v>
       </c>
       <c r="O34" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P34" s="8">
         <v>0</v>
@@ -5088,12 +5164,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:21" ht="18" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35" s="8">
         <v>50</v>
@@ -5105,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8">
@@ -5124,13 +5200,13 @@
         <v>0.5</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N35" s="8">
         <v>4</v>
       </c>
       <c r="O35" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P35" s="8">
         <v>0</v>
@@ -5145,12 +5221,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A36" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C36" s="8">
         <v>59</v>
@@ -5162,9 +5238,11 @@
         <v>1</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="H36" s="8">
         <v>1</v>
       </c>
@@ -5175,19 +5253,19 @@
         <v>0</v>
       </c>
       <c r="K36" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="8">
         <v>0.5</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N36" s="8">
         <v>4</v>
       </c>
       <c r="O36" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P36" s="8">
         <v>0</v>
@@ -5196,22 +5274,22 @@
         <v>1</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T36" s="8"/>
       <c r="U36" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A37" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C37" s="13">
         <v>1</v>
@@ -5223,7 +5301,7 @@
         <v>0.5</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13">
@@ -5242,13 +5320,13 @@
         <v>0.5</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N37" s="13">
         <v>5</v>
       </c>
       <c r="O37" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P37" s="13">
         <v>0</v>
@@ -5263,9 +5341,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:21" ht="18" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1</v>
@@ -5280,10 +5358,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H38" s="8">
         <v>6</v>
@@ -5301,13 +5379,13 @@
         <v>0.5</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N38" s="8">
         <v>5</v>
       </c>
       <c r="O38" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P38" s="8">
         <v>0</v>
@@ -5316,19 +5394,19 @@
         <v>0</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T38" s="8"/>
       <c r="U38" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:21" ht="18" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1</v>
@@ -5343,10 +5421,10 @@
         <v>1</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H39" s="8">
         <v>6</v>
@@ -5364,13 +5442,13 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N39" s="8">
         <v>5</v>
       </c>
       <c r="O39" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P39" s="8">
         <v>0</v>
@@ -5379,19 +5457,19 @@
         <v>0</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S39" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T39" s="8"/>
       <c r="U39" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:21" ht="18" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>1</v>
@@ -5406,10 +5484,10 @@
         <v>1</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40" s="8">
         <v>6</v>
@@ -5427,13 +5505,13 @@
         <v>0.5</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N40" s="8">
         <v>5</v>
       </c>
       <c r="O40" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P40" s="8">
         <v>0</v>
@@ -5442,22 +5520,22 @@
         <v>0</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T40" s="8"/>
       <c r="U40" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:21" ht="18" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C41" s="8">
         <v>15</v>
@@ -5469,10 +5547,10 @@
         <v>0.5</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H41" s="8">
         <v>1</v>
@@ -5490,13 +5568,13 @@
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N41" s="8">
         <v>5</v>
       </c>
       <c r="O41" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P41" s="8">
         <v>0</v>
@@ -5511,12 +5589,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:21" ht="18" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C42" s="8">
         <v>15</v>
@@ -5528,10 +5606,10 @@
         <v>0.5</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H42" s="8">
         <v>1</v>
@@ -5549,13 +5627,13 @@
         <v>0.5</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N42" s="8">
         <v>5</v>
       </c>
       <c r="O42" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P42" s="8">
         <v>0</v>
@@ -5570,9 +5648,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:21" ht="18" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1</v>
@@ -5587,10 +5665,10 @@
         <v>1</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H43" s="8">
         <v>30</v>
@@ -5608,13 +5686,13 @@
         <v>0.5</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N43" s="8">
         <v>5</v>
       </c>
       <c r="O43" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P43" s="8">
         <v>20</v>
@@ -5623,19 +5701,19 @@
         <v>0</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T43" s="8"/>
       <c r="U43" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:21" ht="18" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1</v>
@@ -5650,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8">
@@ -5669,13 +5747,13 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N44" s="8">
         <v>5</v>
       </c>
       <c r="O44" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P44" s="8">
         <v>0</v>
@@ -5690,12 +5768,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:21" ht="18" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C45" s="8">
         <v>30</v>
@@ -5707,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8">
@@ -5726,13 +5804,13 @@
         <v>0.5</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N45" s="8">
         <v>5</v>
       </c>
       <c r="O45" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P45" s="8">
         <v>0</v>
@@ -5747,12 +5825,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:21" ht="18" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C46" s="8">
         <v>35</v>
@@ -5764,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8">
@@ -5783,13 +5861,13 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N46" s="8">
         <v>5</v>
       </c>
       <c r="O46" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P46" s="8">
         <v>0</v>
@@ -5804,9 +5882,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:21" ht="18" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>1</v>
@@ -5821,10 +5899,10 @@
         <v>1</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H47" s="8">
         <v>8</v>
@@ -5842,13 +5920,13 @@
         <v>0.5</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N47" s="8">
         <v>5</v>
       </c>
       <c r="O47" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P47" s="8">
         <v>0</v>
@@ -5857,22 +5935,22 @@
         <v>0</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S47" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:21" ht="18" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C48" s="8">
         <v>50</v>
@@ -5884,10 +5962,10 @@
         <v>0.5</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H48" s="8">
         <v>1</v>
@@ -5905,13 +5983,13 @@
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N48" s="8">
         <v>5</v>
       </c>
       <c r="O48" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P48" s="8">
         <v>0</v>
@@ -5926,12 +6004,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:21" ht="18" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C49" s="8">
         <v>50</v>
@@ -5943,10 +6021,10 @@
         <v>0.5</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H49" s="8">
         <v>1</v>
@@ -5964,13 +6042,13 @@
         <v>0.5</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N49" s="8">
         <v>5</v>
       </c>
       <c r="O49" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P49" s="8">
         <v>0</v>
@@ -5985,12 +6063,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A50" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="8">
         <v>59</v>
@@ -6002,9 +6080,11 @@
         <v>1</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G50" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="H50" s="8">
         <v>1</v>
       </c>
@@ -6015,19 +6095,19 @@
         <v>0</v>
       </c>
       <c r="K50" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="8">
         <v>0.5</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N50" s="8">
         <v>5</v>
       </c>
       <c r="O50" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P50" s="8">
         <v>0</v>
@@ -6036,22 +6116,22 @@
         <v>1</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S50" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T50" s="8"/>
       <c r="U50" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A51" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C51" s="13">
         <v>1</v>
@@ -6063,7 +6143,7 @@
         <v>0.5</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G51" s="13"/>
       <c r="H51" s="13">
@@ -6082,13 +6162,13 @@
         <v>0.5</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N51" s="13">
         <v>6</v>
       </c>
       <c r="O51" s="13">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P51" s="13">
         <v>0</v>
@@ -6103,12 +6183,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:21" ht="18" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C52" s="8">
         <v>5</v>
@@ -6120,10 +6200,10 @@
         <v>1</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H52" s="8">
         <v>8</v>
@@ -6141,13 +6221,13 @@
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N52" s="8">
         <v>6</v>
       </c>
       <c r="O52" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P52" s="8">
         <v>0</v>
@@ -6156,19 +6236,19 @@
         <v>0</v>
       </c>
       <c r="R52" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S52" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T52" s="8"/>
       <c r="U52" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:21" ht="18" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1</v>
@@ -6183,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8">
@@ -6202,13 +6282,13 @@
         <v>0.5</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N53" s="8">
         <v>6</v>
       </c>
       <c r="O53" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P53" s="8">
         <v>0</v>
@@ -6223,12 +6303,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:21" ht="18" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C54" s="8">
         <v>15</v>
@@ -6240,10 +6320,10 @@
         <v>1</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H54" s="8">
         <v>8</v>
@@ -6261,13 +6341,13 @@
         <v>0.5</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N54" s="8">
         <v>6</v>
       </c>
       <c r="O54" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P54" s="8">
         <v>0</v>
@@ -6276,22 +6356,22 @@
         <v>0</v>
       </c>
       <c r="R54" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S54" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T54" s="8"/>
       <c r="U54" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:21" ht="18" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C55" s="8">
         <v>20</v>
@@ -6303,10 +6383,10 @@
         <v>0.5</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
@@ -6324,13 +6404,13 @@
         <v>0.5</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N55" s="8">
         <v>6</v>
       </c>
       <c r="O55" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P55" s="8">
         <v>0</v>
@@ -6345,12 +6425,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:21" ht="18" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C56" s="8">
         <v>20</v>
@@ -6362,10 +6442,10 @@
         <v>0.5</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H56" s="8">
         <v>1</v>
@@ -6383,13 +6463,13 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N56" s="8">
         <v>6</v>
       </c>
       <c r="O56" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P56" s="8">
         <v>0</v>
@@ -6404,12 +6484,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:21" ht="18" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C57" s="8">
         <v>25</v>
@@ -6421,10 +6501,10 @@
         <v>3</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H57" s="8">
         <v>4</v>
@@ -6442,13 +6522,13 @@
         <v>0.5</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N57" s="8">
         <v>6</v>
       </c>
       <c r="O57" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P57" s="8">
         <v>0</v>
@@ -6457,19 +6537,19 @@
         <v>0</v>
       </c>
       <c r="R57" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S57" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T57" s="8"/>
       <c r="U57" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:21" ht="18" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>1</v>
@@ -6484,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8">
@@ -6503,13 +6583,13 @@
         <v>0.5</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N58" s="8">
         <v>6</v>
       </c>
       <c r="O58" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P58" s="8">
         <v>0</v>
@@ -6524,12 +6604,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:21" ht="18" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C59" s="8">
         <v>40</v>
@@ -6541,10 +6621,10 @@
         <v>0.5</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H59" s="8">
         <v>1</v>
@@ -6562,13 +6642,13 @@
         <v>0.5</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N59" s="8">
         <v>6</v>
       </c>
       <c r="O59" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P59" s="8">
         <v>0</v>
@@ -6583,12 +6663,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:21" ht="18" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C60" s="8">
         <v>40</v>
@@ -6600,10 +6680,10 @@
         <v>0.5</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H60" s="8">
         <v>1</v>
@@ -6621,13 +6701,13 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N60" s="8">
         <v>6</v>
       </c>
       <c r="O60" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P60" s="8">
         <v>0</v>
@@ -6642,12 +6722,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:21" ht="18" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C61" s="8">
         <v>45</v>
@@ -6659,10 +6739,10 @@
         <v>1</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H61" s="8">
         <v>6</v>
@@ -6680,13 +6760,13 @@
         <v>0.5</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N61" s="8">
         <v>6</v>
       </c>
       <c r="O61" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P61" s="8">
         <v>0</v>
@@ -6695,22 +6775,22 @@
         <v>0</v>
       </c>
       <c r="R61" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S61" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T61" s="8"/>
       <c r="U61" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:21" ht="18" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C62" s="8">
         <v>45</v>
@@ -6722,10 +6802,10 @@
         <v>1</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H62" s="8">
         <v>4</v>
@@ -6743,13 +6823,13 @@
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N62" s="8">
         <v>6</v>
       </c>
       <c r="O62" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P62" s="8">
         <v>0</v>
@@ -6758,19 +6838,19 @@
         <v>0</v>
       </c>
       <c r="R62" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S62" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:21" ht="18" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>1</v>
@@ -6785,7 +6865,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8">
@@ -6804,13 +6884,13 @@
         <v>0.5</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N63" s="8">
         <v>6</v>
       </c>
       <c r="O63" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P63" s="8">
         <v>0</v>
@@ -6825,12 +6905,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A64" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C64" s="8">
         <v>59</v>
@@ -6842,9 +6922,11 @@
         <v>1</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G64" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="H64" s="8">
         <v>1</v>
       </c>
@@ -6855,19 +6937,19 @@
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="8">
         <v>0.5</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N64" s="8">
         <v>6</v>
       </c>
       <c r="O64" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P64" s="8">
         <v>0</v>
@@ -6876,19 +6958,19 @@
         <v>1</v>
       </c>
       <c r="R64" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S64" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T64" s="8"/>
       <c r="U64" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A65" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>1</v>
@@ -6903,7 +6985,7 @@
         <v>0.75</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G65" s="13"/>
       <c r="H65" s="13">
@@ -6922,13 +7004,13 @@
         <v>0.5</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N65" s="13">
         <v>7</v>
       </c>
       <c r="O65" s="13">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P65" s="13">
         <v>0</v>
@@ -6943,9 +7025,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:21" ht="18" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>1</v>
@@ -6960,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8">
@@ -6979,13 +7061,13 @@
         <v>0.5</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N66" s="8">
         <v>7</v>
       </c>
       <c r="O66" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P66" s="8">
         <v>0</v>
@@ -7000,9 +7082,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:21" ht="18" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>1</v>
@@ -7017,10 +7099,10 @@
         <v>1</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H67" s="8">
         <v>4</v>
@@ -7038,13 +7120,13 @@
         <v>0.5</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N67" s="8">
         <v>7</v>
       </c>
       <c r="O67" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P67" s="8">
         <v>0</v>
@@ -7053,19 +7135,19 @@
         <v>0</v>
       </c>
       <c r="R67" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S67" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T67" s="8"/>
       <c r="U67" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:21" ht="18" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>1</v>
@@ -7080,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8">
@@ -7099,13 +7181,13 @@
         <v>0.5</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N68" s="8">
         <v>7</v>
       </c>
       <c r="O68" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P68" s="8">
         <v>0</v>
@@ -7120,12 +7202,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:21" ht="18" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C69" s="8">
         <v>25</v>
@@ -7137,10 +7219,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H69" s="8">
         <v>1</v>
@@ -7158,13 +7240,13 @@
         <v>0.5</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N69" s="8">
         <v>7</v>
       </c>
       <c r="O69" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P69" s="8">
         <v>0</v>
@@ -7179,12 +7261,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:21" ht="18" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C70" s="8">
         <v>25</v>
@@ -7196,10 +7278,10 @@
         <v>1</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H70" s="8">
         <v>1</v>
@@ -7217,13 +7299,13 @@
         <v>0.5</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N70" s="8">
         <v>7</v>
       </c>
       <c r="O70" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P70" s="8">
         <v>0</v>
@@ -7238,9 +7320,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:21" ht="18" customHeight="1">
       <c r="A71" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1</v>
@@ -7255,10 +7337,10 @@
         <v>1</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H71" s="8">
         <v>2</v>
@@ -7276,13 +7358,13 @@
         <v>0.5</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N71" s="8">
         <v>7</v>
       </c>
       <c r="O71" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P71" s="8">
         <v>0</v>
@@ -7297,9 +7379,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:21" ht="18" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1</v>
@@ -7314,10 +7396,10 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H72" s="8">
         <v>2</v>
@@ -7335,13 +7417,13 @@
         <v>0.5</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N72" s="8">
         <v>7</v>
       </c>
       <c r="O72" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P72" s="8">
         <v>0</v>
@@ -7356,12 +7438,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:21" ht="18" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C73" s="8">
         <v>35</v>
@@ -7373,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8">
@@ -7392,13 +7474,13 @@
         <v>0.5</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N73" s="8">
         <v>7</v>
       </c>
       <c r="O73" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P73" s="8">
         <v>0</v>
@@ -7413,9 +7495,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:21" ht="18" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1</v>
@@ -7430,7 +7512,7 @@
         <v>0.5</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8">
@@ -7449,13 +7531,13 @@
         <v>0.5</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N74" s="8">
         <v>7</v>
       </c>
       <c r="O74" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P74" s="8">
         <v>0</v>
@@ -7470,12 +7552,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:21" ht="18" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C75" s="8">
         <v>45</v>
@@ -7487,10 +7569,10 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H75" s="8">
         <v>1</v>
@@ -7508,13 +7590,13 @@
         <v>0.5</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N75" s="8">
         <v>7</v>
       </c>
       <c r="O75" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P75" s="8">
         <v>0</v>
@@ -7523,19 +7605,19 @@
         <v>0</v>
       </c>
       <c r="R75" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T75" s="8"/>
       <c r="U75" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:21" ht="18" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1</v>
@@ -7550,10 +7632,10 @@
         <v>1</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H76" s="8">
         <v>2</v>
@@ -7571,13 +7653,13 @@
         <v>0.5</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N76" s="8">
         <v>7</v>
       </c>
       <c r="O76" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P76" s="8">
         <v>0</v>
@@ -7592,9 +7674,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:21" ht="18" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1</v>
@@ -7609,10 +7691,10 @@
         <v>1</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H77" s="8">
         <v>2</v>
@@ -7630,13 +7712,13 @@
         <v>0.5</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N77" s="8">
         <v>7</v>
       </c>
       <c r="O77" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P77" s="8">
         <v>0</v>
@@ -7651,9 +7733,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:21" ht="18" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>1</v>
@@ -7668,10 +7750,10 @@
         <v>1</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H78" s="8">
         <v>2</v>
@@ -7689,13 +7771,13 @@
         <v>0.5</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N78" s="8">
         <v>7</v>
       </c>
       <c r="O78" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P78" s="8">
         <v>0</v>
@@ -7710,9 +7792,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:21" ht="18" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1</v>
@@ -7727,10 +7809,10 @@
         <v>1</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H79" s="8">
         <v>2</v>
@@ -7748,13 +7830,13 @@
         <v>0.5</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N79" s="8">
         <v>7</v>
       </c>
       <c r="O79" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P79" s="8">
         <v>0</v>
@@ -7769,12 +7851,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:21" ht="18" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C80" s="8">
         <v>59</v>
@@ -7786,9 +7868,11 @@
         <v>1</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G80" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="H80" s="8">
         <v>1</v>
       </c>
@@ -7799,19 +7883,19 @@
         <v>0</v>
       </c>
       <c r="K80" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="8">
         <v>0.5</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N80" s="8">
         <v>7</v>
       </c>
       <c r="O80" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P80" s="8">
         <v>0</v>
@@ -7820,22 +7904,22 @@
         <v>1</v>
       </c>
       <c r="R80" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T80" s="8"/>
       <c r="U80" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A81" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C81" s="8">
         <v>59</v>
@@ -7847,9 +7931,11 @@
         <v>1</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G81" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="H81" s="8">
         <v>1</v>
       </c>
@@ -7860,19 +7946,19 @@
         <v>0</v>
       </c>
       <c r="K81" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="8">
         <v>0.5</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N81" s="8">
         <v>7</v>
       </c>
       <c r="O81" s="8">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P81" s="8">
         <v>0</v>
@@ -7881,22 +7967,22 @@
         <v>1</v>
       </c>
       <c r="R81" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T81" s="8"/>
       <c r="U81" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A82" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C82" s="13">
         <v>3</v>
@@ -7908,7 +7994,7 @@
         <v>0.75</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G82" s="13"/>
       <c r="H82" s="13">
@@ -7927,13 +8013,13 @@
         <v>0.5</v>
       </c>
       <c r="M82" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N82" s="13">
         <v>7</v>
       </c>
       <c r="O82" s="13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P82" s="13">
         <v>0</v>
@@ -7948,9 +8034,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:21" ht="18" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1</v>
@@ -7965,7 +8051,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8">
@@ -7984,13 +8070,13 @@
         <v>0.5</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N83" s="8">
         <v>7</v>
       </c>
       <c r="O83" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P83" s="8">
         <v>0</v>
@@ -8005,9 +8091,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:21" ht="18" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1</v>
@@ -8022,10 +8108,10 @@
         <v>1</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H84" s="8">
         <v>34</v>
@@ -8043,13 +8129,13 @@
         <v>0.5</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N84" s="8">
         <v>7</v>
       </c>
       <c r="O84" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P84" s="8">
         <v>17.5</v>
@@ -8058,22 +8144,22 @@
         <v>0</v>
       </c>
       <c r="R84" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S84" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T84" s="8"/>
       <c r="U84" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:21" ht="18" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C85" s="8">
         <v>15</v>
@@ -8085,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G85" s="8"/>
       <c r="H85" s="8">
@@ -8104,13 +8190,13 @@
         <v>0.5</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N85" s="8">
         <v>7</v>
       </c>
       <c r="O85" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P85" s="8">
         <v>0</v>
@@ -8125,12 +8211,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:21" ht="18" customHeight="1">
       <c r="A86" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C86" s="8">
         <v>20</v>
@@ -8142,10 +8228,10 @@
         <v>0.75</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H86" s="8">
         <v>1</v>
@@ -8163,13 +8249,13 @@
         <v>0.5</v>
       </c>
       <c r="M86" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N86" s="8">
         <v>7</v>
       </c>
       <c r="O86" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P86" s="8">
         <v>0</v>
@@ -8184,12 +8270,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:21" ht="18" customHeight="1">
       <c r="A87" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C87" s="8">
         <v>20</v>
@@ -8201,10 +8287,10 @@
         <v>0.75</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H87" s="8">
         <v>1</v>
@@ -8222,13 +8308,13 @@
         <v>0.5</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N87" s="8">
         <v>7</v>
       </c>
       <c r="O87" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P87" s="8">
         <v>0</v>
@@ -8243,12 +8329,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:21" ht="18" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C88" s="8">
         <v>30</v>
@@ -8260,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G88" s="8"/>
       <c r="H88" s="8">
@@ -8279,13 +8365,13 @@
         <v>0.5</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N88" s="8">
         <v>7</v>
       </c>
       <c r="O88" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P88" s="8">
         <v>0</v>
@@ -8300,12 +8386,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:21" ht="18" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C89" s="8">
         <v>35</v>
@@ -8317,10 +8403,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H89" s="8">
         <v>6</v>
@@ -8338,13 +8424,13 @@
         <v>0.5</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N89" s="8">
         <v>7</v>
       </c>
       <c r="O89" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P89" s="8">
         <v>0</v>
@@ -8353,19 +8439,19 @@
         <v>0</v>
       </c>
       <c r="R89" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S89" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T89" s="8"/>
       <c r="U89" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:21" ht="18" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>1</v>
@@ -8380,10 +8466,10 @@
         <v>1</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H90" s="8">
         <v>34</v>
@@ -8401,13 +8487,13 @@
         <v>0.5</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N90" s="8">
         <v>7</v>
       </c>
       <c r="O90" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P90" s="8">
         <v>17.5</v>
@@ -8416,22 +8502,22 @@
         <v>0</v>
       </c>
       <c r="R90" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S90" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T90" s="8"/>
       <c r="U90" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:21" ht="18" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C91" s="8">
         <v>45</v>
@@ -8443,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8">
@@ -8462,13 +8548,13 @@
         <v>0.5</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N91" s="8">
         <v>7</v>
       </c>
       <c r="O91" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P91" s="8">
         <v>0</v>
@@ -8483,12 +8569,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:21" ht="18" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C92" s="8">
         <v>50</v>
@@ -8500,10 +8586,10 @@
         <v>0.75</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H92" s="8">
         <v>1</v>
@@ -8521,13 +8607,13 @@
         <v>0.5</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N92" s="8">
         <v>7</v>
       </c>
       <c r="O92" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P92" s="8">
         <v>0</v>
@@ -8542,12 +8628,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:21" ht="18" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C93" s="8">
         <v>50</v>
@@ -8559,10 +8645,10 @@
         <v>0.75</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H93" s="8">
         <v>1</v>
@@ -8580,13 +8666,13 @@
         <v>0.5</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N93" s="8">
         <v>7</v>
       </c>
       <c r="O93" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P93" s="8">
         <v>0</v>
@@ -8601,12 +8687,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:21" ht="18" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C94" s="8">
         <v>55</v>
@@ -8618,10 +8704,10 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H94" s="8">
         <v>6</v>
@@ -8639,13 +8725,13 @@
         <v>0.5</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N94" s="8">
         <v>7</v>
       </c>
       <c r="O94" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P94" s="8">
         <v>0</v>
@@ -8660,12 +8746,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:21" ht="18" customHeight="1" thickBot="1">
       <c r="A95" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C95" s="8">
         <v>59</v>
@@ -8677,9 +8763,11 @@
         <v>1</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G95" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="H95" s="8">
         <v>1</v>
       </c>
@@ -8690,19 +8778,19 @@
         <v>0</v>
       </c>
       <c r="K95" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="8">
         <v>0.5</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N95" s="8">
         <v>7</v>
       </c>
       <c r="O95" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P95" s="8">
         <v>0</v>
@@ -8711,22 +8799,22 @@
         <v>1</v>
       </c>
       <c r="R95" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S95" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T95" s="8"/>
       <c r="U95" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:21" ht="18" customHeight="1" thickTop="1">
       <c r="A96" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="C96" s="13">
         <v>1</v>
@@ -8735,17 +8823,17 @@
         <v>5</v>
       </c>
       <c r="E96" s="13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G96" s="13"/>
       <c r="H96" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J96" s="13">
         <v>0</v>
@@ -8757,13 +8845,13 @@
         <v>0.5</v>
       </c>
       <c r="M96" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N96" s="13">
         <v>8</v>
       </c>
       <c r="O96" s="13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P96" s="13">
         <v>0</v>
@@ -8778,9 +8866,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:21" ht="18" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>1</v>
@@ -8789,15 +8877,17 @@
         <v>5</v>
       </c>
       <c r="D97" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E97" s="10">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G97" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="H97" s="8">
         <v>1</v>
       </c>
@@ -8814,13 +8904,13 @@
         <v>0.5</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N97" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O97" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P97" s="8">
         <v>0</v>
@@ -8835,26 +8925,28 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:21" ht="18" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C98" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D98" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E98" s="10">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G98" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="H98" s="8">
         <v>1</v>
       </c>
@@ -8871,13 +8963,13 @@
         <v>0.5</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N98" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O98" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P98" s="8">
         <v>0</v>
@@ -8892,14 +8984,785 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="99" spans="1:21" ht="18" customHeight="1">
+      <c r="A99" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="8">
+        <v>5</v>
+      </c>
+      <c r="D99" s="10">
+        <v>5</v>
+      </c>
+      <c r="E99" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H99" s="8">
+        <v>1</v>
+      </c>
+      <c r="I99" s="8">
+        <v>1</v>
+      </c>
+      <c r="J99" s="8">
+        <v>0</v>
+      </c>
+      <c r="K99" s="8">
+        <v>0</v>
+      </c>
+      <c r="L99" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N99" s="8">
+        <v>8</v>
+      </c>
+      <c r="O99" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P99" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="8"/>
+      <c r="U99" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="18" customHeight="1">
+      <c r="A100" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="8">
+        <v>5</v>
+      </c>
+      <c r="D100" s="10">
+        <v>5</v>
+      </c>
+      <c r="E100" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H100" s="8">
+        <v>1</v>
+      </c>
+      <c r="I100" s="8">
+        <v>1</v>
+      </c>
+      <c r="J100" s="8">
+        <v>0</v>
+      </c>
+      <c r="K100" s="8">
+        <v>0</v>
+      </c>
+      <c r="L100" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M100" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N100" s="8">
+        <v>8</v>
+      </c>
+      <c r="O100" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P100" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" s="10"/>
+      <c r="S100" s="10"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="18" customHeight="1">
+      <c r="A101" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="8">
+        <v>10</v>
+      </c>
+      <c r="D101" s="10">
+        <v>5</v>
+      </c>
+      <c r="E101" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G101" s="10"/>
+      <c r="H101" s="8">
+        <v>1</v>
+      </c>
+      <c r="I101" s="8">
+        <v>2</v>
+      </c>
+      <c r="J101" s="8">
+        <v>0</v>
+      </c>
+      <c r="K101" s="8">
+        <v>0</v>
+      </c>
+      <c r="L101" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N101" s="8">
+        <v>8</v>
+      </c>
+      <c r="O101" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P101" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="18" customHeight="1">
+      <c r="A102" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="8">
+        <v>15</v>
+      </c>
+      <c r="D102" s="10">
+        <v>1</v>
+      </c>
+      <c r="E102" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H102" s="8">
+        <v>1</v>
+      </c>
+      <c r="I102" s="8">
+        <v>1</v>
+      </c>
+      <c r="J102" s="8">
+        <v>0</v>
+      </c>
+      <c r="K102" s="8">
+        <v>1</v>
+      </c>
+      <c r="L102" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M102" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N102" s="8">
+        <v>8</v>
+      </c>
+      <c r="O102" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P102" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S102" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T102" s="8"/>
+      <c r="U102" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="18" customHeight="1">
+      <c r="A103" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" s="8">
+        <v>20</v>
+      </c>
+      <c r="D103" s="10">
+        <v>10</v>
+      </c>
+      <c r="E103" s="10">
+        <v>1</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G103" s="10"/>
+      <c r="H103" s="8">
+        <v>1</v>
+      </c>
+      <c r="I103" s="8">
+        <v>2</v>
+      </c>
+      <c r="J103" s="8">
+        <v>0</v>
+      </c>
+      <c r="K103" s="8">
+        <v>0</v>
+      </c>
+      <c r="L103" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N103" s="8">
+        <v>8</v>
+      </c>
+      <c r="O103" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P103" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R103" s="10"/>
+      <c r="S103" s="10"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="18" customHeight="1">
+      <c r="A104" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104" s="8">
+        <v>35</v>
+      </c>
+      <c r="D104" s="10">
+        <v>2</v>
+      </c>
+      <c r="E104" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H104" s="8">
+        <v>1</v>
+      </c>
+      <c r="I104" s="8">
+        <v>1</v>
+      </c>
+      <c r="J104" s="8">
+        <v>0</v>
+      </c>
+      <c r="K104" s="8">
+        <v>0</v>
+      </c>
+      <c r="L104" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M104" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N104" s="8">
+        <v>8</v>
+      </c>
+      <c r="O104" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P104" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R104" s="10"/>
+      <c r="S104" s="10"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="18" customHeight="1">
+      <c r="A105" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C105" s="8">
+        <v>35</v>
+      </c>
+      <c r="D105" s="10">
+        <v>2</v>
+      </c>
+      <c r="E105" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H105" s="8">
+        <v>1</v>
+      </c>
+      <c r="I105" s="8">
+        <v>1</v>
+      </c>
+      <c r="J105" s="8">
+        <v>0</v>
+      </c>
+      <c r="K105" s="8">
+        <v>0</v>
+      </c>
+      <c r="L105" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M105" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N105" s="8">
+        <v>8</v>
+      </c>
+      <c r="O105" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P105" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="18" customHeight="1">
+      <c r="A106" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106" s="8">
+        <v>35</v>
+      </c>
+      <c r="D106" s="10">
+        <v>2</v>
+      </c>
+      <c r="E106" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H106" s="8">
+        <v>1</v>
+      </c>
+      <c r="I106" s="8">
+        <v>1</v>
+      </c>
+      <c r="J106" s="8">
+        <v>0</v>
+      </c>
+      <c r="K106" s="8">
+        <v>0</v>
+      </c>
+      <c r="L106" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M106" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N106" s="8">
+        <v>8</v>
+      </c>
+      <c r="O106" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P106" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R106" s="10"/>
+      <c r="S106" s="10"/>
+      <c r="T106" s="8"/>
+      <c r="U106" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="18" customHeight="1">
+      <c r="A107" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" s="8">
+        <v>35</v>
+      </c>
+      <c r="D107" s="10">
+        <v>2</v>
+      </c>
+      <c r="E107" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H107" s="8">
+        <v>1</v>
+      </c>
+      <c r="I107" s="8">
+        <v>1</v>
+      </c>
+      <c r="J107" s="8">
+        <v>0</v>
+      </c>
+      <c r="K107" s="8">
+        <v>0</v>
+      </c>
+      <c r="L107" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N107" s="8">
+        <v>8</v>
+      </c>
+      <c r="O107" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P107" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="8"/>
+      <c r="U107" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="18" customHeight="1">
+      <c r="A108" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="8">
+        <v>45</v>
+      </c>
+      <c r="D108" s="10">
+        <v>6</v>
+      </c>
+      <c r="E108" s="10">
+        <v>1</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H108" s="8">
+        <v>1</v>
+      </c>
+      <c r="I108" s="8">
+        <v>2</v>
+      </c>
+      <c r="J108" s="8">
+        <v>0</v>
+      </c>
+      <c r="K108" s="8">
+        <v>1</v>
+      </c>
+      <c r="L108" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M108" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N108" s="8">
+        <v>8</v>
+      </c>
+      <c r="O108" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P108" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R108" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S108" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T108" s="8"/>
+      <c r="U108" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="18" customHeight="1">
+      <c r="A109" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="8">
+        <v>52</v>
+      </c>
+      <c r="D109" s="10">
+        <v>5</v>
+      </c>
+      <c r="E109" s="10">
+        <v>1</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8">
+        <v>1</v>
+      </c>
+      <c r="I109" s="8">
+        <v>1</v>
+      </c>
+      <c r="J109" s="8">
+        <v>0</v>
+      </c>
+      <c r="K109" s="8">
+        <v>0</v>
+      </c>
+      <c r="L109" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N109" s="8">
+        <v>8</v>
+      </c>
+      <c r="O109" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P109" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R109" s="10"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="8"/>
+      <c r="U109" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" ht="18" customHeight="1" thickBot="1">
+      <c r="A110" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C110" s="8">
+        <v>59</v>
+      </c>
+      <c r="D110" s="10">
+        <v>1</v>
+      </c>
+      <c r="E110" s="10">
+        <v>1</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H110" s="8">
+        <v>3</v>
+      </c>
+      <c r="I110" s="8">
+        <v>3</v>
+      </c>
+      <c r="J110" s="8">
+        <v>0</v>
+      </c>
+      <c r="K110" s="8">
+        <v>1</v>
+      </c>
+      <c r="L110" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M110" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N110" s="8">
+        <v>8</v>
+      </c>
+      <c r="O110" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P110" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R110" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S110" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T110" s="8"/>
+      <c r="U110" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="18" customHeight="1" thickTop="1">
+      <c r="A111" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="13">
+        <v>1</v>
+      </c>
+      <c r="D111" s="13">
+        <v>5</v>
+      </c>
+      <c r="E111" s="13">
+        <v>1</v>
+      </c>
+      <c r="F111" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13">
+        <v>1</v>
+      </c>
+      <c r="I111" s="13">
+        <v>1</v>
+      </c>
+      <c r="J111" s="13">
+        <v>0</v>
+      </c>
+      <c r="K111" s="13">
+        <v>0</v>
+      </c>
+      <c r="L111" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M111" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="N111" s="13">
+        <v>8</v>
+      </c>
+      <c r="O111" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P111" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R111" s="13"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="13"/>
+      <c r="U111" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q98" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q111" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
       <formula1>"false,true"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F98" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
-      <formula1>"SpawnRandom,SpawnSide,SpawnRectangle,SpawnOval"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F111" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
+      <formula1>"SpawnRandom,SpawnSide,SpawmRamdomRange,SpawnRectangle,SpawnOval"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8910,7 +9773,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D671765-6BFE-4606-9C59-1F74507BF60E}">
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.69921875" customWidth="1"/>
     <col min="2" max="2" width="24.19921875" customWidth="1"/>
@@ -8932,68 +9795,68 @@
     <col min="20" max="21" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:19" ht="76.2" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19" ht="18" customHeight="1" thickBot="1">
+      <c r="A2" s="2" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -9029,24 +9892,24 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
@@ -9082,26 +9945,26 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
@@ -9137,26 +10000,26 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="18.600000000000001" thickBot="1">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
@@ -9192,21 +10055,21 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -9218,14 +10081,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22332C8A-7304-4E64-9BD3-13AF5949C9BF}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="39.8984375" customWidth="1"/>
     <col min="2" max="2" width="56.296875" customWidth="1"/>
     <col min="3" max="3" width="34.5" customWidth="1"/>
     <col min="4" max="4" width="25.3984375" customWidth="1"/>
     <col min="5" max="5" width="41" customWidth="1"/>
-    <col min="6" max="6" width="62.59765625" customWidth="1"/>
+    <col min="6" max="6" width="65.8984375" customWidth="1"/>
     <col min="7" max="7" width="109.796875" customWidth="1"/>
     <col min="8" max="9" width="26.19921875" customWidth="1"/>
     <col min="10" max="10" width="37.296875" customWidth="1"/>
@@ -9239,66 +10102,66 @@
     <col min="19" max="19" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:19" ht="41.4" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:19" ht="73.8" customHeight="1" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -9318,7 +10181,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>8</v>
@@ -9330,156 +10193,156 @@
         <v>11</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:19" ht="130.19999999999999" customHeight="1">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:19" ht="18.600000000000001" thickBot="1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
     </row>
-    <row r="5" spans="1:19" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:19" ht="33" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
@@ -9515,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N6" s="7">
         <v>0</v>
@@ -9530,7 +10393,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19">
       <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
@@ -9566,7 +10429,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N7" s="8">
         <v>0</v>
@@ -9581,7 +10444,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19">
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
@@ -9617,7 +10480,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N8" s="8">
         <v>0</v>
@@ -9632,7 +10495,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19">
       <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
@@ -9649,11 +10512,11 @@
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="H9" s="8">
         <v>0.5</v>
       </c>
@@ -9670,7 +10533,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -9685,7 +10548,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
@@ -9702,10 +10565,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H10" s="8">
         <v>0.5</v>
@@ -9723,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -9747,15 +10610,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88203281-AD27-4579-B140-3641B5403CC3}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.09765625" customWidth="1"/>
     <col min="3" max="3" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -9908,9 +10771,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B2">
         <f>$B$3+(B1+$B$4)+(B1^+$B$5)</f>
@@ -10113,25 +10976,25 @@
         <v>2578</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10147,7 +11010,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEA4FC2-4AEE-4423-B407-B48D0DBD3E6C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B525F51-96DA-4FF4-963D-572B955E4945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2723A3-0B13-4B41-99AE-3DF3B35F8671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="552" windowWidth="17280" windowHeight="11304" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
@@ -1494,24 +1494,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:1.7:0;ATK:1.3:0,Speed:1.3:0,DashSpeed:1.3:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.7:0;ATK:1.3:0,Speed:1.3:0,DashSpeed:1.3:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:2.0:20;ATK:1.4:0,Speed:0.2:0,DashSpeed:0.2:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:2.0:0;ATK:1.4:0,Speed:1.35:0,DashSpeed:1.35:0</t>
-  </si>
-  <si>
-    <t>MaxHP:2.0:0;ATK:1.4:0,Speed:1.35:0,DashSpeed:1.35:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MaxHP:2.3:0;ATK:1.5:0,Speed:1.4:0,DashSpeed:1.4:0</t>
   </si>
   <si>
@@ -1576,6 +1558,24 @@
   </si>
   <si>
     <t>SpawnNotice</t>
+  </si>
+  <si>
+    <t>MaxHP:1.5:0;ATK:1.3:0,Speed:1.3:0,DashSpeed:1.3:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.5:0;ATK:1.3:0,Speed:1.3:0,DashSpeed:1.3:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.9:0;ATK:1.4:0,Speed:1.35:0,DashSpeed:1.35:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.9:0;ATK:1.4:0,Speed:1.35:0,DashSpeed:1.35:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.9:20;ATK:1.4:0,Speed:0.2:0,DashSpeed:0.2:0</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -4224,7 +4224,7 @@
         <v>62</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U13" s="10">
         <v>0.5</v>
@@ -4266,7 +4266,7 @@
         <v>0.5</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N14" s="13">
         <v>2</v>
@@ -4323,7 +4323,7 @@
         <v>0.5</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N15" s="8">
         <v>2</v>
@@ -4382,7 +4382,7 @@
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N16" s="8">
         <v>2</v>
@@ -4441,7 +4441,7 @@
         <v>0.5</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N17" s="8">
         <v>2</v>
@@ -4498,7 +4498,7 @@
         <v>0.5</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N18" s="8">
         <v>2</v>
@@ -4557,7 +4557,7 @@
         <v>0.5</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N19" s="8">
         <v>2</v>
@@ -4578,7 +4578,7 @@
         <v>62</v>
       </c>
       <c r="T19" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U19" s="8">
         <v>0.5</v>
@@ -4622,7 +4622,7 @@
         <v>0.5</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N20" s="8">
         <v>2</v>
@@ -4681,7 +4681,7 @@
         <v>0.5</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N21" s="8">
         <v>2</v>
@@ -4738,7 +4738,7 @@
         <v>0.5</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N22" s="8">
         <v>2</v>
@@ -4797,7 +4797,7 @@
         <v>0.5</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N23" s="10">
         <v>2</v>
@@ -4818,7 +4818,7 @@
         <v>62</v>
       </c>
       <c r="T23" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U23" s="10">
         <v>0.5</v>
@@ -4860,10 +4860,10 @@
         <v>0.5</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="N24" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O24" s="13">
         <v>0.1</v>
@@ -4917,10 +4917,10 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="N25" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="8">
         <v>0.1</v>
@@ -4974,10 +4974,10 @@
         <v>0.5</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N26" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26" s="8">
         <v>0.1</v>
@@ -5033,10 +5033,10 @@
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N27" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" s="8">
         <v>0.1</v>
@@ -5054,7 +5054,7 @@
         <v>62</v>
       </c>
       <c r="T27" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U27" s="8">
         <v>0.5</v>
@@ -5098,10 +5098,10 @@
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N28" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28" s="8">
         <v>0.1</v>
@@ -5157,10 +5157,10 @@
         <v>0.5</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N29" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29" s="8">
         <v>0.1</v>
@@ -5214,10 +5214,10 @@
         <v>0.5</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N30" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" s="8">
         <v>0.1</v>
@@ -5273,10 +5273,10 @@
         <v>0.5</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N31" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" s="8">
         <v>0.1</v>
@@ -5332,10 +5332,10 @@
         <v>0.5</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N32" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32" s="8">
         <v>0.1</v>
@@ -5389,10 +5389,10 @@
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N33" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33" s="8">
         <v>0.1</v>
@@ -5446,10 +5446,10 @@
         <v>0.5</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N34" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34" s="8">
         <v>0.1</v>
@@ -5503,10 +5503,10 @@
         <v>0.5</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="N35" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35" s="8">
         <v>0.1</v>
@@ -5562,10 +5562,10 @@
         <v>0.5</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="N36" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36" s="8">
         <v>0.1</v>
@@ -5583,7 +5583,7 @@
         <v>62</v>
       </c>
       <c r="T36" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U36" s="8">
         <v>0.5</v>
@@ -5625,10 +5625,10 @@
         <v>0.5</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="N37" s="13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O37" s="13">
         <v>0.15</v>
@@ -5684,10 +5684,10 @@
         <v>0.5</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N38" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O38" s="8">
         <v>0.15</v>
@@ -5705,7 +5705,7 @@
         <v>62</v>
       </c>
       <c r="T38" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U38" s="8">
         <v>0.5</v>
@@ -5749,10 +5749,10 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N39" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O39" s="8">
         <v>0.15</v>
@@ -5770,7 +5770,7 @@
         <v>62</v>
       </c>
       <c r="T39" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U39" s="8">
         <v>0.5</v>
@@ -5814,10 +5814,10 @@
         <v>0.5</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N40" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O40" s="8">
         <v>0.15</v>
@@ -5835,7 +5835,7 @@
         <v>62</v>
       </c>
       <c r="T40" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U40" s="8">
         <v>0.5</v>
@@ -5879,10 +5879,10 @@
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N41" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O41" s="8">
         <v>0.15</v>
@@ -5938,10 +5938,10 @@
         <v>0.5</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N42" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O42" s="8">
         <v>0.15</v>
@@ -5997,10 +5997,10 @@
         <v>0.5</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="N43" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O43" s="8">
         <v>0.15</v>
@@ -6018,7 +6018,7 @@
         <v>62</v>
       </c>
       <c r="T43" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U43" s="8">
         <v>0.5</v>
@@ -6060,10 +6060,10 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N44" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O44" s="8">
         <v>0.15</v>
@@ -6117,10 +6117,10 @@
         <v>0.5</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N45" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O45" s="8">
         <v>0.15</v>
@@ -6174,10 +6174,10 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N46" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O46" s="8">
         <v>0.15</v>
@@ -6233,10 +6233,10 @@
         <v>0.5</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N47" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O47" s="8">
         <v>0.15</v>
@@ -6254,7 +6254,7 @@
         <v>62</v>
       </c>
       <c r="T47" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U47" s="8">
         <v>0.5</v>
@@ -6298,10 +6298,10 @@
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N48" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O48" s="8">
         <v>0.15</v>
@@ -6357,10 +6357,10 @@
         <v>0.5</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N49" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O49" s="8">
         <v>0.15</v>
@@ -6416,10 +6416,10 @@
         <v>0.5</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N50" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O50" s="8">
         <v>0.15</v>
@@ -6437,7 +6437,7 @@
         <v>62</v>
       </c>
       <c r="T50" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U50" s="8">
         <v>0.5</v>
@@ -6479,10 +6479,10 @@
         <v>0.5</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="N51" s="13">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O51" s="13">
         <v>0.2</v>
@@ -6538,10 +6538,10 @@
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N52" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O52" s="8">
         <v>0.2</v>
@@ -6559,7 +6559,7 @@
         <v>62</v>
       </c>
       <c r="T52" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U52" s="8">
         <v>0.5</v>
@@ -6601,10 +6601,10 @@
         <v>0.5</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N53" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O53" s="8">
         <v>0.2</v>
@@ -6660,10 +6660,10 @@
         <v>0.5</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N54" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O54" s="8">
         <v>0.2</v>
@@ -6681,7 +6681,7 @@
         <v>62</v>
       </c>
       <c r="T54" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U54" s="8">
         <v>0.5</v>
@@ -6725,10 +6725,10 @@
         <v>0.5</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N55" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O55" s="8">
         <v>0.2</v>
@@ -6784,10 +6784,10 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N56" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O56" s="8">
         <v>0.2</v>
@@ -6843,10 +6843,10 @@
         <v>0.5</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N57" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O57" s="8">
         <v>0.2</v>
@@ -6864,7 +6864,7 @@
         <v>62</v>
       </c>
       <c r="T57" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U57" s="8">
         <v>0.5</v>
@@ -6906,10 +6906,10 @@
         <v>0.5</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N58" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O58" s="8">
         <v>0.2</v>
@@ -6965,10 +6965,10 @@
         <v>0.5</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N59" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O59" s="8">
         <v>0.2</v>
@@ -7024,10 +7024,10 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N60" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O60" s="8">
         <v>0.2</v>
@@ -7083,10 +7083,10 @@
         <v>0.5</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N61" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O61" s="8">
         <v>0.2</v>
@@ -7104,7 +7104,7 @@
         <v>62</v>
       </c>
       <c r="T61" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U61" s="8">
         <v>0.5</v>
@@ -7148,10 +7148,10 @@
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N62" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O62" s="8">
         <v>0.2</v>
@@ -7169,7 +7169,7 @@
         <v>62</v>
       </c>
       <c r="T62" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U62" s="8">
         <v>0.5</v>
@@ -7211,10 +7211,10 @@
         <v>0.5</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N63" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O63" s="8">
         <v>0.2</v>
@@ -7270,10 +7270,10 @@
         <v>0.5</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N64" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O64" s="8">
         <v>0.2</v>
@@ -7291,7 +7291,7 @@
         <v>62</v>
       </c>
       <c r="T64" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U64" s="8">
         <v>0.5</v>
@@ -7335,10 +7335,10 @@
         <v>0.5</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N65" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O65" s="8">
         <v>0.2</v>
@@ -7356,7 +7356,7 @@
         <v>62</v>
       </c>
       <c r="T65" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U65" s="8">
         <v>0.5</v>
@@ -7398,10 +7398,10 @@
         <v>0.5</v>
       </c>
       <c r="M66" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N66" s="13">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O66" s="13">
         <v>0.25</v>
@@ -7455,10 +7455,10 @@
         <v>0.5</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N67" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O67" s="8">
         <v>0.25</v>
@@ -7514,10 +7514,10 @@
         <v>0.5</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N68" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O68" s="8">
         <v>0.25</v>
@@ -7535,7 +7535,7 @@
         <v>62</v>
       </c>
       <c r="T68" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U68" s="8">
         <v>0.5</v>
@@ -7577,10 +7577,10 @@
         <v>0.5</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N69" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O69" s="8">
         <v>0.25</v>
@@ -7636,10 +7636,10 @@
         <v>0.5</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N70" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O70" s="8">
         <v>0.25</v>
@@ -7695,10 +7695,10 @@
         <v>0.5</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N71" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O71" s="8">
         <v>0.25</v>
@@ -7754,10 +7754,10 @@
         <v>0.5</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N72" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O72" s="8">
         <v>0.25</v>
@@ -7813,10 +7813,10 @@
         <v>0.5</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N73" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O73" s="8">
         <v>0.25</v>
@@ -7870,10 +7870,10 @@
         <v>0.5</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N74" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O74" s="8">
         <v>0.25</v>
@@ -7927,10 +7927,10 @@
         <v>0.5</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N75" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O75" s="8">
         <v>0.25</v>
@@ -7986,10 +7986,10 @@
         <v>0.5</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N76" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O76" s="8">
         <v>0.25</v>
@@ -8007,7 +8007,7 @@
         <v>62</v>
       </c>
       <c r="T76" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U76" s="8">
         <v>0.5</v>
@@ -8051,10 +8051,10 @@
         <v>0.5</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N77" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O77" s="8">
         <v>0.25</v>
@@ -8110,10 +8110,10 @@
         <v>0.5</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N78" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O78" s="8">
         <v>0.25</v>
@@ -8169,10 +8169,10 @@
         <v>0.5</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N79" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O79" s="8">
         <v>0.25</v>
@@ -8228,10 +8228,10 @@
         <v>0.5</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N80" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O80" s="8">
         <v>0.25</v>
@@ -8287,10 +8287,10 @@
         <v>0.5</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N81" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O81" s="8">
         <v>0.25</v>
@@ -8308,7 +8308,7 @@
         <v>62</v>
       </c>
       <c r="T81" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U81" s="8">
         <v>0.5</v>
@@ -8352,10 +8352,10 @@
         <v>0.5</v>
       </c>
       <c r="M82" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N82" s="8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O82" s="8">
         <v>0.25</v>
@@ -8373,7 +8373,7 @@
         <v>62</v>
       </c>
       <c r="T82" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U82" s="8">
         <v>0.5</v>
@@ -8415,10 +8415,10 @@
         <v>0.5</v>
       </c>
       <c r="M83" s="13" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N83" s="13">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O83" s="13">
         <v>0.3</v>
@@ -8472,10 +8472,10 @@
         <v>0.5</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N84" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O84" s="8">
         <v>0.3</v>
@@ -8531,10 +8531,10 @@
         <v>0.5</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="N85" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O85" s="8">
         <v>0.3</v>
@@ -8552,7 +8552,7 @@
         <v>62</v>
       </c>
       <c r="T85" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U85" s="8">
         <v>0.5</v>
@@ -8594,10 +8594,10 @@
         <v>0.5</v>
       </c>
       <c r="M86" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N86" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O86" s="8">
         <v>0.3</v>
@@ -8653,10 +8653,10 @@
         <v>0.5</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N87" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O87" s="8">
         <v>0.3</v>
@@ -8712,10 +8712,10 @@
         <v>0.5</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N88" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O88" s="8">
         <v>0.3</v>
@@ -8769,10 +8769,10 @@
         <v>0.5</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N89" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O89" s="8">
         <v>0.3</v>
@@ -8828,10 +8828,10 @@
         <v>0.5</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N90" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O90" s="8">
         <v>0.3</v>
@@ -8849,7 +8849,7 @@
         <v>62</v>
       </c>
       <c r="T90" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U90" s="8">
         <v>0.5</v>
@@ -8893,10 +8893,10 @@
         <v>0.5</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N91" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O91" s="8">
         <v>0.3</v>
@@ -8914,7 +8914,7 @@
         <v>62</v>
       </c>
       <c r="T91" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U91" s="8">
         <v>0.5</v>
@@ -8956,10 +8956,10 @@
         <v>0.5</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N92" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O92" s="8">
         <v>0.3</v>
@@ -9015,10 +9015,10 @@
         <v>0.5</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N93" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O93" s="8">
         <v>0.3</v>
@@ -9074,10 +9074,10 @@
         <v>0.5</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N94" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O94" s="8">
         <v>0.3</v>
@@ -9133,10 +9133,10 @@
         <v>0.5</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N95" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O95" s="8">
         <v>0.3</v>
@@ -9192,10 +9192,10 @@
         <v>0.5</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N96" s="8">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O96" s="8">
         <v>0.3</v>
@@ -9213,7 +9213,7 @@
         <v>62</v>
       </c>
       <c r="T96" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U96" s="8">
         <v>0.5</v>
@@ -9255,10 +9255,10 @@
         <v>0.5</v>
       </c>
       <c r="M97" s="13" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="N97" s="13">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O97" s="13">
         <v>0.35</v>
@@ -9314,10 +9314,10 @@
         <v>0.5</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N98" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O98" s="8">
         <v>0.35</v>
@@ -9373,10 +9373,10 @@
         <v>0.5</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N99" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O99" s="8">
         <v>0.35</v>
@@ -9432,10 +9432,10 @@
         <v>0.5</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N100" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O100" s="8">
         <v>0.35</v>
@@ -9491,10 +9491,10 @@
         <v>0.5</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N101" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O101" s="8">
         <v>0.35</v>
@@ -9548,10 +9548,10 @@
         <v>0.5</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N102" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O102" s="8">
         <v>0.35</v>
@@ -9607,10 +9607,10 @@
         <v>0.5</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N103" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O103" s="8">
         <v>0.35</v>
@@ -9628,7 +9628,7 @@
         <v>62</v>
       </c>
       <c r="T103" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U103" s="8">
         <v>0.5</v>
@@ -9670,10 +9670,10 @@
         <v>0.5</v>
       </c>
       <c r="M104" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N104" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O104" s="8">
         <v>0.35</v>
@@ -9729,10 +9729,10 @@
         <v>0.5</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N105" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O105" s="8">
         <v>0.35</v>
@@ -9788,10 +9788,10 @@
         <v>0.5</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N106" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O106" s="8">
         <v>0.35</v>
@@ -9847,10 +9847,10 @@
         <v>0.5</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N107" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O107" s="8">
         <v>0.35</v>
@@ -9906,10 +9906,10 @@
         <v>0.5</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N108" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O108" s="8">
         <v>0.35</v>
@@ -9965,10 +9965,10 @@
         <v>0.5</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N109" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O109" s="8">
         <v>0.35</v>
@@ -9986,7 +9986,7 @@
         <v>62</v>
       </c>
       <c r="T109" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U109" s="8">
         <v>0.5</v>
@@ -10028,10 +10028,10 @@
         <v>0.5</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N110" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O110" s="8">
         <v>0.35</v>
@@ -10087,10 +10087,10 @@
         <v>0.5</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N111" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O111" s="8">
         <v>0.35</v>
@@ -10108,7 +10108,7 @@
         <v>62</v>
       </c>
       <c r="T111" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U111" s="8">
         <v>0.5</v>
@@ -10150,10 +10150,10 @@
         <v>0.5</v>
       </c>
       <c r="M112" s="13" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="N112" s="13">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O112" s="13">
         <v>0.4</v>
@@ -10207,10 +10207,10 @@
         <v>0.5</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N113" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O113" s="8">
         <v>0.4</v>
@@ -10266,10 +10266,10 @@
         <v>0.5</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N114" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O114" s="8">
         <v>0.4</v>
@@ -10323,10 +10323,10 @@
         <v>0.5</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N115" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O115" s="8">
         <v>0.4</v>
@@ -10382,10 +10382,10 @@
         <v>0.5</v>
       </c>
       <c r="M116" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N116" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O116" s="8">
         <v>0.4</v>
@@ -10403,7 +10403,7 @@
         <v>62</v>
       </c>
       <c r="T116" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U116" s="8">
         <v>0.5</v>
@@ -10447,10 +10447,10 @@
         <v>0.5</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N117" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O117" s="8">
         <v>0.4</v>
@@ -10468,7 +10468,7 @@
         <v>62</v>
       </c>
       <c r="T117" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U117" s="8">
         <v>0.5</v>
@@ -10512,10 +10512,10 @@
         <v>0.5</v>
       </c>
       <c r="M118" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N118" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O118" s="8">
         <v>0.4</v>
@@ -10533,7 +10533,7 @@
         <v>62</v>
       </c>
       <c r="T118" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U118" s="8">
         <v>0.5</v>
@@ -10577,10 +10577,10 @@
         <v>0.5</v>
       </c>
       <c r="M119" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N119" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O119" s="8">
         <v>0.4</v>
@@ -10598,7 +10598,7 @@
         <v>62</v>
       </c>
       <c r="T119" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U119" s="8">
         <v>0.5</v>
@@ -10642,10 +10642,10 @@
         <v>0.5</v>
       </c>
       <c r="M120" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N120" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O120" s="8">
         <v>0.4</v>
@@ -10663,7 +10663,7 @@
         <v>62</v>
       </c>
       <c r="T120" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U120" s="8">
         <v>0.5</v>
@@ -10707,10 +10707,10 @@
         <v>0.5</v>
       </c>
       <c r="M121" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N121" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O121" s="8">
         <v>0.4</v>
@@ -10766,10 +10766,10 @@
         <v>0.5</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N122" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O122" s="8">
         <v>0.4</v>
@@ -10825,10 +10825,10 @@
         <v>0.5</v>
       </c>
       <c r="M123" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N123" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O123" s="8">
         <v>0.4</v>
@@ -10884,10 +10884,10 @@
         <v>0.5</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N124" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O124" s="8">
         <v>0.4</v>
@@ -10941,10 +10941,10 @@
         <v>0.5</v>
       </c>
       <c r="M125" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N125" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O125" s="8">
         <v>0.4</v>
@@ -11000,10 +11000,10 @@
         <v>0.5</v>
       </c>
       <c r="M126" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N126" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O126" s="8">
         <v>0.4</v>
@@ -11021,7 +11021,7 @@
         <v>62</v>
       </c>
       <c r="T126" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U126" s="8">
         <v>0.5</v>
@@ -11065,10 +11065,10 @@
         <v>0.5</v>
       </c>
       <c r="M127" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N127" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O127" s="8">
         <v>0.4</v>
@@ -11086,7 +11086,7 @@
         <v>62</v>
       </c>
       <c r="T127" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U127" s="8">
         <v>0.5</v>
@@ -11130,10 +11130,10 @@
         <v>0.5</v>
       </c>
       <c r="M128" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N128" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O128" s="8">
         <v>0.4</v>
@@ -11151,7 +11151,7 @@
         <v>62</v>
       </c>
       <c r="T128" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U128" s="8">
         <v>0.5</v>
@@ -11195,10 +11195,10 @@
         <v>0.5</v>
       </c>
       <c r="M129" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N129" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O129" s="8">
         <v>0.4</v>
@@ -11216,7 +11216,7 @@
         <v>62</v>
       </c>
       <c r="T129" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U129" s="8">
         <v>0.5</v>
@@ -11260,10 +11260,10 @@
         <v>0.5</v>
       </c>
       <c r="M130" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N130" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O130" s="8">
         <v>0.4</v>
@@ -11281,7 +11281,7 @@
         <v>62</v>
       </c>
       <c r="T130" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U130" s="8">
         <v>0.5</v>
@@ -11325,10 +11325,10 @@
         <v>0.5</v>
       </c>
       <c r="M131" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N131" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O131" s="8">
         <v>0.4</v>
@@ -11346,7 +11346,7 @@
         <v>62</v>
       </c>
       <c r="T131" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U131" s="8">
         <v>0.5</v>
@@ -11390,10 +11390,10 @@
         <v>0.5</v>
       </c>
       <c r="M132" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N132" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O132" s="8">
         <v>0.4</v>
@@ -11411,7 +11411,7 @@
         <v>62</v>
       </c>
       <c r="T132" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U132" s="8">
         <v>0.5</v>
@@ -11455,10 +11455,10 @@
         <v>0.5</v>
       </c>
       <c r="M133" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N133" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O133" s="8">
         <v>0.4</v>
@@ -11476,7 +11476,7 @@
         <v>62</v>
       </c>
       <c r="T133" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U133" s="8">
         <v>0.5</v>
@@ -11520,10 +11520,10 @@
         <v>0.5</v>
       </c>
       <c r="M134" s="13" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N134" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O134" s="13">
         <v>0.45</v>
@@ -11579,10 +11579,10 @@
         <v>0.5</v>
       </c>
       <c r="M135" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N135" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O135" s="8">
         <v>0.45</v>
@@ -11638,10 +11638,10 @@
         <v>0.5</v>
       </c>
       <c r="M136" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N136" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O136" s="8">
         <v>0.45</v>
@@ -11697,10 +11697,10 @@
         <v>0.5</v>
       </c>
       <c r="M137" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N137" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O137" s="8">
         <v>0.45</v>
@@ -11756,10 +11756,10 @@
         <v>0.5</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N138" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O138" s="8">
         <v>0.45</v>
@@ -11815,10 +11815,10 @@
         <v>0.5</v>
       </c>
       <c r="M139" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N139" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O139" s="8">
         <v>0.45</v>
@@ -11872,10 +11872,10 @@
         <v>0.5</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N140" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O140" s="8">
         <v>0.45</v>
@@ -11931,10 +11931,10 @@
         <v>0.5</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N141" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O141" s="8">
         <v>0.45</v>
@@ -11952,7 +11952,7 @@
         <v>62</v>
       </c>
       <c r="T141" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U141" s="8">
         <v>0.5</v>
@@ -11996,10 +11996,10 @@
         <v>0.5</v>
       </c>
       <c r="M142" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N142" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O142" s="8">
         <v>0.45</v>
@@ -12017,7 +12017,7 @@
         <v>62</v>
       </c>
       <c r="T142" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U142" s="8">
         <v>0.5</v>
@@ -12061,10 +12061,10 @@
         <v>0.5</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N143" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O143" s="8">
         <v>0.45</v>
@@ -12082,7 +12082,7 @@
         <v>62</v>
       </c>
       <c r="T143" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U143" s="8">
         <v>0.5</v>
@@ -12124,10 +12124,10 @@
         <v>0.5</v>
       </c>
       <c r="M144" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N144" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O144" s="8">
         <v>0.45</v>
@@ -12183,10 +12183,10 @@
         <v>0.5</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N145" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O145" s="8">
         <v>0.45</v>
@@ -12204,7 +12204,7 @@
         <v>62</v>
       </c>
       <c r="T145" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U145" s="8">
         <v>0.5</v>
@@ -12248,10 +12248,10 @@
         <v>0.5</v>
       </c>
       <c r="M146" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N146" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O146" s="8">
         <v>0.45</v>
@@ -12269,7 +12269,7 @@
         <v>62</v>
       </c>
       <c r="T146" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U146" s="8">
         <v>0.5</v>
@@ -12313,10 +12313,10 @@
         <v>0.5</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N147" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O147" s="8">
         <v>0.45</v>
@@ -12334,7 +12334,7 @@
         <v>62</v>
       </c>
       <c r="T147" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U147" s="8">
         <v>0.5</v>
@@ -12376,10 +12376,10 @@
         <v>0.5</v>
       </c>
       <c r="M148" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N148" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O148" s="8">
         <v>0.45</v>
@@ -12435,10 +12435,10 @@
         <v>0.5</v>
       </c>
       <c r="M149" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N149" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O149" s="8">
         <v>0.45</v>
@@ -12456,7 +12456,7 @@
         <v>62</v>
       </c>
       <c r="T149" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U149" s="8">
         <v>0.5</v>
@@ -12500,10 +12500,10 @@
         <v>0.5</v>
       </c>
       <c r="M150" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N150" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O150" s="8">
         <v>0.45</v>
@@ -12521,7 +12521,7 @@
         <v>62</v>
       </c>
       <c r="T150" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U150" s="8">
         <v>0.5</v>
@@ -12565,10 +12565,10 @@
         <v>0.5</v>
       </c>
       <c r="M151" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N151" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O151" s="8">
         <v>0.45</v>
@@ -12586,7 +12586,7 @@
         <v>62</v>
       </c>
       <c r="T151" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U151" s="8">
         <v>0.5</v>
@@ -12630,10 +12630,10 @@
         <v>0.5</v>
       </c>
       <c r="M152" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N152" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O152" s="8">
         <v>0.45</v>
@@ -12651,7 +12651,7 @@
         <v>62</v>
       </c>
       <c r="T152" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U152" s="8">
         <v>0.5</v>
@@ -12662,7 +12662,7 @@
         <v>143</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C153" s="8">
         <v>56</v>
@@ -12695,10 +12695,10 @@
         <v>0.5</v>
       </c>
       <c r="M153" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N153" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O153" s="8">
         <v>0.45</v>
@@ -12716,7 +12716,7 @@
         <v>62</v>
       </c>
       <c r="T153" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U153" s="8">
         <v>0.5</v>
@@ -12727,7 +12727,7 @@
         <v>143</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C154" s="8">
         <v>57</v>
@@ -12760,10 +12760,10 @@
         <v>0.5</v>
       </c>
       <c r="M154" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N154" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O154" s="8">
         <v>0.45</v>
@@ -12781,7 +12781,7 @@
         <v>62</v>
       </c>
       <c r="T154" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="U154" s="8">
         <v>0.5</v>
@@ -12823,7 +12823,7 @@
         <v>0.5</v>
       </c>
       <c r="M155" s="13" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="N155" s="13">
         <v>11</v>
@@ -12880,7 +12880,7 @@
         <v>0.5</v>
       </c>
       <c r="M156" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N156" s="8">
         <v>11</v>
@@ -12937,7 +12937,7 @@
         <v>0.5</v>
       </c>
       <c r="M157" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N157" s="8">
         <v>11</v>
@@ -12994,7 +12994,7 @@
         <v>0.5</v>
       </c>
       <c r="M158" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N158" s="8">
         <v>11</v>
@@ -13051,7 +13051,7 @@
         <v>0.5</v>
       </c>
       <c r="M159" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N159" s="8">
         <v>11</v>
@@ -13108,7 +13108,7 @@
         <v>0.5</v>
       </c>
       <c r="M160" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N160" s="8">
         <v>11</v>
@@ -13165,7 +13165,7 @@
         <v>0.5</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N161" s="8">
         <v>11</v>
@@ -13222,7 +13222,7 @@
         <v>0.5</v>
       </c>
       <c r="M162" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N162" s="8">
         <v>11</v>
@@ -13279,7 +13279,7 @@
         <v>0.5</v>
       </c>
       <c r="M163" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N163" s="8">
         <v>11</v>
@@ -13336,7 +13336,7 @@
         <v>0.5</v>
       </c>
       <c r="M164" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N164" s="8">
         <v>11</v>
@@ -13393,7 +13393,7 @@
         <v>0.5</v>
       </c>
       <c r="M165" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N165" s="8">
         <v>11</v>
@@ -13450,7 +13450,7 @@
         <v>0.5</v>
       </c>
       <c r="M166" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N166" s="8">
         <v>11</v>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2723A3-0B13-4B41-99AE-3DF3B35F8671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C858BB1-D47B-40BE-ACAE-A583277CA46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="552" windowWidth="17280" windowHeight="11304" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="3720" yWindow="3576" windowWidth="20316" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
     <sheet name="ImportData" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="175">
   <si>
     <t>Wave1</t>
   </si>
@@ -1515,13 +1515,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:2.7:0;ATK:1.7:0,Speed:0.15:0,DashSpeed:1.5:0</t>
-  </si>
-  <si>
-    <t>MaxHP:2.7:0;ATK:1.7:0,Speed:0.15:0,DashSpeed:1.5:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MaxHP:3.0:0;ATK:1.8:0,Speed:1.55:0,DashSpeed:1.55:0</t>
   </si>
   <si>
@@ -1575,6 +1568,10 @@
   </si>
   <si>
     <t>MaxHP:1.9:20;ATK:1.4:0,Speed:0.2:0,DashSpeed:0.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.7:30;ATK:1.7:0,Speed:0.15:0,DashSpeed:1.5:0</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4224,7 +4221,7 @@
         <v>62</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U13" s="10">
         <v>0.5</v>
@@ -4266,7 +4263,7 @@
         <v>0.5</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N14" s="13">
         <v>2</v>
@@ -4323,7 +4320,7 @@
         <v>0.5</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N15" s="8">
         <v>2</v>
@@ -4382,7 +4379,7 @@
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N16" s="8">
         <v>2</v>
@@ -4441,7 +4438,7 @@
         <v>0.5</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N17" s="8">
         <v>2</v>
@@ -4498,7 +4495,7 @@
         <v>0.5</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N18" s="8">
         <v>2</v>
@@ -4557,7 +4554,7 @@
         <v>0.5</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N19" s="8">
         <v>2</v>
@@ -4578,7 +4575,7 @@
         <v>62</v>
       </c>
       <c r="T19" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U19" s="8">
         <v>0.5</v>
@@ -4622,7 +4619,7 @@
         <v>0.5</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N20" s="8">
         <v>2</v>
@@ -4681,7 +4678,7 @@
         <v>0.5</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N21" s="8">
         <v>2</v>
@@ -4738,7 +4735,7 @@
         <v>0.5</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N22" s="8">
         <v>2</v>
@@ -4797,7 +4794,7 @@
         <v>0.5</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N23" s="10">
         <v>2</v>
@@ -4809,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="10" t="s">
         <v>61</v>
@@ -4818,7 +4815,7 @@
         <v>62</v>
       </c>
       <c r="T23" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U23" s="10">
         <v>0.5</v>
@@ -4860,7 +4857,7 @@
         <v>0.5</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N24" s="13">
         <v>5</v>
@@ -4917,7 +4914,7 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N25" s="8">
         <v>5</v>
@@ -4974,7 +4971,7 @@
         <v>0.5</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N26" s="8">
         <v>5</v>
@@ -5033,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N27" s="8">
         <v>5</v>
@@ -5054,7 +5051,7 @@
         <v>62</v>
       </c>
       <c r="T27" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U27" s="8">
         <v>0.5</v>
@@ -5098,7 +5095,7 @@
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N28" s="8">
         <v>5</v>
@@ -5157,7 +5154,7 @@
         <v>0.5</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N29" s="8">
         <v>5</v>
@@ -5214,7 +5211,7 @@
         <v>0.5</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N30" s="8">
         <v>5</v>
@@ -5273,7 +5270,7 @@
         <v>0.5</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N31" s="8">
         <v>5</v>
@@ -5332,7 +5329,7 @@
         <v>0.5</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N32" s="8">
         <v>5</v>
@@ -5389,7 +5386,7 @@
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N33" s="8">
         <v>5</v>
@@ -5446,7 +5443,7 @@
         <v>0.5</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N34" s="8">
         <v>5</v>
@@ -5503,7 +5500,7 @@
         <v>0.5</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N35" s="8">
         <v>5</v>
@@ -5562,7 +5559,7 @@
         <v>0.5</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N36" s="8">
         <v>5</v>
@@ -5583,7 +5580,7 @@
         <v>62</v>
       </c>
       <c r="T36" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U36" s="8">
         <v>0.5</v>
@@ -5625,7 +5622,7 @@
         <v>0.5</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N37" s="13">
         <v>10</v>
@@ -5684,7 +5681,7 @@
         <v>0.5</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N38" s="8">
         <v>10</v>
@@ -5705,7 +5702,7 @@
         <v>62</v>
       </c>
       <c r="T38" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U38" s="8">
         <v>0.5</v>
@@ -5749,7 +5746,7 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N39" s="8">
         <v>10</v>
@@ -5770,7 +5767,7 @@
         <v>62</v>
       </c>
       <c r="T39" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U39" s="8">
         <v>0.5</v>
@@ -5814,7 +5811,7 @@
         <v>0.5</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N40" s="8">
         <v>10</v>
@@ -5835,7 +5832,7 @@
         <v>62</v>
       </c>
       <c r="T40" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U40" s="8">
         <v>0.5</v>
@@ -5879,7 +5876,7 @@
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N41" s="8">
         <v>10</v>
@@ -5938,7 +5935,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N42" s="8">
         <v>10</v>
@@ -5997,7 +5994,7 @@
         <v>0.5</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N43" s="8">
         <v>10</v>
@@ -6018,7 +6015,7 @@
         <v>62</v>
       </c>
       <c r="T43" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U43" s="8">
         <v>0.5</v>
@@ -6060,7 +6057,7 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N44" s="8">
         <v>10</v>
@@ -6117,7 +6114,7 @@
         <v>0.5</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N45" s="8">
         <v>10</v>
@@ -6174,7 +6171,7 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N46" s="8">
         <v>10</v>
@@ -6233,7 +6230,7 @@
         <v>0.5</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N47" s="8">
         <v>10</v>
@@ -6254,7 +6251,7 @@
         <v>62</v>
       </c>
       <c r="T47" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U47" s="8">
         <v>0.5</v>
@@ -6298,7 +6295,7 @@
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N48" s="8">
         <v>10</v>
@@ -6357,7 +6354,7 @@
         <v>0.5</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N49" s="8">
         <v>10</v>
@@ -6416,7 +6413,7 @@
         <v>0.5</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N50" s="8">
         <v>10</v>
@@ -6428,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="10" t="s">
         <v>61</v>
@@ -6437,7 +6434,7 @@
         <v>62</v>
       </c>
       <c r="T50" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U50" s="8">
         <v>0.5</v>
@@ -6559,7 +6556,7 @@
         <v>62</v>
       </c>
       <c r="T52" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U52" s="8">
         <v>0.5</v>
@@ -6681,7 +6678,7 @@
         <v>62</v>
       </c>
       <c r="T54" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U54" s="8">
         <v>0.5</v>
@@ -6864,7 +6861,7 @@
         <v>62</v>
       </c>
       <c r="T57" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U57" s="8">
         <v>0.5</v>
@@ -7104,7 +7101,7 @@
         <v>62</v>
       </c>
       <c r="T61" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U61" s="8">
         <v>0.5</v>
@@ -7169,7 +7166,7 @@
         <v>62</v>
       </c>
       <c r="T62" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U62" s="8">
         <v>0.5</v>
@@ -7291,7 +7288,7 @@
         <v>62</v>
       </c>
       <c r="T64" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U64" s="8">
         <v>0.5</v>
@@ -7356,7 +7353,7 @@
         <v>62</v>
       </c>
       <c r="T65" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U65" s="8">
         <v>0.5</v>
@@ -7535,7 +7532,7 @@
         <v>62</v>
       </c>
       <c r="T68" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U68" s="8">
         <v>0.5</v>
@@ -8007,7 +8004,7 @@
         <v>62</v>
       </c>
       <c r="T76" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U76" s="8">
         <v>0.5</v>
@@ -8299,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="10" t="s">
         <v>61</v>
@@ -8308,7 +8305,7 @@
         <v>62</v>
       </c>
       <c r="T81" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U81" s="8">
         <v>0.5</v>
@@ -8364,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="10" t="s">
         <v>61</v>
@@ -8373,7 +8370,7 @@
         <v>62</v>
       </c>
       <c r="T82" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U82" s="8">
         <v>0.5</v>
@@ -8531,7 +8528,7 @@
         <v>0.5</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="N85" s="8">
         <v>27</v>
@@ -8552,7 +8549,7 @@
         <v>62</v>
       </c>
       <c r="T85" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U85" s="8">
         <v>0.5</v>
@@ -8849,7 +8846,7 @@
         <v>62</v>
       </c>
       <c r="T90" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U90" s="8">
         <v>0.5</v>
@@ -8893,7 +8890,7 @@
         <v>0.5</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="N91" s="8">
         <v>27</v>
@@ -8914,7 +8911,7 @@
         <v>62</v>
       </c>
       <c r="T91" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U91" s="8">
         <v>0.5</v>
@@ -9213,7 +9210,7 @@
         <v>62</v>
       </c>
       <c r="T96" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U96" s="8">
         <v>0.5</v>
@@ -9255,7 +9252,7 @@
         <v>0.5</v>
       </c>
       <c r="M97" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N97" s="13">
         <v>31</v>
@@ -9314,7 +9311,7 @@
         <v>0.5</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N98" s="8">
         <v>31</v>
@@ -9373,7 +9370,7 @@
         <v>0.5</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N99" s="8">
         <v>31</v>
@@ -9432,7 +9429,7 @@
         <v>0.5</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N100" s="8">
         <v>31</v>
@@ -9491,7 +9488,7 @@
         <v>0.5</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N101" s="8">
         <v>31</v>
@@ -9548,7 +9545,7 @@
         <v>0.5</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N102" s="8">
         <v>31</v>
@@ -9607,7 +9604,7 @@
         <v>0.5</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N103" s="8">
         <v>31</v>
@@ -9628,7 +9625,7 @@
         <v>62</v>
       </c>
       <c r="T103" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U103" s="8">
         <v>0.5</v>
@@ -9670,7 +9667,7 @@
         <v>0.5</v>
       </c>
       <c r="M104" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N104" s="8">
         <v>31</v>
@@ -9729,7 +9726,7 @@
         <v>0.5</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N105" s="8">
         <v>31</v>
@@ -9788,7 +9785,7 @@
         <v>0.5</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N106" s="8">
         <v>31</v>
@@ -9847,7 +9844,7 @@
         <v>0.5</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N107" s="8">
         <v>31</v>
@@ -9906,7 +9903,7 @@
         <v>0.5</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N108" s="8">
         <v>31</v>
@@ -9965,7 +9962,7 @@
         <v>0.5</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N109" s="8">
         <v>31</v>
@@ -9986,7 +9983,7 @@
         <v>62</v>
       </c>
       <c r="T109" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U109" s="8">
         <v>0.5</v>
@@ -10028,7 +10025,7 @@
         <v>0.5</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N110" s="8">
         <v>31</v>
@@ -10087,7 +10084,7 @@
         <v>0.5</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N111" s="8">
         <v>31</v>
@@ -10099,7 +10096,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="10" t="s">
         <v>61</v>
@@ -10108,7 +10105,7 @@
         <v>62</v>
       </c>
       <c r="T111" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U111" s="8">
         <v>0.5</v>
@@ -10150,7 +10147,7 @@
         <v>0.5</v>
       </c>
       <c r="M112" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N112" s="13">
         <v>35</v>
@@ -10207,7 +10204,7 @@
         <v>0.5</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N113" s="8">
         <v>35</v>
@@ -10260,13 +10257,13 @@
         <v>0</v>
       </c>
       <c r="K114" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="8">
         <v>0.5</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N114" s="8">
         <v>35</v>
@@ -10280,9 +10277,15 @@
       <c r="Q114" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="R114" s="10"/>
-      <c r="S114" s="10"/>
-      <c r="T114" s="18"/>
+      <c r="R114" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S114" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T114" s="18" t="s">
+        <v>168</v>
+      </c>
       <c r="U114" s="8">
         <v>0.5</v>
       </c>
@@ -10323,7 +10326,7 @@
         <v>0.5</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N115" s="8">
         <v>35</v>
@@ -10382,7 +10385,7 @@
         <v>0.5</v>
       </c>
       <c r="M116" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N116" s="8">
         <v>35</v>
@@ -10403,7 +10406,7 @@
         <v>62</v>
       </c>
       <c r="T116" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U116" s="8">
         <v>0.5</v>
@@ -10447,7 +10450,7 @@
         <v>0.5</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N117" s="8">
         <v>35</v>
@@ -10468,7 +10471,7 @@
         <v>62</v>
       </c>
       <c r="T117" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U117" s="8">
         <v>0.5</v>
@@ -10512,7 +10515,7 @@
         <v>0.5</v>
       </c>
       <c r="M118" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N118" s="8">
         <v>35</v>
@@ -10533,7 +10536,7 @@
         <v>62</v>
       </c>
       <c r="T118" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U118" s="8">
         <v>0.5</v>
@@ -10577,7 +10580,7 @@
         <v>0.5</v>
       </c>
       <c r="M119" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N119" s="8">
         <v>35</v>
@@ -10598,7 +10601,7 @@
         <v>62</v>
       </c>
       <c r="T119" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U119" s="8">
         <v>0.5</v>
@@ -10642,7 +10645,7 @@
         <v>0.5</v>
       </c>
       <c r="M120" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N120" s="8">
         <v>35</v>
@@ -10663,7 +10666,7 @@
         <v>62</v>
       </c>
       <c r="T120" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U120" s="8">
         <v>0.5</v>
@@ -10707,7 +10710,7 @@
         <v>0.5</v>
       </c>
       <c r="M121" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N121" s="8">
         <v>35</v>
@@ -10766,7 +10769,7 @@
         <v>0.5</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N122" s="8">
         <v>35</v>
@@ -10825,7 +10828,7 @@
         <v>0.5</v>
       </c>
       <c r="M123" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N123" s="8">
         <v>35</v>
@@ -10884,7 +10887,7 @@
         <v>0.5</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N124" s="8">
         <v>35</v>
@@ -10941,7 +10944,7 @@
         <v>0.5</v>
       </c>
       <c r="M125" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N125" s="8">
         <v>35</v>
@@ -11000,7 +11003,7 @@
         <v>0.5</v>
       </c>
       <c r="M126" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N126" s="8">
         <v>35</v>
@@ -11021,7 +11024,7 @@
         <v>62</v>
       </c>
       <c r="T126" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U126" s="8">
         <v>0.5</v>
@@ -11065,7 +11068,7 @@
         <v>0.5</v>
       </c>
       <c r="M127" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N127" s="8">
         <v>35</v>
@@ -11086,7 +11089,7 @@
         <v>62</v>
       </c>
       <c r="T127" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U127" s="8">
         <v>0.5</v>
@@ -11130,7 +11133,7 @@
         <v>0.5</v>
       </c>
       <c r="M128" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N128" s="8">
         <v>35</v>
@@ -11151,7 +11154,7 @@
         <v>62</v>
       </c>
       <c r="T128" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U128" s="8">
         <v>0.5</v>
@@ -11195,7 +11198,7 @@
         <v>0.5</v>
       </c>
       <c r="M129" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N129" s="8">
         <v>35</v>
@@ -11216,7 +11219,7 @@
         <v>62</v>
       </c>
       <c r="T129" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U129" s="8">
         <v>0.5</v>
@@ -11260,7 +11263,7 @@
         <v>0.5</v>
       </c>
       <c r="M130" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N130" s="8">
         <v>35</v>
@@ -11281,7 +11284,7 @@
         <v>62</v>
       </c>
       <c r="T130" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U130" s="8">
         <v>0.5</v>
@@ -11325,7 +11328,7 @@
         <v>0.5</v>
       </c>
       <c r="M131" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N131" s="8">
         <v>35</v>
@@ -11346,7 +11349,7 @@
         <v>62</v>
       </c>
       <c r="T131" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U131" s="8">
         <v>0.5</v>
@@ -11390,7 +11393,7 @@
         <v>0.5</v>
       </c>
       <c r="M132" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N132" s="8">
         <v>35</v>
@@ -11411,7 +11414,7 @@
         <v>62</v>
       </c>
       <c r="T132" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U132" s="8">
         <v>0.5</v>
@@ -11455,7 +11458,7 @@
         <v>0.5</v>
       </c>
       <c r="M133" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N133" s="8">
         <v>35</v>
@@ -11476,7 +11479,7 @@
         <v>62</v>
       </c>
       <c r="T133" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U133" s="8">
         <v>0.5</v>
@@ -11520,7 +11523,7 @@
         <v>0.5</v>
       </c>
       <c r="M134" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N134" s="13">
         <v>40</v>
@@ -11579,7 +11582,7 @@
         <v>0.5</v>
       </c>
       <c r="M135" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N135" s="8">
         <v>40</v>
@@ -11638,7 +11641,7 @@
         <v>0.5</v>
       </c>
       <c r="M136" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N136" s="8">
         <v>40</v>
@@ -11697,7 +11700,7 @@
         <v>0.5</v>
       </c>
       <c r="M137" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N137" s="8">
         <v>40</v>
@@ -11756,7 +11759,7 @@
         <v>0.5</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N138" s="8">
         <v>40</v>
@@ -11815,7 +11818,7 @@
         <v>0.5</v>
       </c>
       <c r="M139" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N139" s="8">
         <v>40</v>
@@ -11872,7 +11875,7 @@
         <v>0.5</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N140" s="8">
         <v>40</v>
@@ -11931,7 +11934,7 @@
         <v>0.5</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N141" s="8">
         <v>40</v>
@@ -11952,7 +11955,7 @@
         <v>62</v>
       </c>
       <c r="T141" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U141" s="8">
         <v>0.5</v>
@@ -11996,7 +11999,7 @@
         <v>0.5</v>
       </c>
       <c r="M142" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N142" s="8">
         <v>40</v>
@@ -12017,7 +12020,7 @@
         <v>62</v>
       </c>
       <c r="T142" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U142" s="8">
         <v>0.5</v>
@@ -12061,7 +12064,7 @@
         <v>0.5</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N143" s="8">
         <v>40</v>
@@ -12082,7 +12085,7 @@
         <v>62</v>
       </c>
       <c r="T143" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U143" s="8">
         <v>0.5</v>
@@ -12124,7 +12127,7 @@
         <v>0.5</v>
       </c>
       <c r="M144" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N144" s="8">
         <v>40</v>
@@ -12183,7 +12186,7 @@
         <v>0.5</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N145" s="8">
         <v>40</v>
@@ -12204,7 +12207,7 @@
         <v>62</v>
       </c>
       <c r="T145" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U145" s="8">
         <v>0.5</v>
@@ -12248,7 +12251,7 @@
         <v>0.5</v>
       </c>
       <c r="M146" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N146" s="8">
         <v>40</v>
@@ -12269,7 +12272,7 @@
         <v>62</v>
       </c>
       <c r="T146" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U146" s="8">
         <v>0.5</v>
@@ -12313,7 +12316,7 @@
         <v>0.5</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N147" s="8">
         <v>40</v>
@@ -12334,7 +12337,7 @@
         <v>62</v>
       </c>
       <c r="T147" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U147" s="8">
         <v>0.5</v>
@@ -12376,7 +12379,7 @@
         <v>0.5</v>
       </c>
       <c r="M148" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N148" s="8">
         <v>40</v>
@@ -12435,7 +12438,7 @@
         <v>0.5</v>
       </c>
       <c r="M149" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N149" s="8">
         <v>40</v>
@@ -12456,7 +12459,7 @@
         <v>62</v>
       </c>
       <c r="T149" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U149" s="8">
         <v>0.5</v>
@@ -12500,7 +12503,7 @@
         <v>0.5</v>
       </c>
       <c r="M150" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N150" s="8">
         <v>40</v>
@@ -12521,7 +12524,7 @@
         <v>62</v>
       </c>
       <c r="T150" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U150" s="8">
         <v>0.5</v>
@@ -12565,7 +12568,7 @@
         <v>0.5</v>
       </c>
       <c r="M151" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N151" s="8">
         <v>40</v>
@@ -12586,7 +12589,7 @@
         <v>62</v>
       </c>
       <c r="T151" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U151" s="8">
         <v>0.5</v>
@@ -12630,7 +12633,7 @@
         <v>0.5</v>
       </c>
       <c r="M152" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N152" s="8">
         <v>40</v>
@@ -12651,7 +12654,7 @@
         <v>62</v>
       </c>
       <c r="T152" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U152" s="8">
         <v>0.5</v>
@@ -12695,7 +12698,7 @@
         <v>0.5</v>
       </c>
       <c r="M153" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N153" s="8">
         <v>40</v>
@@ -12716,7 +12719,7 @@
         <v>62</v>
       </c>
       <c r="T153" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U153" s="8">
         <v>0.5</v>
@@ -12760,7 +12763,7 @@
         <v>0.5</v>
       </c>
       <c r="M154" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N154" s="8">
         <v>40</v>
@@ -12781,7 +12784,7 @@
         <v>62</v>
       </c>
       <c r="T154" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="U154" s="8">
         <v>0.5</v>
@@ -12823,7 +12826,7 @@
         <v>0.5</v>
       </c>
       <c r="M155" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N155" s="13">
         <v>11</v>
@@ -12880,7 +12883,7 @@
         <v>0.5</v>
       </c>
       <c r="M156" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N156" s="8">
         <v>11</v>
@@ -12937,7 +12940,7 @@
         <v>0.5</v>
       </c>
       <c r="M157" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N157" s="8">
         <v>11</v>
@@ -12994,7 +12997,7 @@
         <v>0.5</v>
       </c>
       <c r="M158" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N158" s="8">
         <v>11</v>
@@ -13051,7 +13054,7 @@
         <v>0.5</v>
       </c>
       <c r="M159" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N159" s="8">
         <v>11</v>
@@ -13108,7 +13111,7 @@
         <v>0.5</v>
       </c>
       <c r="M160" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N160" s="8">
         <v>11</v>
@@ -13165,7 +13168,7 @@
         <v>0.5</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N161" s="8">
         <v>11</v>
@@ -13222,7 +13225,7 @@
         <v>0.5</v>
       </c>
       <c r="M162" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N162" s="8">
         <v>11</v>
@@ -13279,7 +13282,7 @@
         <v>0.5</v>
       </c>
       <c r="M163" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N163" s="8">
         <v>11</v>
@@ -13336,7 +13339,7 @@
         <v>0.5</v>
       </c>
       <c r="M164" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N164" s="8">
         <v>11</v>
@@ -13393,7 +13396,7 @@
         <v>0.5</v>
       </c>
       <c r="M165" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N165" s="8">
         <v>11</v>
@@ -13450,7 +13453,7 @@
         <v>0.5</v>
       </c>
       <c r="M166" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N166" s="8">
         <v>11</v>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C858BB1-D47B-40BE-ACAE-A583277CA46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F91CB8-4DC5-47AF-B41E-0FA55B55EC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3576" windowWidth="20316" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="2172" yWindow="3360" windowWidth="20316" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
-    <sheet name="ImportData" sheetId="1" r:id="rId1"/>
-    <sheet name="TestData" sheetId="4" r:id="rId2"/>
-    <sheet name="explanation" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="NormalStageData" sheetId="1" r:id="rId1"/>
+    <sheet name="EasyStageData" sheetId="7" r:id="rId2"/>
+    <sheet name="TestData" sheetId="4" r:id="rId3"/>
+    <sheet name="explanation" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,8 +184,106 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FC81FF9B-90B6-4E03-822A-9BC3975768B5}</author>
+    <author>tc={25DFC095-6A3D-4639-BDEB-134D419DCB4D}</author>
+    <author>tc={BE582D0A-E43B-49CB-8B5C-34A82C93C04C}</author>
+    <author>tc={AE6B5070-5ADF-42A9-A512-897979CEC8E9}</author>
+    <author>tc={3B2AF2D6-1724-493B-BDB8-4780437F1B45}</author>
+    <author>tc={7DCD97E7-946D-4DC2-927D-DD4944279AF3}</author>
+    <author>tc={6F3450AD-FE27-4F77-B832-066935E74F4F}</author>
+    <author>tc={E2B05461-19B5-4813-A9EC-4AAAD75173F5}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{FC81FF9B-90B6-4E03-822A-9BC3975768B5}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave1
+ノーマルの動きを知ってもらう。
+最初なので生成数は少なめを意識。</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="1" shapeId="0" xr:uid="{25DFC095-6A3D-4639-BDEB-134D419DCB4D}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave２
+Wave１より出現数を増やす。
+まだノーマルのみでゲームに慣れさせる。
+生成法則でバリエーションを増やす。
+ボスを2Waveごとに出現させる。</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="2" shapeId="0" xr:uid="{BE582D0A-E43B-49CB-8B5C-34A82C93C04C}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave３
+スナイパーの動きを知ってもらう。
+ノーマルの生成を減らす。</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="3" shapeId="0" xr:uid="{AE6B5070-5ADF-42A9-A512-897979CEC8E9}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇EasyWave４
+タンクを初出現させる。
+ノーマルを多めに生成し、
+スナイパーの数を減らす。</t>
+      </text>
+    </comment>
+    <comment ref="A42" authorId="4" shapeId="0" xr:uid="{3B2AF2D6-1724-493B-BDB8-4780437F1B45}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</t>
+      </text>
+    </comment>
+    <comment ref="A50" authorId="5" shapeId="0" xr:uid="{7DCD97E7-946D-4DC2-927D-DD4944279AF3}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇Wave５
+スナイパーをより多く出現させる。
+弾幕の中を移動する方法を探らせる。</t>
+      </text>
+    </comment>
+    <comment ref="A54" authorId="6" shapeId="0" xr:uid="{6F3450AD-FE27-4F77-B832-066935E74F4F}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</t>
+      </text>
+    </comment>
+    <comment ref="A66" authorId="7" shapeId="0" xr:uid="{E2B05461-19B5-4813-A9EC-4AAAD75173F5}">
+      <text>
+        <t xml:space="preserve">[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇EndlessWave１
+N：S：Tの順で交互に敵を生成
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="203">
   <si>
     <t>Wave1</t>
   </si>
@@ -1572,6 +1671,104 @@
   </si>
   <si>
     <t>MaxHP:2.7:30;ATK:1.7:0,Speed:0.15:0,DashSpeed:1.5:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Enemy_Normal_Comp</t>
+  </si>
+  <si>
+    <t>Enemy_Sniper_Comp</t>
+  </si>
+  <si>
+    <t>EasyWave1</t>
+  </si>
+  <si>
+    <t>EasyWave1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EasyWave2</t>
+  </si>
+  <si>
+    <t>EasyWave2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EasyWave3</t>
+  </si>
+  <si>
+    <t>EasyWave3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EasyWave4</t>
+  </si>
+  <si>
+    <t>EasyWave4</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EasyWave5</t>
+  </si>
+  <si>
+    <t>EasyWave5</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EasyEndlessWave1</t>
+  </si>
+  <si>
+    <t>EasyEndlessWave1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:1.5:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+  </si>
+  <si>
+    <t>MaxHP:2.0:0;ATK:1.5:0,Speed:1.5:0,DashSpeed:1.5:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.4:0;ATK:1.3:0,Speed:1.2:0,DashSpeed:1.2:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.4:0;ATK:1.3:0,Speed:1.2:0,DashSpeed:1.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.6:0;ATK:1.3:5,Speed:1.3:0,DashSpeed:1.3:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.6:0;ATK:1.3:5,Speed:1.3:0,DashSpeed:1.3:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.8:0;ATK:1.5:0,Speed:1.4:0,DashSpeed:1.4:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.8:0;ATK:1.5:0,Speed:1.4:0,DashSpeed:1.4:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.6:0;ATK:1.4:0,Speed:1.3:0,DashSpeed:1.3:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.6:0;ATK:1.4:0,Speed:1.3:0,DashSpeed:1.3:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Boss_Normal_Comp</t>
+  </si>
+  <si>
+    <t>radiusx:12;radiusy:9</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.0:20;ATK:1.5:0,Speed:0.2:0,DashSpeed:0.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:18;sizey:14</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3436,6 +3633,52 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2026-02-09T05:45:06.73" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{FC81FF9B-90B6-4E03-822A-9BC3975768B5}">
+    <text>〇Wave1
+ノーマルの動きを知ってもらう。
+最初なので生成数は少なめを意識。</text>
+  </threadedComment>
+  <threadedComment ref="A14" dT="2026-02-09T05:44:23.57" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{25DFC095-6A3D-4639-BDEB-134D419DCB4D}">
+    <text>〇Wave２
+Wave１より出現数を増やす。
+まだノーマルのみでゲームに慣れさせる。
+生成法則でバリエーションを増やす。
+ボスを2Waveごとに出現させる。</text>
+  </threadedComment>
+  <threadedComment ref="A24" dT="2026-02-09T05:43:11.55" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{BE582D0A-E43B-49CB-8B5C-34A82C93C04C}">
+    <text>〇Wave３
+スナイパーの動きを知ってもらう。
+ノーマルの生成を減らす。</text>
+  </threadedComment>
+  <threadedComment ref="A37" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{AE6B5070-5ADF-42A9-A512-897979CEC8E9}">
+    <text>〇EasyWave４
+タンクを初出現させる。
+ノーマルを多めに生成し、
+スナイパーの数を減らす。</text>
+  </threadedComment>
+  <threadedComment ref="A42" dT="2026-02-09T06:02:10.44" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{3B2AF2D6-1724-493B-BDB8-4780437F1B45}">
+    <text>囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</text>
+  </threadedComment>
+  <threadedComment ref="A50" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{7DCD97E7-946D-4DC2-927D-DD4944279AF3}">
+    <text>〇Wave５
+スナイパーをより多く出現させる。
+弾幕の中を移動する方法を探らせる。</text>
+  </threadedComment>
+  <threadedComment ref="A54" dT="2026-02-09T06:02:10.44" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{6F3450AD-FE27-4F77-B832-066935E74F4F}">
+    <text>囲むように出現させ、ゆっくり移動させる。
+（ジャンプを催促する意図）</text>
+  </threadedComment>
+  <threadedComment ref="A66" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{E2B05461-19B5-4813-A9EC-4AAAD75173F5}">
+    <text xml:space="preserve">〇EndlessWave１
+N：S：Tの順で交互に敵を生成
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
   <dimension ref="A1:U166"/>
@@ -13490,6 +13733,4278 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB32428D-2178-44C9-8E3D-FF560DE0051D}">
+  <dimension ref="A1:U71"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" customWidth="1"/>
+    <col min="5" max="5" width="27.19921875" customWidth="1"/>
+    <col min="6" max="6" width="23.59765625" customWidth="1"/>
+    <col min="7" max="7" width="35.796875" customWidth="1"/>
+    <col min="8" max="9" width="15.19921875" customWidth="1"/>
+    <col min="10" max="10" width="20.59765625" customWidth="1"/>
+    <col min="11" max="11" width="16.3984375" customWidth="1"/>
+    <col min="12" max="12" width="24.796875" customWidth="1"/>
+    <col min="13" max="13" width="63.19921875" customWidth="1"/>
+    <col min="14" max="14" width="24.796875" customWidth="1"/>
+    <col min="15" max="15" width="26.5" customWidth="1"/>
+    <col min="16" max="16" width="16.796875" customWidth="1"/>
+    <col min="17" max="17" width="16.19921875" customWidth="1"/>
+    <col min="18" max="19" width="24.59765625" customWidth="1"/>
+    <col min="20" max="20" width="25.796875" customWidth="1"/>
+    <col min="21" max="21" width="27.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>5</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>15</v>
+      </c>
+      <c r="D5" s="8">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>25</v>
+      </c>
+      <c r="D7" s="8">
+        <v>5</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <v>30</v>
+      </c>
+      <c r="D8" s="8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8">
+        <v>5</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>40</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8">
+        <v>45</v>
+      </c>
+      <c r="D11" s="8">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8">
+        <v>50</v>
+      </c>
+      <c r="D12" s="10">
+        <v>5</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8">
+        <v>2</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10">
+        <v>55</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13" s="10">
+        <v>5</v>
+      </c>
+      <c r="I13" s="10">
+        <v>5</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>1</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
+        <v>15</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13">
+        <v>1</v>
+      </c>
+      <c r="I14" s="13">
+        <v>1</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="N14" s="13">
+        <v>2</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10">
+        <v>5</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="N15" s="8">
+        <v>2</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A16" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="8">
+        <v>10</v>
+      </c>
+      <c r="D16" s="10">
+        <v>3</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N16" s="8">
+        <v>2</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A17" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="8">
+        <v>10</v>
+      </c>
+      <c r="D17" s="10">
+        <v>3</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N17" s="8">
+        <v>2</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A18" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8">
+        <v>20</v>
+      </c>
+      <c r="D18" s="10">
+        <v>10</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N18" s="8">
+        <v>2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="8">
+        <v>30</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="8">
+        <v>10</v>
+      </c>
+      <c r="I19" s="8">
+        <v>10</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N19" s="8">
+        <v>2</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U19" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A20" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="8">
+        <v>40</v>
+      </c>
+      <c r="D20" s="10">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N20" s="8">
+        <v>2</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A21" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="8">
+        <v>40</v>
+      </c>
+      <c r="D21" s="10">
+        <v>2</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N21" s="8">
+        <v>2</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A22" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="8">
+        <v>50</v>
+      </c>
+      <c r="D22" s="10">
+        <v>10</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N22" s="8">
+        <v>2</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="10">
+        <v>55</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="10">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>1</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="N23" s="10">
+        <v>2</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T23" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U23" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="13">
+        <v>5</v>
+      </c>
+      <c r="D24" s="13">
+        <v>10</v>
+      </c>
+      <c r="E24" s="13">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13">
+        <v>1</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="N24" s="13">
+        <v>7</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="P24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8">
+        <v>5</v>
+      </c>
+      <c r="D25" s="10">
+        <v>3</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8">
+        <v>2</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N25" s="8">
+        <v>7</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="8">
+        <v>10</v>
+      </c>
+      <c r="D26" s="10">
+        <v>5</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8">
+        <v>2</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N26" s="8">
+        <v>7</v>
+      </c>
+      <c r="O26" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8">
+        <v>20</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="8">
+        <v>13</v>
+      </c>
+      <c r="I27" s="8">
+        <v>13</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N27" s="8">
+        <v>7</v>
+      </c>
+      <c r="O27" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="8">
+        <v>30</v>
+      </c>
+      <c r="D28" s="10">
+        <v>3</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N28" s="8">
+        <v>7</v>
+      </c>
+      <c r="O28" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="8">
+        <v>30</v>
+      </c>
+      <c r="D29" s="10">
+        <v>3</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="8">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N29" s="8">
+        <v>7</v>
+      </c>
+      <c r="O29" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8">
+        <v>35</v>
+      </c>
+      <c r="D30" s="10">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="8">
+        <v>2</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N30" s="8">
+        <v>7</v>
+      </c>
+      <c r="O30" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="8">
+        <v>40</v>
+      </c>
+      <c r="D31" s="10">
+        <v>3</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N31" s="8">
+        <v>7</v>
+      </c>
+      <c r="O31" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="8">
+        <v>40</v>
+      </c>
+      <c r="D32" s="10">
+        <v>3</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="8">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N32" s="8">
+        <v>7</v>
+      </c>
+      <c r="O32" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="8">
+        <v>45</v>
+      </c>
+      <c r="D33" s="10">
+        <v>2</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8">
+        <v>2</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N33" s="8">
+        <v>7</v>
+      </c>
+      <c r="O33" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="8">
+        <v>45</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="8">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N34" s="8">
+        <v>7</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="8">
+        <v>50</v>
+      </c>
+      <c r="D35" s="10">
+        <v>2</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8">
+        <v>1</v>
+      </c>
+      <c r="I35" s="8">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N35" s="8">
+        <v>7</v>
+      </c>
+      <c r="O35" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="8">
+        <v>59</v>
+      </c>
+      <c r="D36" s="10">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="8">
+        <v>5</v>
+      </c>
+      <c r="I36" s="8">
+        <v>5</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
+        <v>1</v>
+      </c>
+      <c r="L36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N36" s="8">
+        <v>7</v>
+      </c>
+      <c r="O36" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="P36" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S36" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U36" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="13">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1</v>
+      </c>
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="N37" s="13">
+        <v>13</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="P37" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8">
+        <v>5</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="8">
+        <v>6</v>
+      </c>
+      <c r="I38" s="8">
+        <v>6</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0</v>
+      </c>
+      <c r="K38" s="8">
+        <v>1</v>
+      </c>
+      <c r="L38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="N38" s="8">
+        <v>13</v>
+      </c>
+      <c r="O38" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P38" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S38" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T38" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U38" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="8">
+        <v>10</v>
+      </c>
+      <c r="D39" s="10">
+        <v>3</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N39" s="8">
+        <v>13</v>
+      </c>
+      <c r="O39" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P39" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8">
+        <v>15</v>
+      </c>
+      <c r="D40" s="10">
+        <v>2</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" s="8">
+        <v>1</v>
+      </c>
+      <c r="I40" s="8">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8">
+        <v>0</v>
+      </c>
+      <c r="K40" s="8">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N40" s="8">
+        <v>13</v>
+      </c>
+      <c r="O40" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P40" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8">
+        <v>15</v>
+      </c>
+      <c r="D41" s="10">
+        <v>2</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="8">
+        <v>1</v>
+      </c>
+      <c r="I41" s="8">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N41" s="8">
+        <v>13</v>
+      </c>
+      <c r="O41" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P41" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8">
+        <v>20</v>
+      </c>
+      <c r="D42" s="10">
+        <v>1</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="8">
+        <v>30</v>
+      </c>
+      <c r="I42" s="8">
+        <v>30</v>
+      </c>
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <v>1</v>
+      </c>
+      <c r="L42" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N42" s="8">
+        <v>13</v>
+      </c>
+      <c r="O42" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P42" s="8">
+        <v>15</v>
+      </c>
+      <c r="Q42" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S42" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T42" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U42" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8">
+        <v>25</v>
+      </c>
+      <c r="D43" s="10">
+        <v>3</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N43" s="8">
+        <v>13</v>
+      </c>
+      <c r="O43" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P43" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="8">
+        <v>30</v>
+      </c>
+      <c r="D44" s="10">
+        <v>2</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N44" s="8">
+        <v>13</v>
+      </c>
+      <c r="O44" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P44" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="8">
+        <v>35</v>
+      </c>
+      <c r="D45" s="10">
+        <v>2</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N45" s="8">
+        <v>13</v>
+      </c>
+      <c r="O45" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P45" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="8">
+        <v>40</v>
+      </c>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="8">
+        <v>8</v>
+      </c>
+      <c r="I46" s="8">
+        <v>8</v>
+      </c>
+      <c r="J46" s="8">
+        <v>0</v>
+      </c>
+      <c r="K46" s="8">
+        <v>1</v>
+      </c>
+      <c r="L46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N46" s="8">
+        <v>13</v>
+      </c>
+      <c r="O46" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P46" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T46" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U46" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="8">
+        <v>50</v>
+      </c>
+      <c r="D47" s="10">
+        <v>2</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" s="8">
+        <v>1</v>
+      </c>
+      <c r="I47" s="8">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N47" s="8">
+        <v>13</v>
+      </c>
+      <c r="O47" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P47" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="8">
+        <v>50</v>
+      </c>
+      <c r="D48" s="10">
+        <v>2</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1</v>
+      </c>
+      <c r="I48" s="8">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8">
+        <v>0</v>
+      </c>
+      <c r="K48" s="8">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N48" s="8">
+        <v>13</v>
+      </c>
+      <c r="O48" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P48" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A49" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="8">
+        <v>59</v>
+      </c>
+      <c r="D49" s="10">
+        <v>1</v>
+      </c>
+      <c r="E49" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="8">
+        <v>1</v>
+      </c>
+      <c r="I49" s="8">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>1</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="N49" s="8">
+        <v>13</v>
+      </c>
+      <c r="O49" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="P49" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R49" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S49" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T49" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U49" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="13">
+        <v>5</v>
+      </c>
+      <c r="D50" s="13">
+        <v>5</v>
+      </c>
+      <c r="E50" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13">
+        <v>1</v>
+      </c>
+      <c r="I50" s="13">
+        <v>1</v>
+      </c>
+      <c r="J50" s="13">
+        <v>0</v>
+      </c>
+      <c r="K50" s="13">
+        <v>0</v>
+      </c>
+      <c r="L50" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="N50" s="13">
+        <v>20</v>
+      </c>
+      <c r="O50" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P50" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" s="13"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="19"/>
+      <c r="U50" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="8">
+        <v>5</v>
+      </c>
+      <c r="D51" s="10">
+        <v>1</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H51" s="8">
+        <v>6</v>
+      </c>
+      <c r="I51" s="8">
+        <v>6</v>
+      </c>
+      <c r="J51" s="8">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8">
+        <v>1</v>
+      </c>
+      <c r="L51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N51" s="8">
+        <v>20</v>
+      </c>
+      <c r="O51" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P51" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S51" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T51" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U51" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="8">
+        <v>10</v>
+      </c>
+      <c r="D52" s="10">
+        <v>3</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8">
+        <v>1</v>
+      </c>
+      <c r="J52" s="8">
+        <v>0</v>
+      </c>
+      <c r="K52" s="8">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N52" s="8">
+        <v>20</v>
+      </c>
+      <c r="O52" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P52" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="8">
+        <v>15</v>
+      </c>
+      <c r="D53" s="10">
+        <v>1</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H53" s="8">
+        <v>6</v>
+      </c>
+      <c r="I53" s="8">
+        <v>6</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>1</v>
+      </c>
+      <c r="L53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N53" s="8">
+        <v>20</v>
+      </c>
+      <c r="O53" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P53" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S53" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T53" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U53" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="8">
+        <v>20</v>
+      </c>
+      <c r="D54" s="10">
+        <v>1</v>
+      </c>
+      <c r="E54" s="10">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H54" s="8">
+        <v>30</v>
+      </c>
+      <c r="I54" s="8">
+        <v>30</v>
+      </c>
+      <c r="J54" s="8">
+        <v>0</v>
+      </c>
+      <c r="K54" s="8">
+        <v>1</v>
+      </c>
+      <c r="L54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="N54" s="8">
+        <v>20</v>
+      </c>
+      <c r="O54" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P54" s="8">
+        <v>15</v>
+      </c>
+      <c r="Q54" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R54" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S54" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T54" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U54" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="8">
+        <v>22</v>
+      </c>
+      <c r="D55" s="10">
+        <v>3</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1</v>
+      </c>
+      <c r="I55" s="8">
+        <v>2</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N55" s="8">
+        <v>20</v>
+      </c>
+      <c r="O55" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="8">
+        <v>22</v>
+      </c>
+      <c r="D56" s="10">
+        <v>3</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8">
+        <v>2</v>
+      </c>
+      <c r="J56" s="8">
+        <v>0</v>
+      </c>
+      <c r="K56" s="8">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N56" s="8">
+        <v>20</v>
+      </c>
+      <c r="O56" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P56" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="8">
+        <v>25</v>
+      </c>
+      <c r="D57" s="10">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H57" s="8">
+        <v>4</v>
+      </c>
+      <c r="I57" s="8">
+        <v>4</v>
+      </c>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>1</v>
+      </c>
+      <c r="L57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N57" s="8">
+        <v>20</v>
+      </c>
+      <c r="O57" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S57" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T57" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U57" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="8">
+        <v>30</v>
+      </c>
+      <c r="D58" s="10">
+        <v>5</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8">
+        <v>1</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N58" s="8">
+        <v>20</v>
+      </c>
+      <c r="O58" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P58" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="18"/>
+      <c r="U58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="8">
+        <v>35</v>
+      </c>
+      <c r="D59" s="10">
+        <v>3</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" s="8">
+        <v>1</v>
+      </c>
+      <c r="I59" s="8">
+        <v>2</v>
+      </c>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N59" s="8">
+        <v>20</v>
+      </c>
+      <c r="O59" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="18"/>
+      <c r="U59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="8">
+        <v>35</v>
+      </c>
+      <c r="D60" s="10">
+        <v>3</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8">
+        <v>2</v>
+      </c>
+      <c r="J60" s="8">
+        <v>0</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N60" s="8">
+        <v>20</v>
+      </c>
+      <c r="O60" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P60" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="18"/>
+      <c r="U60" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="8">
+        <v>40</v>
+      </c>
+      <c r="D61" s="10">
+        <v>1</v>
+      </c>
+      <c r="E61" s="10">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H61" s="8">
+        <v>6</v>
+      </c>
+      <c r="I61" s="8">
+        <v>6</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8">
+        <v>1</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N61" s="8">
+        <v>20</v>
+      </c>
+      <c r="O61" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P61" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S61" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T61" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U61" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="8">
+        <v>45</v>
+      </c>
+      <c r="D62" s="10">
+        <v>1</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H62" s="8">
+        <v>4</v>
+      </c>
+      <c r="I62" s="8">
+        <v>4</v>
+      </c>
+      <c r="J62" s="8">
+        <v>0</v>
+      </c>
+      <c r="K62" s="8">
+        <v>1</v>
+      </c>
+      <c r="L62" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N62" s="8">
+        <v>20</v>
+      </c>
+      <c r="O62" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P62" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S62" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T62" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U62" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="8">
+        <v>50</v>
+      </c>
+      <c r="D63" s="10">
+        <v>5</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8">
+        <v>1</v>
+      </c>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N63" s="8">
+        <v>20</v>
+      </c>
+      <c r="O63" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="18"/>
+      <c r="U63" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="8">
+        <v>55</v>
+      </c>
+      <c r="D64" s="10">
+        <v>1</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H64" s="8">
+        <v>3</v>
+      </c>
+      <c r="I64" s="8">
+        <v>3</v>
+      </c>
+      <c r="J64" s="8">
+        <v>0</v>
+      </c>
+      <c r="K64" s="8">
+        <v>1</v>
+      </c>
+      <c r="L64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N64" s="8">
+        <v>20</v>
+      </c>
+      <c r="O64" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P64" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S64" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T64" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U64" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A65" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="8">
+        <v>59</v>
+      </c>
+      <c r="D65" s="10">
+        <v>1</v>
+      </c>
+      <c r="E65" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H65" s="8">
+        <v>3</v>
+      </c>
+      <c r="I65" s="8">
+        <v>3</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="N65" s="8">
+        <v>20</v>
+      </c>
+      <c r="O65" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S65" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T65" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U65" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="13">
+        <v>1</v>
+      </c>
+      <c r="D66" s="13">
+        <v>5</v>
+      </c>
+      <c r="E66" s="13">
+        <v>1</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13">
+        <v>1</v>
+      </c>
+      <c r="I66" s="13">
+        <v>2</v>
+      </c>
+      <c r="J66" s="13">
+        <v>0</v>
+      </c>
+      <c r="K66" s="13">
+        <v>0</v>
+      </c>
+      <c r="L66" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M66" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="N66" s="13">
+        <v>25</v>
+      </c>
+      <c r="O66" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="P66" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" s="8">
+        <v>10</v>
+      </c>
+      <c r="D67" s="10">
+        <v>4</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8">
+        <v>1</v>
+      </c>
+      <c r="I67" s="8">
+        <v>2</v>
+      </c>
+      <c r="J67" s="8">
+        <v>0</v>
+      </c>
+      <c r="K67" s="8">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N67" s="8">
+        <v>25</v>
+      </c>
+      <c r="O67" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P67" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="8">
+        <v>20</v>
+      </c>
+      <c r="D68" s="10">
+        <v>3</v>
+      </c>
+      <c r="E68" s="10">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8">
+        <v>1</v>
+      </c>
+      <c r="I68" s="8">
+        <v>2</v>
+      </c>
+      <c r="J68" s="8">
+        <v>0</v>
+      </c>
+      <c r="K68" s="8">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N68" s="8">
+        <v>25</v>
+      </c>
+      <c r="O68" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P68" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="8">
+        <v>30</v>
+      </c>
+      <c r="D69" s="10">
+        <v>5</v>
+      </c>
+      <c r="E69" s="10">
+        <v>1</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8">
+        <v>2</v>
+      </c>
+      <c r="J69" s="8">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8">
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N69" s="8">
+        <v>25</v>
+      </c>
+      <c r="O69" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P69" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="8"/>
+      <c r="U69" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C70" s="8">
+        <v>40</v>
+      </c>
+      <c r="D70" s="10">
+        <v>4</v>
+      </c>
+      <c r="E70" s="10">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8">
+        <v>1</v>
+      </c>
+      <c r="I70" s="8">
+        <v>2</v>
+      </c>
+      <c r="J70" s="8">
+        <v>0</v>
+      </c>
+      <c r="K70" s="8">
+        <v>0</v>
+      </c>
+      <c r="L70" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N70" s="8">
+        <v>25</v>
+      </c>
+      <c r="O70" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P70" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="8"/>
+      <c r="U70" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71" s="8">
+        <v>50</v>
+      </c>
+      <c r="D71" s="10">
+        <v>3</v>
+      </c>
+      <c r="E71" s="10">
+        <v>1</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8">
+        <v>1</v>
+      </c>
+      <c r="I71" s="8">
+        <v>2</v>
+      </c>
+      <c r="J71" s="8">
+        <v>0</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="L71" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N71" s="8">
+        <v>25</v>
+      </c>
+      <c r="O71" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P71" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F62:F71 F2:F61" xr:uid="{3835476A-8A3A-4360-93E9-ACA6F6B87066}">
+      <formula1>"SpawnRandom,SpawnSide,SpawnRandomRange,SpawnRectangle,SpawnOval"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q62:Q71 Q2:Q61" xr:uid="{AB3B203D-B49C-42C6-9A99-904C6D7AB7B0}">
+      <formula1>"false,true"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D671765-6BFE-4606-9C59-1F74507BF60E}">
   <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -13797,7 +18312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22332C8A-7304-4E64-9BD3-13AF5949C9BF}">
   <dimension ref="A1:S10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -14326,7 +18841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88203281-AD27-4579-B140-3641B5403CC3}">
   <dimension ref="A2:F101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -15264,7 +19779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEA4FC2-4AEE-4423-B407-B48D0DBD3E6C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>

--- a/makina-drive/Assets/WaveData.xlsx
+++ b/makina-drive/Assets/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FFAC7A-4329-4D6C-BCF8-D2240E50C5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D6E313-71F9-49EA-AE9B-097F27172712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="2556" windowWidth="15792" windowHeight="9672" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
+    <workbookView xWindow="7248" yWindow="2556" windowWidth="15792" windowHeight="9672" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
   <sheets>
     <sheet name="NormalStageData" sheetId="1" r:id="rId1"/>
@@ -73,6 +73,8 @@
     <author>tc={F1303010-2A80-4241-B0AB-D55B8854DBD2}</author>
     <author>tc={B9F1E812-D077-44D5-ABBC-C517834950CD}</author>
     <author>tc={1A2181FE-6889-4372-9971-867B2DFCF24B}</author>
+    <author>tc={3DA512FF-57D6-4424-BFC9-58D73AE2A994}</author>
+    <author>tc={FB504C90-F82E-4056-ACB9-55ECE8D2AD1F}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{65B6A188-F81E-4121-9301-0FFE406E0779}">
@@ -398,6 +400,26 @@
 ボス出現は20分間隔。</t>
       </text>
     </comment>
+    <comment ref="A392" authorId="32" shapeId="0" xr:uid="{3DA512FF-57D6-4424-BFC9-58D73AE2A994}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇EndlessWaveLast
+ここからある程度無作為に敵を出現させる。
+ボス出現は20分間隔。</t>
+      </text>
+    </comment>
+    <comment ref="A406" authorId="33" shapeId="0" xr:uid="{FB504C90-F82E-4056-ACB9-55ECE8D2AD1F}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    〇EndlessWaveLast
+ここからある程度無作為に敵を出現させる。
+ボス出現は20分間隔。</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -501,7 +523,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="331">
   <si>
     <t>Wave1</t>
   </si>
@@ -2250,13 +2272,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.2:0,DashSpeed:2.2:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.2:0,DashSpeed:2.2:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MaxHP:4.4:0;ATK:3.1:0,Speed:1.5:0,DashSpeed:1.5:0</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -2294,16 +2309,6 @@
   </si>
   <si>
     <t>MaxHP:2.0:0;ATK:2.0:0,Speed:0.1:0,DashSpeed:0.1:0</t>
-  </si>
-  <si>
-    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:0.1:0,DashSpeed:0.1:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.3:0,DashSpeed:2.3:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.3:0,DashSpeed:2.3:0</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2314,21 +2319,10 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:2.0:0;ATK:2.0:0,Speed:0.1:0,DashSpeed:1.0:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>EndlessWave17</t>
   </si>
   <si>
     <t>EndlessWave17</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.4:0,DashSpeed:2.4:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.0:0;ATK:0.5:0,Speed:2.4:0,DashSpeed:2.4:0</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2403,10 +2397,75 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MaxHP:5.25:0;ATK:4.0:0,Speed:2.6:0,DashSpeed:2.6:0</t>
+    <t>EndlessWaveLast2</t>
   </si>
   <si>
-    <t>MaxHP:5.25:0;ATK:4.0:0,Speed:2.6:0,DashSpeed:2.6:0</t>
+    <t>EndlessWaveLast2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:5.25:0;ATK:4.2:0,Speed:2.6:0,DashSpeed:2.6:0</t>
+  </si>
+  <si>
+    <t>MaxHP:5.25:0;ATK:4.2:0,Speed:2.6:0,DashSpeed:2.6:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sizex:42;sizey:30</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:2.5:0;ATK:2.5:0,Speed:0.1:0,DashSpeed:0.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>minDistance:12;maxDistance:30</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.4:0,DashSpeed:2.4:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.4:0,DashSpeed:2.4:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.3:0,DashSpeed:2.3:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.3:0,DashSpeed:2.3:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.2:0,DashSpeed:2.2:0</t>
+  </si>
+  <si>
+    <t>MaxHP:1.0:0;ATK:1.0:0,Speed:2.2:0,DashSpeed:2.2:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EndlessWaveLast3</t>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:3.0:0,Speed:0.1:0,DashSpeed:0.1:0</t>
+  </si>
+  <si>
+    <t>MaxHP:3.0:0;ATK:3.0:0,Speed:0.1:0,DashSpeed:0.1:0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>EndlessWaveLast3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>minDistance:12;maxDistance:75</t>
+  </si>
+  <si>
+    <t>minDistance:12;maxDistance:75</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>radiusx:20;radiusy:14</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4377,6 +4436,16 @@
 ここからある程度無作為に敵を出現させる。
 ボス出現は20分間隔。</text>
   </threadedComment>
+  <threadedComment ref="A392" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{3DA512FF-57D6-4424-BFC9-58D73AE2A994}">
+    <text>〇EndlessWaveLast
+ここからある程度無作為に敵を出現させる。
+ボス出現は20分間隔。</text>
+  </threadedComment>
+  <threadedComment ref="A406" dT="2026-02-09T05:47:58.82" personId="{2A0A573D-128B-4A28-ADE9-75BA9BE0A066}" id="{FB504C90-F82E-4056-ACB9-55ECE8D2AD1F}">
+    <text>〇EndlessWaveLast
+ここからある程度無作為に敵を出現させる。
+ボス出現は20分間隔。</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -4428,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543D6F-3772-40A2-A5A0-40A394077466}">
-  <dimension ref="A1:W388"/>
+  <dimension ref="A1:W417"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.69921875" customWidth="1"/>
@@ -4480,7 +4549,7 @@
         <v>85</v>
       </c>
       <c r="I1" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>87</v>
@@ -22763,7 +22832,7 @@
         <v>102</v>
       </c>
       <c r="G276" s="10" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H276" s="8">
         <v>30</v>
@@ -23496,7 +23565,7 @@
         <v>0.5</v>
       </c>
       <c r="M287" s="13" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="N287" s="13">
         <v>550</v>
@@ -23559,7 +23628,7 @@
         <v>0.5</v>
       </c>
       <c r="M288" s="8" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="N288" s="8">
         <v>550</v>
@@ -23606,13 +23675,13 @@
         <v>143</v>
       </c>
       <c r="G289" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H289" s="8">
         <v>1</v>
       </c>
       <c r="I289" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -23624,7 +23693,7 @@
         <v>0.5</v>
       </c>
       <c r="M289" s="8" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="N289" s="8">
         <v>550</v>
@@ -23677,13 +23746,13 @@
         <v>143</v>
       </c>
       <c r="G290" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H290" s="8">
         <v>1</v>
       </c>
       <c r="I290" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J290" s="8">
         <v>0</v>
@@ -23695,7 +23764,7 @@
         <v>0.5</v>
       </c>
       <c r="M290" s="8" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="N290" s="8">
         <v>550</v>
@@ -23764,7 +23833,7 @@
         <v>0.5</v>
       </c>
       <c r="M291" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N291" s="8">
         <v>550</v>
@@ -23827,7 +23896,7 @@
         <v>0.5</v>
       </c>
       <c r="M292" s="8" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="N292" s="8">
         <v>550</v>
@@ -23890,7 +23959,7 @@
         <v>0.5</v>
       </c>
       <c r="M293" s="8" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="N293" s="8">
         <v>550</v>
@@ -23937,13 +24006,13 @@
         <v>143</v>
       </c>
       <c r="G294" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H294" s="8">
         <v>1</v>
       </c>
       <c r="I294" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -23955,7 +24024,7 @@
         <v>0.5</v>
       </c>
       <c r="M294" s="8" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="N294" s="8">
         <v>550</v>
@@ -24008,13 +24077,13 @@
         <v>143</v>
       </c>
       <c r="G295" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H295" s="8">
         <v>1</v>
       </c>
       <c r="I295" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J295" s="8">
         <v>0</v>
@@ -24026,7 +24095,7 @@
         <v>0.5</v>
       </c>
       <c r="M295" s="8" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="N295" s="8">
         <v>550</v>
@@ -24095,7 +24164,7 @@
         <v>0.5</v>
       </c>
       <c r="M296" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N296" s="8">
         <v>550</v>
@@ -24124,7 +24193,7 @@
     </row>
     <row r="297" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A297" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>1</v>
@@ -24160,7 +24229,7 @@
         <v>0.5</v>
       </c>
       <c r="M297" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N297" s="13">
         <v>620</v>
@@ -24189,7 +24258,7 @@
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A298" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B298" s="8" t="s">
         <v>101</v>
@@ -24225,7 +24294,7 @@
         <v>0.5</v>
       </c>
       <c r="M298" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N298" s="8">
         <v>620</v>
@@ -24254,7 +24323,7 @@
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A299" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B299" s="8" t="s">
         <v>1</v>
@@ -24290,7 +24359,7 @@
         <v>0.5</v>
       </c>
       <c r="M299" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N299" s="8">
         <v>620</v>
@@ -24319,7 +24388,7 @@
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A300" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B300" s="8" t="s">
         <v>101</v>
@@ -24355,7 +24424,7 @@
         <v>0.5</v>
       </c>
       <c r="M300" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N300" s="8">
         <v>620</v>
@@ -24390,7 +24459,7 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A301" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B301" s="8" t="s">
         <v>117</v>
@@ -24426,7 +24495,7 @@
         <v>0.5</v>
       </c>
       <c r="M301" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N301" s="8">
         <v>620</v>
@@ -24455,7 +24524,7 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A302" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B302" s="8" t="s">
         <v>1</v>
@@ -24491,7 +24560,7 @@
         <v>0.5</v>
       </c>
       <c r="M302" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N302" s="8">
         <v>620</v>
@@ -24520,7 +24589,7 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A303" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B303" s="8" t="s">
         <v>107</v>
@@ -24556,7 +24625,7 @@
         <v>0.5</v>
       </c>
       <c r="M303" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N303" s="8">
         <v>620</v>
@@ -24591,7 +24660,7 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A304" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B304" s="8" t="s">
         <v>1</v>
@@ -24627,7 +24696,7 @@
         <v>0.5</v>
       </c>
       <c r="M304" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N304" s="8">
         <v>620</v>
@@ -24656,7 +24725,7 @@
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A305" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B305" s="8" t="s">
         <v>117</v>
@@ -24692,7 +24761,7 @@
         <v>0.5</v>
       </c>
       <c r="M305" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N305" s="8">
         <v>620</v>
@@ -24721,7 +24790,7 @@
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A306" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B306" s="8" t="s">
         <v>117</v>
@@ -24757,7 +24826,7 @@
         <v>0.5</v>
       </c>
       <c r="M306" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N306" s="8">
         <v>620</v>
@@ -24792,7 +24861,7 @@
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A307" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B307" s="8" t="s">
         <v>1</v>
@@ -24828,7 +24897,7 @@
         <v>0.5</v>
       </c>
       <c r="M307" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N307" s="8">
         <v>620</v>
@@ -24857,7 +24926,7 @@
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A308" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B308" s="8" t="s">
         <v>101</v>
@@ -24893,7 +24962,7 @@
         <v>0.5</v>
       </c>
       <c r="M308" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N308" s="8">
         <v>620</v>
@@ -24922,7 +24991,7 @@
     </row>
     <row r="309" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A309" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B309" s="8" t="s">
         <v>76</v>
@@ -24958,7 +25027,7 @@
         <v>0.5</v>
       </c>
       <c r="M309" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N309" s="8">
         <v>620</v>
@@ -24993,7 +25062,7 @@
     </row>
     <row r="310" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A310" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B310" s="13" t="s">
         <v>101</v>
@@ -25027,7 +25096,7 @@
         <v>0.5</v>
       </c>
       <c r="M310" s="13" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="N310" s="13">
         <v>670</v>
@@ -25056,7 +25125,7 @@
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A311" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B311" s="8" t="s">
         <v>170</v>
@@ -25090,7 +25159,7 @@
         <v>0.5</v>
       </c>
       <c r="M311" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N311" s="8">
         <v>670</v>
@@ -25119,7 +25188,7 @@
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A312" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B312" s="8" t="s">
         <v>170</v>
@@ -25137,13 +25206,13 @@
         <v>143</v>
       </c>
       <c r="G312" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H312" s="8">
         <v>1</v>
       </c>
       <c r="I312" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J312" s="8">
         <v>0</v>
@@ -25155,7 +25224,7 @@
         <v>0.5</v>
       </c>
       <c r="M312" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N312" s="8">
         <v>670</v>
@@ -25190,7 +25259,7 @@
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A313" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B313" s="8" t="s">
         <v>170</v>
@@ -25208,13 +25277,13 @@
         <v>143</v>
       </c>
       <c r="G313" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H313" s="8">
         <v>1</v>
       </c>
       <c r="I313" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J313" s="8">
         <v>0</v>
@@ -25226,7 +25295,7 @@
         <v>0.5</v>
       </c>
       <c r="M313" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N313" s="8">
         <v>670</v>
@@ -25261,7 +25330,7 @@
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A314" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B314" s="8" t="s">
         <v>126</v>
@@ -25295,7 +25364,7 @@
         <v>0.5</v>
       </c>
       <c r="M314" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N314" s="8">
         <v>670</v>
@@ -25324,7 +25393,7 @@
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A315" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B315" s="8" t="s">
         <v>170</v>
@@ -25358,7 +25427,7 @@
         <v>0.5</v>
       </c>
       <c r="M315" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N315" s="8">
         <v>670</v>
@@ -25387,7 +25456,7 @@
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A316" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B316" s="8" t="s">
         <v>170</v>
@@ -25421,7 +25490,7 @@
         <v>0.5</v>
       </c>
       <c r="M316" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N316" s="8">
         <v>670</v>
@@ -25450,7 +25519,7 @@
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A317" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B317" s="8" t="s">
         <v>170</v>
@@ -25468,13 +25537,13 @@
         <v>143</v>
       </c>
       <c r="G317" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H317" s="8">
         <v>1</v>
       </c>
       <c r="I317" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
@@ -25486,7 +25555,7 @@
         <v>0.5</v>
       </c>
       <c r="M317" s="8" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="N317" s="8">
         <v>670</v>
@@ -25521,7 +25590,7 @@
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A318" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B318" s="8" t="s">
         <v>170</v>
@@ -25539,13 +25608,13 @@
         <v>143</v>
       </c>
       <c r="G318" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H318" s="8">
         <v>1</v>
       </c>
       <c r="I318" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
@@ -25557,7 +25626,7 @@
         <v>0.5</v>
       </c>
       <c r="M318" s="8" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="N318" s="8">
         <v>670</v>
@@ -25592,7 +25661,7 @@
     </row>
     <row r="319" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A319" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B319" s="8" t="s">
         <v>76</v>
@@ -25626,7 +25695,7 @@
         <v>0.5</v>
       </c>
       <c r="M319" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N319" s="8">
         <v>670</v>
@@ -25655,7 +25724,7 @@
     </row>
     <row r="320" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A320" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B320" s="13" t="s">
         <v>1</v>
@@ -25673,13 +25742,13 @@
         <v>143</v>
       </c>
       <c r="G320" s="13" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="H320" s="13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I320" s="13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J320" s="13">
         <v>0</v>
@@ -25691,7 +25760,7 @@
         <v>0.5</v>
       </c>
       <c r="M320" s="13" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="N320" s="13">
         <v>750</v>
@@ -25706,7 +25775,7 @@
         <v>1.2</v>
       </c>
       <c r="R320" s="13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S320" s="13" t="b">
         <v>0</v>
@@ -25726,7 +25795,7 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A321" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B321" s="8" t="s">
         <v>101</v>
@@ -25744,13 +25813,13 @@
         <v>143</v>
       </c>
       <c r="G321" s="10" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="H321" s="8">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I321" s="8">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -25762,7 +25831,7 @@
         <v>0.5</v>
       </c>
       <c r="M321" s="8" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="N321" s="8">
         <v>750</v>
@@ -25777,7 +25846,7 @@
         <v>1.2</v>
       </c>
       <c r="R321" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S321" s="12" t="b">
         <v>0</v>
@@ -25797,7 +25866,7 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A322" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B322" s="8" t="s">
         <v>117</v>
@@ -25831,7 +25900,7 @@
         <v>0.5</v>
       </c>
       <c r="M322" s="8" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N322" s="8">
         <v>750</v>
@@ -25860,7 +25929,7 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A323" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B323" s="8" t="s">
         <v>1</v>
@@ -25878,13 +25947,13 @@
         <v>143</v>
       </c>
       <c r="G323" s="10" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="H323" s="8">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="I323" s="8">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J323" s="8">
         <v>0</v>
@@ -25896,7 +25965,7 @@
         <v>0.5</v>
       </c>
       <c r="M323" s="8" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="N323" s="8">
         <v>750</v>
@@ -25911,7 +25980,7 @@
         <v>1.2</v>
       </c>
       <c r="R323" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S323" s="12" t="b">
         <v>0</v>
@@ -25931,7 +26000,7 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A324" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B324" s="8" t="s">
         <v>76</v>
@@ -25965,7 +26034,7 @@
         <v>0.5</v>
       </c>
       <c r="M324" s="8" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N324" s="8">
         <v>750</v>
@@ -25994,7 +26063,7 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A325" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B325" s="8" t="s">
         <v>117</v>
@@ -26012,13 +26081,13 @@
         <v>143</v>
       </c>
       <c r="G325" s="10" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="H325" s="8">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I325" s="8">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J325" s="8">
         <v>0</v>
@@ -26030,7 +26099,7 @@
         <v>0.5</v>
       </c>
       <c r="M325" s="8" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="N325" s="8">
         <v>750</v>
@@ -26045,7 +26114,7 @@
         <v>1.2</v>
       </c>
       <c r="R325" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S325" s="12" t="b">
         <v>0</v>
@@ -26065,7 +26134,7 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A326" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B326" s="8" t="s">
         <v>1</v>
@@ -26099,7 +26168,7 @@
         <v>0.5</v>
       </c>
       <c r="M326" s="8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N326" s="8">
         <v>750</v>
@@ -26128,7 +26197,7 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A327" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B327" s="8" t="s">
         <v>101</v>
@@ -26146,13 +26215,13 @@
         <v>143</v>
       </c>
       <c r="G327" s="10" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="H327" s="8">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I327" s="8">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J327" s="8">
         <v>0</v>
@@ -26164,7 +26233,7 @@
         <v>0.5</v>
       </c>
       <c r="M327" s="8" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="N327" s="8">
         <v>750</v>
@@ -26179,7 +26248,7 @@
         <v>1.2</v>
       </c>
       <c r="R327" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S327" s="12" t="b">
         <v>0</v>
@@ -26199,7 +26268,7 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A328" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B328" s="8" t="s">
         <v>76</v>
@@ -26233,7 +26302,7 @@
         <v>0.5</v>
       </c>
       <c r="M328" s="8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N328" s="8">
         <v>750</v>
@@ -26262,7 +26331,7 @@
     </row>
     <row r="329" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A329" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B329" s="8" t="s">
         <v>126</v>
@@ -26296,7 +26365,7 @@
         <v>0.5</v>
       </c>
       <c r="M329" s="8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N329" s="8">
         <v>750</v>
@@ -26325,7 +26394,7 @@
     </row>
     <row r="330" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A330" s="13" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B330" s="13" t="s">
         <v>117</v>
@@ -26359,7 +26428,7 @@
         <v>0.5</v>
       </c>
       <c r="M330" s="13" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="N330" s="13">
         <v>830</v>
@@ -26388,7 +26457,7 @@
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A331" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B331" s="8" t="s">
         <v>249</v>
@@ -26422,7 +26491,7 @@
         <v>0.5</v>
       </c>
       <c r="M331" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N331" s="8">
         <v>830</v>
@@ -26451,7 +26520,7 @@
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A332" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B332" s="8" t="s">
         <v>249</v>
@@ -26469,13 +26538,13 @@
         <v>143</v>
       </c>
       <c r="G332" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H332" s="8">
         <v>1</v>
       </c>
       <c r="I332" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J332" s="8">
         <v>0</v>
@@ -26487,7 +26556,7 @@
         <v>0.5</v>
       </c>
       <c r="M332" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N332" s="8">
         <v>830</v>
@@ -26522,7 +26591,7 @@
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A333" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B333" s="8" t="s">
         <v>117</v>
@@ -26540,13 +26609,13 @@
         <v>143</v>
       </c>
       <c r="G333" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H333" s="8">
         <v>1</v>
       </c>
       <c r="I333" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J333" s="8">
         <v>0</v>
@@ -26558,7 +26627,7 @@
         <v>0.5</v>
       </c>
       <c r="M333" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N333" s="8">
         <v>830</v>
@@ -26593,7 +26662,7 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A334" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B334" s="8" t="s">
         <v>76</v>
@@ -26627,7 +26696,7 @@
         <v>0.5</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="N334" s="8">
         <v>830</v>
@@ -26656,7 +26725,7 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A335" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B335" s="8" t="s">
         <v>249</v>
@@ -26690,7 +26759,7 @@
         <v>0.5</v>
       </c>
       <c r="M335" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N335" s="8">
         <v>830</v>
@@ -26719,7 +26788,7 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A336" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B336" s="8" t="s">
         <v>249</v>
@@ -26753,7 +26822,7 @@
         <v>0.5</v>
       </c>
       <c r="M336" s="8" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="N336" s="8">
         <v>830</v>
@@ -26782,7 +26851,7 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A337" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B337" s="8" t="s">
         <v>249</v>
@@ -26800,13 +26869,13 @@
         <v>143</v>
       </c>
       <c r="G337" s="10" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="H337" s="8">
         <v>1</v>
       </c>
       <c r="I337" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -26818,7 +26887,7 @@
         <v>0.5</v>
       </c>
       <c r="M337" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N337" s="8">
         <v>830</v>
@@ -26853,7 +26922,7 @@
     </row>
     <row r="338" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A338" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B338" s="8" t="s">
         <v>249</v>
@@ -26871,13 +26940,13 @@
         <v>143</v>
       </c>
       <c r="G338" s="10" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H338" s="8">
         <v>1</v>
       </c>
       <c r="I338" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -26889,7 +26958,7 @@
         <v>0.5</v>
       </c>
       <c r="M338" s="8" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N338" s="8">
         <v>830</v>
@@ -26924,7 +26993,7 @@
     </row>
     <row r="339" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A339" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B339" s="8" t="s">
         <v>107</v>
@@ -26958,7 +27027,7 @@
         <v>0.5</v>
       </c>
       <c r="M339" s="8" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="N339" s="8">
         <v>830</v>
@@ -26987,7 +27056,7 @@
     </row>
     <row r="340" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A340" s="13" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B340" s="13" t="s">
         <v>1</v>
@@ -27021,7 +27090,7 @@
         <v>0.5</v>
       </c>
       <c r="M340" s="13" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="N340" s="13">
         <v>910</v>
@@ -27050,7 +27119,7 @@
     </row>
     <row r="341" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A341" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B341" s="8" t="s">
         <v>101</v>
@@ -27084,7 +27153,7 @@
         <v>0.5</v>
       </c>
       <c r="M341" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N341" s="8">
         <v>910</v>
@@ -27113,7 +27182,7 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A342" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B342" s="8" t="s">
         <v>117</v>
@@ -27147,7 +27216,7 @@
         <v>0.5</v>
       </c>
       <c r="M342" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N342" s="8">
         <v>910</v>
@@ -27176,7 +27245,7 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A343" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B343" s="8" t="s">
         <v>1</v>
@@ -27210,7 +27279,7 @@
         <v>0.5</v>
       </c>
       <c r="M343" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N343" s="8">
         <v>910</v>
@@ -27239,7 +27308,7 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A344" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B344" s="8" t="s">
         <v>101</v>
@@ -27275,7 +27344,7 @@
         <v>0.5</v>
       </c>
       <c r="M344" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N344" s="8">
         <v>910</v>
@@ -27310,7 +27379,7 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A345" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B345" s="8" t="s">
         <v>1</v>
@@ -27344,7 +27413,7 @@
         <v>0.5</v>
       </c>
       <c r="M345" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N345" s="8">
         <v>910</v>
@@ -27373,7 +27442,7 @@
     </row>
     <row r="346" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A346" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B346" s="8" t="s">
         <v>76</v>
@@ -27407,7 +27476,7 @@
         <v>0.5</v>
       </c>
       <c r="M346" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N346" s="8">
         <v>910</v>
@@ -27436,7 +27505,7 @@
     </row>
     <row r="347" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A347" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B347" s="8" t="s">
         <v>1</v>
@@ -27454,7 +27523,7 @@
         <v>81</v>
       </c>
       <c r="G347" s="10" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="H347" s="8">
         <v>4</v>
@@ -27472,7 +27541,7 @@
         <v>0.5</v>
       </c>
       <c r="M347" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N347" s="8">
         <v>910</v>
@@ -27507,7 +27576,7 @@
     </row>
     <row r="348" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A348" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B348" s="8" t="s">
         <v>117</v>
@@ -27543,7 +27612,7 @@
         <v>0.5</v>
       </c>
       <c r="M348" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N348" s="8">
         <v>910</v>
@@ -27578,7 +27647,7 @@
     </row>
     <row r="349" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A349" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B349" s="8" t="s">
         <v>107</v>
@@ -27612,7 +27681,7 @@
         <v>0.5</v>
       </c>
       <c r="M349" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N349" s="8">
         <v>910</v>
@@ -27641,7 +27710,7 @@
     </row>
     <row r="350" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A350" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B350" s="8" t="s">
         <v>101</v>
@@ -27677,7 +27746,7 @@
         <v>0.5</v>
       </c>
       <c r="M350" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N350" s="8">
         <v>910</v>
@@ -27712,7 +27781,7 @@
     </row>
     <row r="351" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A351" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B351" s="8" t="s">
         <v>1</v>
@@ -27748,7 +27817,7 @@
         <v>0.5</v>
       </c>
       <c r="M351" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N351" s="8">
         <v>910</v>
@@ -27783,7 +27852,7 @@
     </row>
     <row r="352" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A352" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B352" s="8" t="s">
         <v>126</v>
@@ -27817,7 +27886,7 @@
         <v>0.5</v>
       </c>
       <c r="M352" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N352" s="8">
         <v>910</v>
@@ -27846,7 +27915,7 @@
     </row>
     <row r="353" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A353" s="13" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B353" s="13" t="s">
         <v>1</v>
@@ -27880,7 +27949,7 @@
         <v>0.5</v>
       </c>
       <c r="M353" s="13" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N353" s="13">
         <v>1000</v>
@@ -27909,7 +27978,7 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A354" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B354" s="8" t="s">
         <v>101</v>
@@ -27943,7 +28012,7 @@
         <v>0.5</v>
       </c>
       <c r="M354" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N354" s="8">
         <v>1000</v>
@@ -27972,7 +28041,7 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A355" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B355" s="8" t="s">
         <v>117</v>
@@ -28006,7 +28075,7 @@
         <v>0.5</v>
       </c>
       <c r="M355" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N355" s="8">
         <v>1000</v>
@@ -28035,7 +28104,7 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A356" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B356" s="8" t="s">
         <v>117</v>
@@ -28071,7 +28140,7 @@
         <v>0.5</v>
       </c>
       <c r="M356" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N356" s="8">
         <v>1000</v>
@@ -28106,7 +28175,7 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A357" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B357" s="8" t="s">
         <v>1</v>
@@ -28140,7 +28209,7 @@
         <v>0.5</v>
       </c>
       <c r="M357" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N357" s="8">
         <v>1000</v>
@@ -28169,7 +28238,7 @@
     </row>
     <row r="358" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A358" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B358" s="8" t="s">
         <v>76</v>
@@ -28205,7 +28274,7 @@
         <v>0.5</v>
       </c>
       <c r="M358" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N358" s="8">
         <v>1000</v>
@@ -28240,7 +28309,7 @@
     </row>
     <row r="359" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A359" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B359" s="8" t="s">
         <v>107</v>
@@ -28274,7 +28343,7 @@
         <v>0.5</v>
       </c>
       <c r="M359" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N359" s="8">
         <v>1000</v>
@@ -28303,7 +28372,7 @@
     </row>
     <row r="360" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A360" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B360" s="8" t="s">
         <v>1</v>
@@ -28321,7 +28390,7 @@
         <v>102</v>
       </c>
       <c r="G360" s="10" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H360" s="8">
         <v>16</v>
@@ -28339,7 +28408,7 @@
         <v>0.5</v>
       </c>
       <c r="M360" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N360" s="8">
         <v>1000</v>
@@ -28374,7 +28443,7 @@
     </row>
     <row r="361" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A361" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B361" s="8" t="s">
         <v>117</v>
@@ -28410,7 +28479,7 @@
         <v>0.5</v>
       </c>
       <c r="M361" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N361" s="8">
         <v>1000</v>
@@ -28445,7 +28514,7 @@
     </row>
     <row r="362" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A362" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B362" s="8" t="s">
         <v>107</v>
@@ -28479,7 +28548,7 @@
         <v>0.5</v>
       </c>
       <c r="M362" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N362" s="8">
         <v>1000</v>
@@ -28508,7 +28577,7 @@
     </row>
     <row r="363" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A363" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B363" s="8" t="s">
         <v>126</v>
@@ -28544,7 +28613,7 @@
         <v>0.5</v>
       </c>
       <c r="M363" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N363" s="8">
         <v>1000</v>
@@ -28579,7 +28648,7 @@
     </row>
     <row r="364" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A364" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B364" s="8" t="s">
         <v>1</v>
@@ -28615,7 +28684,7 @@
         <v>0.5</v>
       </c>
       <c r="M364" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N364" s="8">
         <v>1000</v>
@@ -28650,7 +28719,7 @@
     </row>
     <row r="365" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A365" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B365" s="8" t="s">
         <v>1</v>
@@ -28684,7 +28753,7 @@
         <v>0.5</v>
       </c>
       <c r="M365" s="8" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="N365" s="8">
         <v>1000</v>
@@ -28713,7 +28782,7 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A366" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B366" s="8" t="s">
         <v>76</v>
@@ -28749,7 +28818,7 @@
         <v>0.5</v>
       </c>
       <c r="M366" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N366" s="8">
         <v>1000</v>
@@ -28784,7 +28853,7 @@
     </row>
     <row r="367" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A367" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B367" s="8" t="s">
         <v>107</v>
@@ -28818,7 +28887,7 @@
         <v>0.5</v>
       </c>
       <c r="M367" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N367" s="8">
         <v>1000</v>
@@ -28847,7 +28916,7 @@
     </row>
     <row r="368" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A368" s="13" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B368" s="13" t="s">
         <v>1</v>
@@ -28881,7 +28950,7 @@
         <v>0.5</v>
       </c>
       <c r="M368" s="13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="N368" s="13">
         <v>1100</v>
@@ -28910,7 +28979,7 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A369" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B369" s="8" t="s">
         <v>101</v>
@@ -28944,7 +29013,7 @@
         <v>0.5</v>
       </c>
       <c r="M369" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N369" s="8">
         <v>1100</v>
@@ -28973,7 +29042,7 @@
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A370" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B370" s="8" t="s">
         <v>117</v>
@@ -29007,7 +29076,7 @@
         <v>0.5</v>
       </c>
       <c r="M370" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N370" s="8">
         <v>1100</v>
@@ -29036,7 +29105,7 @@
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A371" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B371" s="8" t="s">
         <v>1</v>
@@ -29054,7 +29123,7 @@
         <v>102</v>
       </c>
       <c r="G371" s="10" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="H371" s="8">
         <v>30</v>
@@ -29072,7 +29141,7 @@
         <v>0.5</v>
       </c>
       <c r="M371" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N371" s="8">
         <v>1100</v>
@@ -29107,7 +29176,7 @@
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A372" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B372" s="8" t="s">
         <v>1</v>
@@ -29141,7 +29210,7 @@
         <v>0.5</v>
       </c>
       <c r="M372" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N372" s="8">
         <v>1100</v>
@@ -29170,7 +29239,7 @@
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A373" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B373" s="8" t="s">
         <v>76</v>
@@ -29204,7 +29273,7 @@
         <v>0.5</v>
       </c>
       <c r="M373" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N373" s="8">
         <v>1100</v>
@@ -29233,7 +29302,7 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A374" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B374" s="8" t="s">
         <v>101</v>
@@ -29251,7 +29320,7 @@
         <v>81</v>
       </c>
       <c r="G374" s="10" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="H374" s="8">
         <v>4</v>
@@ -29269,7 +29338,7 @@
         <v>0.5</v>
       </c>
       <c r="M374" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N374" s="8">
         <v>1100</v>
@@ -29304,7 +29373,7 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A375" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B375" s="8" t="s">
         <v>101</v>
@@ -29338,7 +29407,7 @@
         <v>0.5</v>
       </c>
       <c r="M375" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N375" s="8">
         <v>1100</v>
@@ -29367,7 +29436,7 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A376" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B376" s="8" t="s">
         <v>107</v>
@@ -29401,7 +29470,7 @@
         <v>0.5</v>
       </c>
       <c r="M376" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N376" s="8">
         <v>1100</v>
@@ -29430,7 +29499,7 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A377" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B377" s="8" t="s">
         <v>117</v>
@@ -29448,7 +29517,7 @@
         <v>143</v>
       </c>
       <c r="G377" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H377" s="8">
         <v>5</v>
@@ -29466,7 +29535,7 @@
         <v>0.5</v>
       </c>
       <c r="M377" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N377" s="8">
         <v>1100</v>
@@ -29501,7 +29570,7 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A378" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B378" s="8" t="s">
         <v>117</v>
@@ -29535,7 +29604,7 @@
         <v>0.5</v>
       </c>
       <c r="M378" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N378" s="8">
         <v>1100</v>
@@ -29564,7 +29633,7 @@
     </row>
     <row r="379" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A379" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B379" s="8" t="s">
         <v>126</v>
@@ -29598,7 +29667,7 @@
         <v>0.5</v>
       </c>
       <c r="M379" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N379" s="8">
         <v>1100</v>
@@ -29627,7 +29696,7 @@
     </row>
     <row r="380" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A380" s="13" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B380" s="13" t="s">
         <v>1</v>
@@ -29646,7 +29715,7 @@
       </c>
       <c r="G380" s="13"/>
       <c r="H380" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I380" s="13">
         <v>2</v>
@@ -29661,7 +29730,7 @@
         <v>0.5</v>
       </c>
       <c r="M380" s="13" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="N380" s="13">
         <v>1200</v>
@@ -29690,7 +29759,7 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A381" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B381" s="8" t="s">
         <v>101</v>
@@ -29709,7 +29778,7 @@
       </c>
       <c r="G381" s="10"/>
       <c r="H381" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I381" s="8">
         <v>2</v>
@@ -29724,7 +29793,7 @@
         <v>0.5</v>
       </c>
       <c r="M381" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N381" s="8">
         <v>1200</v>
@@ -29753,7 +29822,7 @@
     </row>
     <row r="382" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A382" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B382" s="8" t="s">
         <v>117</v>
@@ -29772,7 +29841,7 @@
       </c>
       <c r="G382" s="10"/>
       <c r="H382" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I382" s="8">
         <v>2</v>
@@ -29787,7 +29856,7 @@
         <v>0.5</v>
       </c>
       <c r="M382" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N382" s="8">
         <v>1200</v>
@@ -29816,41 +29885,43 @@
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A383" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C383" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D383" s="10">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E383" s="10">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="F383" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G383" s="10"/>
+        <v>143</v>
+      </c>
+      <c r="G383" s="10" t="s">
+        <v>258</v>
+      </c>
       <c r="H383" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I383" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J383" s="8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K383" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L383" s="8">
         <v>0.5</v>
       </c>
       <c r="M383" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N383" s="8">
         <v>1200</v>
@@ -29870,50 +29941,58 @@
       <c r="S383" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="T383" s="10"/>
-      <c r="U383" s="10"/>
-      <c r="V383" s="18"/>
+      <c r="T383" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U383" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V383" s="18" t="s">
+        <v>217</v>
+      </c>
       <c r="W383" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A384" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C384" s="8">
+        <v>1</v>
+      </c>
+      <c r="D384" s="10">
         <v>20</v>
       </c>
-      <c r="D384" s="10">
-        <v>1</v>
-      </c>
       <c r="E384" s="10">
-        <v>0.5</v>
+        <v>19</v>
       </c>
       <c r="F384" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G384" s="10"/>
+        <v>143</v>
+      </c>
+      <c r="G384" s="10" t="s">
+        <v>258</v>
+      </c>
       <c r="H384" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I384" s="8">
         <v>1</v>
       </c>
       <c r="J384" s="8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K384" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L384" s="8">
         <v>0.5</v>
       </c>
       <c r="M384" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N384" s="8">
         <v>1200</v>
@@ -29933,50 +30012,58 @@
       <c r="S384" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="T384" s="10"/>
-      <c r="U384" s="10"/>
-      <c r="V384" s="18"/>
+      <c r="T384" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U384" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V384" s="18" t="s">
+        <v>217</v>
+      </c>
       <c r="W384" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="385" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A385" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C385" s="8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D385" s="10">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E385" s="10">
-        <v>0.5</v>
+        <v>29.5</v>
       </c>
       <c r="F385" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G385" s="10"/>
+        <v>143</v>
+      </c>
+      <c r="G385" s="10" t="s">
+        <v>258</v>
+      </c>
       <c r="H385" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I385" s="8">
         <v>1</v>
       </c>
       <c r="J385" s="8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K385" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L385" s="8">
         <v>0.5</v>
       </c>
       <c r="M385" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N385" s="8">
         <v>1200</v>
@@ -29996,22 +30083,28 @@
       <c r="S385" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="T385" s="10"/>
-      <c r="U385" s="10"/>
-      <c r="V385" s="18"/>
+      <c r="T385" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U385" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V385" s="18" t="s">
+        <v>217</v>
+      </c>
       <c r="W385" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="386" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A386" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B386" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C386" s="8">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D386" s="10">
         <v>1</v>
@@ -30039,7 +30132,7 @@
         <v>0.5</v>
       </c>
       <c r="M386" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N386" s="8">
         <v>1200</v>
@@ -30068,13 +30161,13 @@
     </row>
     <row r="387" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A387" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B387" s="8" t="s">
         <v>107</v>
       </c>
       <c r="C387" s="8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D387" s="10">
         <v>1</v>
@@ -30102,7 +30195,7 @@
         <v>0.5</v>
       </c>
       <c r="M387" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N387" s="8">
         <v>1200</v>
@@ -30131,13 +30224,13 @@
     </row>
     <row r="388" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A388" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B388" s="8" t="s">
         <v>126</v>
       </c>
       <c r="C388" s="8">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D388" s="10">
         <v>1</v>
@@ -30165,7 +30258,7 @@
         <v>0.5</v>
       </c>
       <c r="M388" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N388" s="8">
         <v>1200</v>
@@ -30192,18 +30285,1909 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="389" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A389" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C389" s="8">
+        <v>40</v>
+      </c>
+      <c r="D389" s="10">
+        <v>1</v>
+      </c>
+      <c r="E389" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F389" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G389" s="10"/>
+      <c r="H389" s="8">
+        <v>1</v>
+      </c>
+      <c r="I389" s="8">
+        <v>1</v>
+      </c>
+      <c r="J389" s="8">
+        <v>0</v>
+      </c>
+      <c r="K389" s="8">
+        <v>0</v>
+      </c>
+      <c r="L389" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M389" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N389" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O389" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P389" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q389" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R389" s="8">
+        <v>0</v>
+      </c>
+      <c r="S389" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T389" s="10"/>
+      <c r="U389" s="10"/>
+      <c r="V389" s="18"/>
+      <c r="W389" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A390" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C390" s="8">
+        <v>50</v>
+      </c>
+      <c r="D390" s="10">
+        <v>1</v>
+      </c>
+      <c r="E390" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F390" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G390" s="10"/>
+      <c r="H390" s="8">
+        <v>1</v>
+      </c>
+      <c r="I390" s="8">
+        <v>1</v>
+      </c>
+      <c r="J390" s="8">
+        <v>0</v>
+      </c>
+      <c r="K390" s="8">
+        <v>0</v>
+      </c>
+      <c r="L390" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M390" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N390" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O390" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P390" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q390" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R390" s="8">
+        <v>0</v>
+      </c>
+      <c r="S390" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T390" s="10"/>
+      <c r="U390" s="10"/>
+      <c r="V390" s="18"/>
+      <c r="W390" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A391" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B391" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C391" s="8">
+        <v>59</v>
+      </c>
+      <c r="D391" s="10">
+        <v>1</v>
+      </c>
+      <c r="E391" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F391" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G391" s="10"/>
+      <c r="H391" s="8">
+        <v>1</v>
+      </c>
+      <c r="I391" s="8">
+        <v>1</v>
+      </c>
+      <c r="J391" s="8">
+        <v>0</v>
+      </c>
+      <c r="K391" s="8">
+        <v>0</v>
+      </c>
+      <c r="L391" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M391" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N391" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O391" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P391" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q391" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R391" s="8">
+        <v>0</v>
+      </c>
+      <c r="S391" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T391" s="10"/>
+      <c r="U391" s="10"/>
+      <c r="V391" s="18"/>
+      <c r="W391" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A392" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="B392" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C392" s="13">
+        <v>1</v>
+      </c>
+      <c r="D392" s="13">
+        <v>20</v>
+      </c>
+      <c r="E392" s="13">
+        <v>5</v>
+      </c>
+      <c r="F392" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G392" s="13"/>
+      <c r="H392" s="13">
+        <v>0</v>
+      </c>
+      <c r="I392" s="13">
+        <v>2</v>
+      </c>
+      <c r="J392" s="13">
+        <v>59</v>
+      </c>
+      <c r="K392" s="13">
+        <v>0</v>
+      </c>
+      <c r="L392" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M392" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="N392" s="13">
+        <v>1200</v>
+      </c>
+      <c r="O392" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="P392" s="13">
+        <v>150</v>
+      </c>
+      <c r="Q392" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="R392" s="13">
+        <v>0</v>
+      </c>
+      <c r="S392" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T392" s="13"/>
+      <c r="U392" s="13"/>
+      <c r="V392" s="13"/>
+      <c r="W392" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A393" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B393" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C393" s="8">
+        <v>1</v>
+      </c>
+      <c r="D393" s="10">
+        <v>20</v>
+      </c>
+      <c r="E393" s="10">
+        <v>8</v>
+      </c>
+      <c r="F393" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G393" s="10"/>
+      <c r="H393" s="8">
+        <v>0</v>
+      </c>
+      <c r="I393" s="8">
+        <v>2</v>
+      </c>
+      <c r="J393" s="8">
+        <v>59</v>
+      </c>
+      <c r="K393" s="8">
+        <v>0</v>
+      </c>
+      <c r="L393" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M393" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N393" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O393" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P393" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q393" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R393" s="8">
+        <v>0</v>
+      </c>
+      <c r="S393" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T393" s="10"/>
+      <c r="U393" s="10"/>
+      <c r="V393" s="18"/>
+      <c r="W393" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="394" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A394" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C394" s="8">
+        <v>1</v>
+      </c>
+      <c r="D394" s="10">
+        <v>20</v>
+      </c>
+      <c r="E394" s="10">
+        <v>14.5</v>
+      </c>
+      <c r="F394" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G394" s="10"/>
+      <c r="H394" s="8">
+        <v>0</v>
+      </c>
+      <c r="I394" s="8">
+        <v>2</v>
+      </c>
+      <c r="J394" s="8">
+        <v>59</v>
+      </c>
+      <c r="K394" s="8">
+        <v>0</v>
+      </c>
+      <c r="L394" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M394" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N394" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O394" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P394" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q394" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R394" s="8">
+        <v>0</v>
+      </c>
+      <c r="S394" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T394" s="10"/>
+      <c r="U394" s="10"/>
+      <c r="V394" s="18"/>
+      <c r="W394" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A395" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C395" s="8">
+        <v>1</v>
+      </c>
+      <c r="D395" s="10">
+        <v>20</v>
+      </c>
+      <c r="E395" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F395" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G395" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H395" s="8">
+        <v>0</v>
+      </c>
+      <c r="I395" s="8">
+        <v>1</v>
+      </c>
+      <c r="J395" s="8">
+        <v>59</v>
+      </c>
+      <c r="K395" s="8">
+        <v>1</v>
+      </c>
+      <c r="L395" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M395" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N395" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O395" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P395" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q395" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R395" s="8">
+        <v>0</v>
+      </c>
+      <c r="S395" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T395" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U395" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V395" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W395" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A396" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B396" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C396" s="8">
+        <v>1</v>
+      </c>
+      <c r="D396" s="10">
+        <v>20</v>
+      </c>
+      <c r="E396" s="10">
+        <v>19</v>
+      </c>
+      <c r="F396" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G396" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H396" s="8">
+        <v>0</v>
+      </c>
+      <c r="I396" s="8">
+        <v>3</v>
+      </c>
+      <c r="J396" s="8">
+        <v>59</v>
+      </c>
+      <c r="K396" s="8">
+        <v>1</v>
+      </c>
+      <c r="L396" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M396" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N396" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O396" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P396" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q396" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R396" s="8">
+        <v>0</v>
+      </c>
+      <c r="S396" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T396" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U396" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V396" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W396" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A397" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C397" s="8">
+        <v>1</v>
+      </c>
+      <c r="D397" s="10">
+        <v>20</v>
+      </c>
+      <c r="E397" s="10">
+        <v>29.5</v>
+      </c>
+      <c r="F397" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G397" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H397" s="8">
+        <v>0</v>
+      </c>
+      <c r="I397" s="8">
+        <v>1</v>
+      </c>
+      <c r="J397" s="8">
+        <v>59</v>
+      </c>
+      <c r="K397" s="8">
+        <v>1</v>
+      </c>
+      <c r="L397" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M397" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N397" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O397" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P397" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q397" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R397" s="8">
+        <v>0</v>
+      </c>
+      <c r="S397" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T397" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U397" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V397" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W397" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A398" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C398" s="8">
+        <v>1</v>
+      </c>
+      <c r="D398" s="10">
+        <v>1</v>
+      </c>
+      <c r="E398" s="10">
+        <v>2</v>
+      </c>
+      <c r="F398" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G398" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="H398" s="8">
+        <v>50</v>
+      </c>
+      <c r="I398" s="8">
+        <v>50</v>
+      </c>
+      <c r="J398" s="8">
+        <v>0</v>
+      </c>
+      <c r="K398" s="8">
+        <v>1</v>
+      </c>
+      <c r="L398" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M398" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N398" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O398" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P398" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q398" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R398" s="8">
+        <v>25</v>
+      </c>
+      <c r="S398" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T398" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U398" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V398" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W398" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A399" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C399" s="8">
+        <v>10</v>
+      </c>
+      <c r="D399" s="10">
+        <v>1</v>
+      </c>
+      <c r="E399" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F399" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G399" s="10"/>
+      <c r="H399" s="8">
+        <v>1</v>
+      </c>
+      <c r="I399" s="8">
+        <v>1</v>
+      </c>
+      <c r="J399" s="8">
+        <v>0</v>
+      </c>
+      <c r="K399" s="8">
+        <v>0</v>
+      </c>
+      <c r="L399" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M399" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N399" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O399" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P399" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q399" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R399" s="8">
+        <v>0</v>
+      </c>
+      <c r="S399" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T399" s="10"/>
+      <c r="U399" s="10"/>
+      <c r="V399" s="18"/>
+      <c r="W399" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A400" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C400" s="8">
+        <v>20</v>
+      </c>
+      <c r="D400" s="10">
+        <v>1</v>
+      </c>
+      <c r="E400" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F400" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G400" s="10"/>
+      <c r="H400" s="8">
+        <v>1</v>
+      </c>
+      <c r="I400" s="8">
+        <v>1</v>
+      </c>
+      <c r="J400" s="8">
+        <v>0</v>
+      </c>
+      <c r="K400" s="8">
+        <v>0</v>
+      </c>
+      <c r="L400" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M400" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N400" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O400" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P400" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q400" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R400" s="8">
+        <v>0</v>
+      </c>
+      <c r="S400" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T400" s="10"/>
+      <c r="U400" s="10"/>
+      <c r="V400" s="18"/>
+      <c r="W400" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="401" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A401" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C401" s="8">
+        <v>30</v>
+      </c>
+      <c r="D401" s="10">
+        <v>1</v>
+      </c>
+      <c r="E401" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F401" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G401" s="10"/>
+      <c r="H401" s="8">
+        <v>1</v>
+      </c>
+      <c r="I401" s="8">
+        <v>1</v>
+      </c>
+      <c r="J401" s="8">
+        <v>0</v>
+      </c>
+      <c r="K401" s="8">
+        <v>0</v>
+      </c>
+      <c r="L401" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M401" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N401" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O401" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P401" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q401" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R401" s="8">
+        <v>0</v>
+      </c>
+      <c r="S401" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T401" s="10"/>
+      <c r="U401" s="10"/>
+      <c r="V401" s="18"/>
+      <c r="W401" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="402" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A402" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C402" s="8">
+        <v>30</v>
+      </c>
+      <c r="D402" s="10">
+        <v>1</v>
+      </c>
+      <c r="E402" s="10">
+        <v>2</v>
+      </c>
+      <c r="F402" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G402" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="H402" s="8">
+        <v>50</v>
+      </c>
+      <c r="I402" s="8">
+        <v>50</v>
+      </c>
+      <c r="J402" s="8">
+        <v>0</v>
+      </c>
+      <c r="K402" s="8">
+        <v>1</v>
+      </c>
+      <c r="L402" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M402" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N402" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O402" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P402" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q402" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R402" s="8">
+        <v>25</v>
+      </c>
+      <c r="S402" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T402" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U402" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V402" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W402" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="403" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A403" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C403" s="8">
+        <v>40</v>
+      </c>
+      <c r="D403" s="10">
+        <v>1</v>
+      </c>
+      <c r="E403" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F403" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G403" s="10"/>
+      <c r="H403" s="8">
+        <v>1</v>
+      </c>
+      <c r="I403" s="8">
+        <v>1</v>
+      </c>
+      <c r="J403" s="8">
+        <v>0</v>
+      </c>
+      <c r="K403" s="8">
+        <v>0</v>
+      </c>
+      <c r="L403" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M403" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N403" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O403" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P403" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q403" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R403" s="8">
+        <v>0</v>
+      </c>
+      <c r="S403" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T403" s="10"/>
+      <c r="U403" s="10"/>
+      <c r="V403" s="18"/>
+      <c r="W403" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="404" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A404" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C404" s="8">
+        <v>50</v>
+      </c>
+      <c r="D404" s="10">
+        <v>1</v>
+      </c>
+      <c r="E404" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F404" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G404" s="10"/>
+      <c r="H404" s="8">
+        <v>1</v>
+      </c>
+      <c r="I404" s="8">
+        <v>1</v>
+      </c>
+      <c r="J404" s="8">
+        <v>0</v>
+      </c>
+      <c r="K404" s="8">
+        <v>0</v>
+      </c>
+      <c r="L404" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M404" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N404" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O404" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P404" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q404" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R404" s="8">
+        <v>0</v>
+      </c>
+      <c r="S404" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T404" s="10"/>
+      <c r="U404" s="10"/>
+      <c r="V404" s="18"/>
+      <c r="W404" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="405" spans="1:23" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A405" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C405" s="8">
+        <v>59</v>
+      </c>
+      <c r="D405" s="10">
+        <v>1</v>
+      </c>
+      <c r="E405" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F405" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G405" s="10"/>
+      <c r="H405" s="8">
+        <v>1</v>
+      </c>
+      <c r="I405" s="8">
+        <v>1</v>
+      </c>
+      <c r="J405" s="8">
+        <v>0</v>
+      </c>
+      <c r="K405" s="8">
+        <v>0</v>
+      </c>
+      <c r="L405" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M405" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N405" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O405" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P405" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q405" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R405" s="8">
+        <v>0</v>
+      </c>
+      <c r="S405" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T405" s="10"/>
+      <c r="U405" s="10"/>
+      <c r="V405" s="18"/>
+      <c r="W405" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="406" spans="1:23" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A406" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B406" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C406" s="13">
+        <v>1</v>
+      </c>
+      <c r="D406" s="13">
+        <v>20</v>
+      </c>
+      <c r="E406" s="13">
+        <v>5</v>
+      </c>
+      <c r="F406" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G406" s="13"/>
+      <c r="H406" s="13">
+        <v>0</v>
+      </c>
+      <c r="I406" s="13">
+        <v>2</v>
+      </c>
+      <c r="J406" s="13">
+        <v>59</v>
+      </c>
+      <c r="K406" s="13">
+        <v>0</v>
+      </c>
+      <c r="L406" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="M406" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="N406" s="13">
+        <v>1200</v>
+      </c>
+      <c r="O406" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="P406" s="13">
+        <v>150</v>
+      </c>
+      <c r="Q406" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="R406" s="13">
+        <v>0</v>
+      </c>
+      <c r="S406" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T406" s="13"/>
+      <c r="U406" s="13"/>
+      <c r="V406" s="13"/>
+      <c r="W406" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A407" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C407" s="8">
+        <v>1</v>
+      </c>
+      <c r="D407" s="10">
+        <v>20</v>
+      </c>
+      <c r="E407" s="10">
+        <v>8</v>
+      </c>
+      <c r="F407" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G407" s="10"/>
+      <c r="H407" s="8">
+        <v>0</v>
+      </c>
+      <c r="I407" s="8">
+        <v>2</v>
+      </c>
+      <c r="J407" s="8">
+        <v>59</v>
+      </c>
+      <c r="K407" s="8">
+        <v>0</v>
+      </c>
+      <c r="L407" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M407" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N407" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O407" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P407" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q407" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R407" s="8">
+        <v>0</v>
+      </c>
+      <c r="S407" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T407" s="10"/>
+      <c r="U407" s="10"/>
+      <c r="V407" s="18"/>
+      <c r="W407" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A408" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C408" s="8">
+        <v>1</v>
+      </c>
+      <c r="D408" s="10">
+        <v>20</v>
+      </c>
+      <c r="E408" s="10">
+        <v>14.5</v>
+      </c>
+      <c r="F408" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G408" s="10"/>
+      <c r="H408" s="8">
+        <v>0</v>
+      </c>
+      <c r="I408" s="8">
+        <v>2</v>
+      </c>
+      <c r="J408" s="8">
+        <v>59</v>
+      </c>
+      <c r="K408" s="8">
+        <v>0</v>
+      </c>
+      <c r="L408" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M408" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N408" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O408" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P408" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q408" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R408" s="8">
+        <v>0</v>
+      </c>
+      <c r="S408" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T408" s="10"/>
+      <c r="U408" s="10"/>
+      <c r="V408" s="18"/>
+      <c r="W408" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A409" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C409" s="8">
+        <v>1</v>
+      </c>
+      <c r="D409" s="10">
+        <v>20</v>
+      </c>
+      <c r="E409" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F409" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G409" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H409" s="8">
+        <v>0</v>
+      </c>
+      <c r="I409" s="8">
+        <v>1</v>
+      </c>
+      <c r="J409" s="8">
+        <v>59</v>
+      </c>
+      <c r="K409" s="8">
+        <v>1</v>
+      </c>
+      <c r="L409" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M409" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N409" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O409" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P409" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q409" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R409" s="8">
+        <v>0</v>
+      </c>
+      <c r="S409" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T409" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U409" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V409" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W409" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="410" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A410" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C410" s="8">
+        <v>1</v>
+      </c>
+      <c r="D410" s="10">
+        <v>20</v>
+      </c>
+      <c r="E410" s="10">
+        <v>19</v>
+      </c>
+      <c r="F410" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G410" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H410" s="8">
+        <v>0</v>
+      </c>
+      <c r="I410" s="8">
+        <v>1</v>
+      </c>
+      <c r="J410" s="8">
+        <v>59</v>
+      </c>
+      <c r="K410" s="8">
+        <v>1</v>
+      </c>
+      <c r="L410" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M410" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N410" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O410" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P410" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q410" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R410" s="8">
+        <v>0</v>
+      </c>
+      <c r="S410" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T410" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U410" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V410" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W410" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="411" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A411" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C411" s="8">
+        <v>1</v>
+      </c>
+      <c r="D411" s="10">
+        <v>20</v>
+      </c>
+      <c r="E411" s="10">
+        <v>29.5</v>
+      </c>
+      <c r="F411" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G411" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H411" s="8">
+        <v>0</v>
+      </c>
+      <c r="I411" s="8">
+        <v>3</v>
+      </c>
+      <c r="J411" s="8">
+        <v>59</v>
+      </c>
+      <c r="K411" s="8">
+        <v>1</v>
+      </c>
+      <c r="L411" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M411" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N411" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O411" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P411" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q411" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R411" s="8">
+        <v>0</v>
+      </c>
+      <c r="S411" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T411" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U411" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V411" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W411" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="412" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A412" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C412" s="8">
+        <v>10</v>
+      </c>
+      <c r="D412" s="10">
+        <v>1</v>
+      </c>
+      <c r="E412" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F412" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G412" s="10"/>
+      <c r="H412" s="8">
+        <v>1</v>
+      </c>
+      <c r="I412" s="8">
+        <v>1</v>
+      </c>
+      <c r="J412" s="8">
+        <v>0</v>
+      </c>
+      <c r="K412" s="8">
+        <v>0</v>
+      </c>
+      <c r="L412" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M412" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N412" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O412" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P412" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q412" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R412" s="8">
+        <v>0</v>
+      </c>
+      <c r="S412" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T412" s="10"/>
+      <c r="U412" s="10"/>
+      <c r="V412" s="18"/>
+      <c r="W412" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="413" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A413" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C413" s="8">
+        <v>20</v>
+      </c>
+      <c r="D413" s="10">
+        <v>1</v>
+      </c>
+      <c r="E413" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F413" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G413" s="10"/>
+      <c r="H413" s="8">
+        <v>1</v>
+      </c>
+      <c r="I413" s="8">
+        <v>1</v>
+      </c>
+      <c r="J413" s="8">
+        <v>0</v>
+      </c>
+      <c r="K413" s="8">
+        <v>0</v>
+      </c>
+      <c r="L413" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M413" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N413" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O413" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P413" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q413" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R413" s="8">
+        <v>0</v>
+      </c>
+      <c r="S413" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T413" s="10"/>
+      <c r="U413" s="10"/>
+      <c r="V413" s="18"/>
+      <c r="W413" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="414" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A414" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C414" s="8">
+        <v>30</v>
+      </c>
+      <c r="D414" s="10">
+        <v>1</v>
+      </c>
+      <c r="E414" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F414" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G414" s="10"/>
+      <c r="H414" s="8">
+        <v>1</v>
+      </c>
+      <c r="I414" s="8">
+        <v>1</v>
+      </c>
+      <c r="J414" s="8">
+        <v>0</v>
+      </c>
+      <c r="K414" s="8">
+        <v>0</v>
+      </c>
+      <c r="L414" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M414" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N414" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O414" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P414" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q414" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R414" s="8">
+        <v>0</v>
+      </c>
+      <c r="S414" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T414" s="10"/>
+      <c r="U414" s="10"/>
+      <c r="V414" s="18"/>
+      <c r="W414" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="415" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A415" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C415" s="8">
+        <v>40</v>
+      </c>
+      <c r="D415" s="10">
+        <v>1</v>
+      </c>
+      <c r="E415" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F415" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G415" s="10"/>
+      <c r="H415" s="8">
+        <v>1</v>
+      </c>
+      <c r="I415" s="8">
+        <v>1</v>
+      </c>
+      <c r="J415" s="8">
+        <v>0</v>
+      </c>
+      <c r="K415" s="8">
+        <v>0</v>
+      </c>
+      <c r="L415" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M415" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N415" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O415" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P415" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q415" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R415" s="8">
+        <v>0</v>
+      </c>
+      <c r="S415" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T415" s="10"/>
+      <c r="U415" s="10"/>
+      <c r="V415" s="18"/>
+      <c r="W415" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="416" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A416" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C416" s="8">
+        <v>50</v>
+      </c>
+      <c r="D416" s="10">
+        <v>1</v>
+      </c>
+      <c r="E416" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F416" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G416" s="10"/>
+      <c r="H416" s="8">
+        <v>1</v>
+      </c>
+      <c r="I416" s="8">
+        <v>1</v>
+      </c>
+      <c r="J416" s="8">
+        <v>0</v>
+      </c>
+      <c r="K416" s="8">
+        <v>0</v>
+      </c>
+      <c r="L416" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M416" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N416" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O416" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P416" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q416" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R416" s="8">
+        <v>0</v>
+      </c>
+      <c r="S416" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T416" s="10"/>
+      <c r="U416" s="10"/>
+      <c r="V416" s="18"/>
+      <c r="W416" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="417" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A417" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C417" s="8">
+        <v>59</v>
+      </c>
+      <c r="D417" s="10">
+        <v>1</v>
+      </c>
+      <c r="E417" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F417" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G417" s="10"/>
+      <c r="H417" s="8">
+        <v>1</v>
+      </c>
+      <c r="I417" s="8">
+        <v>1</v>
+      </c>
+      <c r="J417" s="8">
+        <v>0</v>
+      </c>
+      <c r="K417" s="8">
+        <v>0</v>
+      </c>
+      <c r="L417" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M417" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N417" s="8">
+        <v>1200</v>
+      </c>
+      <c r="O417" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P417" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q417" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R417" s="8">
+        <v>0</v>
+      </c>
+      <c r="S417" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T417" s="10"/>
+      <c r="U417" s="10"/>
+      <c r="V417" s="18"/>
+      <c r="W417" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="F2:F388 K2:K388 T2:V388">
+  <conditionalFormatting sqref="F2:F417 K2:K417 T2:V417">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(OR(COUNTBLANK($T2:$V2),$K2&lt;=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S388" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S417" xr:uid="{358C8FD7-9BB2-4790-9B7D-37307CA727E6}">
       <formula1>"false,true"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F388" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F417" xr:uid="{D09AAB4C-67FA-4A68-B83E-5A1578E3D874}">
       <formula1>"SpawnRandom,SpawnSide,SpawnRandomRange,SpawnRectangle,SpawnOval"</formula1>
     </dataValidation>
   </dataValidations>
